--- a/api/1/xlsx/pt/RegionM49.xlsx
+++ b/api/1/xlsx/pt/RegionM49.xlsx
@@ -22,63 +22,63 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:small-island-developing-states</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:land-locked-developing-countries</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:developed-developing</t>
+  </si>
+  <si>
+    <t>codeforiati:least-developed-countries</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>codeforiati:global-code</t>
   </si>
   <si>
-    <t>codeforiati:developed-developing</t>
-  </si>
-  <si>
-    <t>codeforiati:least-developed-countries</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:land-locked-developing-countries</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:small-island-developing-states</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>Developing</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
     <t>001</t>
   </si>
   <si>
-    <t>Developing</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>729</t>
   </si>
   <si>
+    <t>SDN</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>SDN</t>
-  </si>
-  <si>
     <t>SD</t>
   </si>
   <si>
@@ -1114,13 +1114,13 @@
     <t>060</t>
   </si>
   <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>BMU</t>
+  </si>
+  <si>
     <t>Developed</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
-    <t>BMU</t>
   </si>
   <si>
     <t>BM</t>
@@ -2785,22 +2785,22 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2820,22 +2820,22 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2855,22 +2855,22 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2890,22 +2890,22 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2922,25 +2922,25 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
       <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
       </c>
       <c r="K6" t="s">
         <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2960,22 +2960,22 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>14</v>
       </c>
       <c r="K7" t="s">
         <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2995,22 +2995,22 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3027,28 +3027,28 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3065,28 +3065,28 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
         <v>47</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3097,34 +3097,34 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
         <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3141,28 +3141,28 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
         <v>53</v>
       </c>
       <c r="L12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3179,28 +3179,28 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3217,28 +3217,28 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
         <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3255,28 +3255,28 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K15" t="s">
         <v>62</v>
       </c>
       <c r="L15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3293,28 +3293,28 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K16" t="s">
         <v>65</v>
       </c>
       <c r="L16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3331,28 +3331,28 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
         <v>68</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3369,28 +3369,28 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
         <v>71</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3401,34 +3401,34 @@
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K19" t="s">
         <v>74</v>
       </c>
       <c r="L19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3445,28 +3445,28 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K20" t="s">
         <v>77</v>
       </c>
       <c r="L20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3483,28 +3483,28 @@
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
         <v>80</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -3521,28 +3521,28 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K22" t="s">
         <v>83</v>
       </c>
       <c r="L22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3559,28 +3559,28 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
         <v>86</v>
       </c>
       <c r="L23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -3591,34 +3591,34 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K24" t="s">
         <v>89</v>
       </c>
       <c r="L24" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -3635,28 +3635,28 @@
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
         <v>92</v>
       </c>
       <c r="L25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -3673,28 +3673,28 @@
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
         <v>95</v>
       </c>
       <c r="L26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -3711,28 +3711,28 @@
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
         <v>98</v>
       </c>
       <c r="L27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -3749,28 +3749,28 @@
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K28" t="s">
         <v>101</v>
       </c>
       <c r="L28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -3787,28 +3787,28 @@
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="H29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I29" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
         <v>104</v>
       </c>
       <c r="L29" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -3825,28 +3825,28 @@
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="H30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s">
         <v>107</v>
       </c>
       <c r="L30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -3863,28 +3863,28 @@
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
         <v>111</v>
       </c>
       <c r="L31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3901,28 +3901,28 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="K32" t="s">
         <v>114</v>
       </c>
       <c r="L32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3939,28 +3939,28 @@
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I33" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
         <v>117</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3977,28 +3977,28 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="H34" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
         <v>120</v>
       </c>
       <c r="L34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -4015,28 +4015,28 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="K35" t="s">
         <v>123</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -4053,28 +4053,28 @@
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I36" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="K36" t="s">
         <v>126</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -4091,28 +4091,28 @@
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I37" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="K37" t="s">
         <v>129</v>
       </c>
       <c r="L37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -4129,28 +4129,28 @@
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="K38" t="s">
         <v>132</v>
       </c>
       <c r="L38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4161,34 +4161,34 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="I39" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="K39" t="s">
         <v>135</v>
       </c>
       <c r="L39" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -4205,28 +4205,28 @@
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="I40" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="K40" t="s">
         <v>139</v>
       </c>
       <c r="L40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -4243,28 +4243,28 @@
         <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="J41" t="s">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="K41" t="s">
         <v>142</v>
       </c>
       <c r="L41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -4281,28 +4281,28 @@
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="I42" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="K42" t="s">
         <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -4319,28 +4319,28 @@
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="I43" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="K43" t="s">
         <v>148</v>
       </c>
       <c r="L43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -4357,28 +4357,28 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="I44" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="K44" t="s">
         <v>151</v>
       </c>
       <c r="L44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -4395,28 +4395,28 @@
         <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I45" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K45" t="s">
         <v>155</v>
       </c>
       <c r="L45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -4433,28 +4433,28 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G46" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="H46" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I46" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K46" t="s">
         <v>158</v>
       </c>
       <c r="L46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -4465,34 +4465,34 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="H47" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I47" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="K47" t="s">
         <v>161</v>
       </c>
       <c r="L47" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -4509,28 +4509,28 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I48" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="K48" t="s">
         <v>164</v>
       </c>
       <c r="L48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -4547,28 +4547,28 @@
         <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I49" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K49" t="s">
         <v>167</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -4585,28 +4585,28 @@
         <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I50" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="K50" t="s">
         <v>170</v>
       </c>
       <c r="L50" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -4623,28 +4623,28 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I51" t="s">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K51" t="s">
         <v>173</v>
       </c>
       <c r="L51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -4655,34 +4655,34 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I52" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J52" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K52" t="s">
         <v>176</v>
       </c>
       <c r="L52" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -4699,28 +4699,28 @@
         <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I53" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="J53" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K53" t="s">
         <v>179</v>
       </c>
       <c r="L53" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -4737,28 +4737,28 @@
         <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F54" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G54" t="s">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I54" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="J54" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K54" t="s">
         <v>182</v>
       </c>
       <c r="L54" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -4775,28 +4775,28 @@
         <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I55" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="J55" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K55" t="s">
         <v>185</v>
       </c>
       <c r="L55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -4813,28 +4813,28 @@
         <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F56" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="H56" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I56" t="s">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K56" t="s">
         <v>188</v>
       </c>
       <c r="L56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -4851,28 +4851,28 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F57" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I57" t="s">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="K57" t="s">
         <v>191</v>
       </c>
       <c r="L57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -4889,28 +4889,28 @@
         <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I58" t="s">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="K58" t="s">
         <v>194</v>
       </c>
       <c r="L58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -4927,28 +4927,28 @@
         <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>196</v>
       </c>
       <c r="H59" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I59" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K59" t="s">
         <v>197</v>
       </c>
       <c r="L59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -4965,28 +4965,28 @@
         <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>199</v>
       </c>
       <c r="H60" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I60" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K60" t="s">
         <v>200</v>
       </c>
       <c r="L60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -5003,28 +5003,28 @@
         <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F61" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="H61" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="I61" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="K61" t="s">
         <v>203</v>
       </c>
       <c r="L61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -5035,34 +5035,34 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E62" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F62" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="H62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I62" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K62" t="s">
         <v>209</v>
       </c>
       <c r="L62" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -5073,34 +5073,34 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E63" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="H63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I63" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K63" t="s">
         <v>212</v>
       </c>
       <c r="L63" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -5111,34 +5111,34 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>214</v>
       </c>
       <c r="H64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I64" t="s">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K64" t="s">
         <v>215</v>
       </c>
       <c r="L64" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -5149,34 +5149,34 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>16</v>
+        <v>217</v>
       </c>
       <c r="H65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I65" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K65" t="s">
         <v>218</v>
       </c>
       <c r="L65" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -5187,34 +5187,34 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E66" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="H66" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I66" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K66" t="s">
         <v>221</v>
       </c>
       <c r="L66" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -5225,34 +5225,34 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F67" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>223</v>
       </c>
       <c r="H67" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I67" t="s">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K67" t="s">
         <v>224</v>
       </c>
       <c r="L67" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -5263,34 +5263,34 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E68" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F68" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>226</v>
       </c>
       <c r="H68" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I68" t="s">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K68" t="s">
         <v>227</v>
       </c>
       <c r="L68" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5304,31 +5304,31 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E69" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F69" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="H69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I69" t="s">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="J69" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K69" t="s">
         <v>230</v>
       </c>
       <c r="L69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -5339,34 +5339,34 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F70" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I70" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K70" t="s">
         <v>233</v>
       </c>
       <c r="L70" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -5377,34 +5377,34 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E71" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F71" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I71" t="s">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="J71" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K71" t="s">
         <v>236</v>
       </c>
       <c r="L71" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -5415,34 +5415,34 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F72" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>238</v>
       </c>
       <c r="H72" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I72" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="J72" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K72" t="s">
         <v>239</v>
       </c>
       <c r="L72" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -5453,34 +5453,34 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E73" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F73" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="H73" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I73" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K73" t="s">
         <v>242</v>
       </c>
       <c r="L73" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -5491,34 +5491,34 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F74" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="H74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I74" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="J74" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K74" t="s">
         <v>245</v>
       </c>
       <c r="L74" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -5532,31 +5532,31 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F75" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="H75" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I75" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="J75" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K75" t="s">
         <v>248</v>
       </c>
       <c r="L75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -5567,34 +5567,34 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E76" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="F76" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="H76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I76" t="s">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="J76" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="K76" t="s">
         <v>251</v>
       </c>
       <c r="L76" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -5605,34 +5605,34 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F77" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
       <c r="H77" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I77" t="s">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K77" t="s">
         <v>254</v>
       </c>
       <c r="L77" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -5646,31 +5646,31 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F78" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="H78" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I78" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K78" t="s">
         <v>257</v>
       </c>
       <c r="L78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -5681,34 +5681,34 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E79" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F79" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>259</v>
       </c>
       <c r="H79" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I79" t="s">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K79" t="s">
         <v>260</v>
       </c>
       <c r="L79" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -5719,34 +5719,34 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F80" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="H80" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I80" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K80" t="s">
         <v>263</v>
       </c>
       <c r="L80" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -5760,31 +5760,31 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F81" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>265</v>
       </c>
       <c r="H81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I81" t="s">
-        <v>265</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K81" t="s">
         <v>266</v>
       </c>
       <c r="L81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -5795,34 +5795,34 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F82" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c r="H82" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I82" t="s">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K82" t="s">
         <v>269</v>
       </c>
       <c r="L82" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -5833,34 +5833,34 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F83" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="H83" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I83" t="s">
-        <v>271</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K83" t="s">
         <v>272</v>
       </c>
       <c r="L83" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -5874,31 +5874,31 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F84" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>274</v>
       </c>
       <c r="H84" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I84" t="s">
-        <v>274</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K84" t="s">
         <v>275</v>
       </c>
       <c r="L84" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -5909,34 +5909,34 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F85" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="H85" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I85" t="s">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K85" t="s">
         <v>278</v>
       </c>
       <c r="L85" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -5947,34 +5947,34 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="H86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I86" t="s">
-        <v>280</v>
+        <v>18</v>
       </c>
       <c r="J86" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K86" t="s">
         <v>281</v>
       </c>
       <c r="L86" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -5985,34 +5985,34 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E87" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F87" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>16</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I87" t="s">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K87" t="s">
         <v>284</v>
       </c>
       <c r="L87" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -6026,31 +6026,31 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F88" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="H88" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I88" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="J88" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K88" t="s">
         <v>287</v>
       </c>
       <c r="L88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -6061,34 +6061,34 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F89" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>289</v>
       </c>
       <c r="H89" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I89" t="s">
-        <v>289</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="K89" t="s">
         <v>290</v>
       </c>
       <c r="L89" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -6099,34 +6099,34 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F90" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s">
-        <v>16</v>
+        <v>292</v>
       </c>
       <c r="H90" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I90" t="s">
-        <v>292</v>
+        <v>18</v>
       </c>
       <c r="J90" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K90" t="s">
         <v>294</v>
       </c>
       <c r="L90" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -6140,31 +6140,31 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E91" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F91" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="H91" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I91" t="s">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="J91" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K91" t="s">
         <v>297</v>
       </c>
       <c r="L91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -6178,31 +6178,31 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E92" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F92" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>299</v>
       </c>
       <c r="H92" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I92" t="s">
-        <v>299</v>
+        <v>18</v>
       </c>
       <c r="J92" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K92" t="s">
         <v>300</v>
       </c>
       <c r="L92" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -6216,31 +6216,31 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E93" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c r="H93" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
-        <v>302</v>
+        <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K93" t="s">
         <v>303</v>
       </c>
       <c r="L93" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -6254,31 +6254,31 @@
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F94" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>305</v>
       </c>
       <c r="H94" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I94" t="s">
-        <v>305</v>
+        <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K94" t="s">
         <v>306</v>
       </c>
       <c r="L94" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -6292,31 +6292,31 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F95" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>16</v>
+        <v>308</v>
       </c>
       <c r="H95" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I95" t="s">
-        <v>308</v>
+        <v>18</v>
       </c>
       <c r="J95" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K95" t="s">
         <v>309</v>
       </c>
       <c r="L95" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -6330,31 +6330,31 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E96" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F96" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>311</v>
       </c>
       <c r="H96" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I96" t="s">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="J96" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K96" t="s">
         <v>312</v>
       </c>
       <c r="L96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -6368,31 +6368,31 @@
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>16</v>
+        <v>314</v>
       </c>
       <c r="H97" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="I97" t="s">
-        <v>314</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="K97" t="s">
         <v>315</v>
       </c>
       <c r="L97" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -6406,31 +6406,31 @@
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F98" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="H98" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I98" t="s">
-        <v>317</v>
+        <v>18</v>
       </c>
       <c r="J98" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K98" t="s">
         <v>319</v>
       </c>
       <c r="L98" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -6444,31 +6444,31 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="G99" t="s">
-        <v>31</v>
+        <v>321</v>
       </c>
       <c r="H99" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I99" t="s">
-        <v>321</v>
+        <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K99" t="s">
         <v>322</v>
       </c>
       <c r="L99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -6482,31 +6482,31 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E100" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F100" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="H100" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I100" t="s">
-        <v>324</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K100" t="s">
         <v>325</v>
       </c>
       <c r="L100" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -6520,31 +6520,31 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F101" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c r="H101" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I101" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K101" t="s">
         <v>328</v>
       </c>
       <c r="L101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -6558,31 +6558,31 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E102" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F102" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="H102" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I102" t="s">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K102" t="s">
         <v>331</v>
       </c>
       <c r="L102" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -6596,31 +6596,31 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F103" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="H103" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I103" t="s">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K103" t="s">
         <v>334</v>
       </c>
       <c r="L103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -6634,31 +6634,31 @@
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F104" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="H104" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I104" t="s">
-        <v>336</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K104" t="s">
         <v>337</v>
       </c>
       <c r="L104" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -6672,31 +6672,31 @@
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F105" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="H105" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I105" t="s">
-        <v>339</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K105" t="s">
         <v>340</v>
       </c>
       <c r="L105" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -6710,31 +6710,31 @@
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E106" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F106" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s">
-        <v>16</v>
+        <v>342</v>
       </c>
       <c r="H106" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I106" t="s">
-        <v>342</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K106" t="s">
         <v>343</v>
       </c>
       <c r="L106" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -6745,34 +6745,34 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="H107" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I107" t="s">
-        <v>345</v>
+        <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K107" t="s">
         <v>346</v>
       </c>
       <c r="L107" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -6786,31 +6786,31 @@
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F108" t="s">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>348</v>
       </c>
       <c r="H108" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I108" t="s">
-        <v>348</v>
+        <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K108" t="s">
         <v>349</v>
       </c>
       <c r="L108" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -6824,31 +6824,31 @@
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>16</v>
+        <v>351</v>
       </c>
       <c r="H109" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I109" t="s">
-        <v>351</v>
+        <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K109" t="s">
         <v>352</v>
       </c>
       <c r="L109" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -6862,31 +6862,31 @@
         <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E110" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F110" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="H110" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I110" t="s">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="J110" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K110" t="s">
         <v>355</v>
       </c>
       <c r="L110" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -6897,34 +6897,34 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E111" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F111" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="H111" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I111" t="s">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="J111" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K111" t="s">
         <v>358</v>
       </c>
       <c r="L111" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -6938,31 +6938,31 @@
         <v>14</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E112" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>16</v>
+        <v>360</v>
       </c>
       <c r="H112" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I112" t="s">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="J112" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K112" t="s">
         <v>361</v>
       </c>
       <c r="L112" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -6976,31 +6976,31 @@
         <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="F113" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="H113" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="I113" t="s">
-        <v>363</v>
+        <v>18</v>
       </c>
       <c r="J113" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="K113" t="s">
         <v>364</v>
       </c>
       <c r="L113" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -7014,28 +7014,28 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
+        <v>205</v>
+      </c>
+      <c r="E114" t="s">
         <v>366</v>
       </c>
-      <c r="E114" t="s">
-        <v>16</v>
-      </c>
       <c r="F114" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>16</v>
-      </c>
-      <c r="H114" t="s">
         <v>367</v>
       </c>
       <c r="I114" t="s">
         <v>368</v>
       </c>
+      <c r="J114" t="s">
+        <v>14</v>
+      </c>
       <c r="K114" t="s">
         <v>369</v>
       </c>
       <c r="L114" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -7049,28 +7049,28 @@
         <v>14</v>
       </c>
       <c r="D115" t="s">
+        <v>205</v>
+      </c>
+      <c r="E115" t="s">
         <v>366</v>
       </c>
-      <c r="E115" t="s">
-        <v>16</v>
-      </c>
       <c r="F115" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>16</v>
-      </c>
-      <c r="H115" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I115" t="s">
-        <v>371</v>
+        <v>368</v>
+      </c>
+      <c r="J115" t="s">
+        <v>14</v>
       </c>
       <c r="K115" t="s">
         <v>372</v>
       </c>
       <c r="L115" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -7084,28 +7084,28 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
+        <v>205</v>
+      </c>
+      <c r="E116" t="s">
         <v>366</v>
       </c>
-      <c r="E116" t="s">
-        <v>16</v>
-      </c>
       <c r="F116" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>16</v>
-      </c>
-      <c r="H116" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="I116" t="s">
-        <v>374</v>
+        <v>368</v>
+      </c>
+      <c r="J116" t="s">
+        <v>14</v>
       </c>
       <c r="K116" t="s">
         <v>375</v>
       </c>
       <c r="L116" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -7119,28 +7119,28 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
+        <v>205</v>
+      </c>
+      <c r="E117" t="s">
         <v>366</v>
       </c>
-      <c r="E117" t="s">
-        <v>16</v>
-      </c>
       <c r="F117" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="I117" t="s">
-        <v>377</v>
+        <v>368</v>
+      </c>
+      <c r="J117" t="s">
+        <v>14</v>
       </c>
       <c r="K117" t="s">
         <v>378</v>
       </c>
       <c r="L117" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -7154,28 +7154,28 @@
         <v>14</v>
       </c>
       <c r="D118" t="s">
+        <v>205</v>
+      </c>
+      <c r="E118" t="s">
         <v>366</v>
       </c>
-      <c r="E118" t="s">
-        <v>16</v>
-      </c>
       <c r="F118" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>16</v>
-      </c>
-      <c r="H118" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="I118" t="s">
-        <v>380</v>
+        <v>368</v>
+      </c>
+      <c r="J118" t="s">
+        <v>14</v>
       </c>
       <c r="K118" t="s">
         <v>381</v>
       </c>
       <c r="L118" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -7188,20 +7188,20 @@
       <c r="C119" t="s">
         <v>14</v>
       </c>
-      <c r="E119" t="s">
-        <v>16</v>
+      <c r="F119" t="s">
+        <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>16</v>
-      </c>
-      <c r="I119" t="s">
         <v>383</v>
+      </c>
+      <c r="J119" t="s">
+        <v>14</v>
       </c>
       <c r="K119" t="s">
         <v>384</v>
       </c>
       <c r="L119" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7215,28 +7215,28 @@
         <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E120" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="F120" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G120" t="s">
-        <v>31</v>
-      </c>
-      <c r="H120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I120" t="s">
-        <v>388</v>
+        <v>18</v>
+      </c>
+      <c r="J120" t="s">
+        <v>14</v>
       </c>
       <c r="K120" t="s">
         <v>389</v>
       </c>
       <c r="L120" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -7250,28 +7250,28 @@
         <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E121" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="F121" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G121" t="s">
-        <v>31</v>
-      </c>
-      <c r="H121" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I121" t="s">
-        <v>391</v>
+        <v>18</v>
+      </c>
+      <c r="J121" t="s">
+        <v>14</v>
       </c>
       <c r="K121" t="s">
         <v>392</v>
       </c>
       <c r="L121" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -7285,28 +7285,28 @@
         <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E122" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="F122" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G122" t="s">
-        <v>31</v>
-      </c>
-      <c r="H122" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="I122" t="s">
-        <v>394</v>
+        <v>18</v>
+      </c>
+      <c r="J122" t="s">
+        <v>14</v>
       </c>
       <c r="K122" t="s">
         <v>395</v>
       </c>
       <c r="L122" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -7320,28 +7320,28 @@
         <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="F123" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G123" t="s">
-        <v>31</v>
-      </c>
-      <c r="H123" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="I123" t="s">
-        <v>397</v>
+        <v>18</v>
+      </c>
+      <c r="J123" t="s">
+        <v>14</v>
       </c>
       <c r="K123" t="s">
         <v>398</v>
       </c>
       <c r="L123" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -7355,28 +7355,28 @@
         <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>387</v>
       </c>
       <c r="F124" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G124" t="s">
-        <v>31</v>
-      </c>
-      <c r="H124" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="I124" t="s">
-        <v>400</v>
+        <v>18</v>
+      </c>
+      <c r="J124" t="s">
+        <v>14</v>
       </c>
       <c r="K124" t="s">
         <v>401</v>
       </c>
       <c r="L124" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -7390,28 +7390,28 @@
         <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E125" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F125" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G125" t="s">
-        <v>16</v>
-      </c>
-      <c r="H125" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I125" t="s">
-        <v>404</v>
+        <v>18</v>
+      </c>
+      <c r="J125" t="s">
+        <v>14</v>
       </c>
       <c r="K125" t="s">
         <v>405</v>
       </c>
       <c r="L125" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -7425,28 +7425,28 @@
         <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E126" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F126" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s">
-        <v>16</v>
-      </c>
-      <c r="H126" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I126" t="s">
-        <v>407</v>
+        <v>18</v>
+      </c>
+      <c r="J126" t="s">
+        <v>14</v>
       </c>
       <c r="K126" t="s">
         <v>408</v>
       </c>
       <c r="L126" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -7460,28 +7460,28 @@
         <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E127" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F127" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>16</v>
-      </c>
-      <c r="H127" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="I127" t="s">
-        <v>410</v>
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>14</v>
       </c>
       <c r="K127" t="s">
         <v>411</v>
       </c>
       <c r="L127" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -7495,28 +7495,28 @@
         <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E128" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F128" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>16</v>
-      </c>
-      <c r="H128" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="I128" t="s">
-        <v>413</v>
+        <v>18</v>
+      </c>
+      <c r="J128" t="s">
+        <v>14</v>
       </c>
       <c r="K128" t="s">
         <v>414</v>
       </c>
       <c r="L128" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -7530,28 +7530,28 @@
         <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F129" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>16</v>
-      </c>
-      <c r="H129" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="I129" t="s">
-        <v>416</v>
+        <v>368</v>
+      </c>
+      <c r="J129" t="s">
+        <v>14</v>
       </c>
       <c r="K129" t="s">
         <v>417</v>
       </c>
       <c r="L129" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -7565,28 +7565,28 @@
         <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F130" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G130" t="s">
-        <v>31</v>
-      </c>
-      <c r="H130" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="I130" t="s">
-        <v>419</v>
+        <v>18</v>
+      </c>
+      <c r="J130" t="s">
+        <v>14</v>
       </c>
       <c r="K130" t="s">
         <v>420</v>
       </c>
       <c r="L130" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -7600,28 +7600,28 @@
         <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E131" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="F131" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="I131" t="s">
-        <v>422</v>
+        <v>18</v>
+      </c>
+      <c r="J131" t="s">
+        <v>14</v>
       </c>
       <c r="K131" t="s">
         <v>423</v>
       </c>
       <c r="L131" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -7635,28 +7635,28 @@
         <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E132" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F132" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G132" t="s">
-        <v>16</v>
-      </c>
-      <c r="H132" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I132" t="s">
-        <v>426</v>
+        <v>18</v>
+      </c>
+      <c r="J132" t="s">
+        <v>14</v>
       </c>
       <c r="K132" t="s">
         <v>427</v>
       </c>
       <c r="L132" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -7670,28 +7670,28 @@
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E133" t="s">
-        <v>31</v>
+        <v>425</v>
       </c>
       <c r="F133" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>16</v>
-      </c>
-      <c r="H133" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="I133" t="s">
-        <v>429</v>
+        <v>18</v>
+      </c>
+      <c r="J133" t="s">
+        <v>32</v>
       </c>
       <c r="K133" t="s">
         <v>430</v>
       </c>
       <c r="L133" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -7705,28 +7705,28 @@
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E134" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F134" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s">
-        <v>16</v>
-      </c>
-      <c r="H134" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="I134" t="s">
-        <v>432</v>
+        <v>18</v>
+      </c>
+      <c r="J134" t="s">
+        <v>14</v>
       </c>
       <c r="K134" t="s">
         <v>433</v>
       </c>
       <c r="L134" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -7740,28 +7740,28 @@
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E135" t="s">
-        <v>31</v>
+        <v>425</v>
       </c>
       <c r="F135" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G135" t="s">
-        <v>31</v>
-      </c>
-      <c r="H135" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="I135" t="s">
-        <v>435</v>
+        <v>18</v>
+      </c>
+      <c r="J135" t="s">
+        <v>32</v>
       </c>
       <c r="K135" t="s">
         <v>436</v>
       </c>
       <c r="L135" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -7775,28 +7775,28 @@
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E136" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F136" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>16</v>
-      </c>
-      <c r="H136" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="I136" t="s">
-        <v>438</v>
+        <v>18</v>
+      </c>
+      <c r="J136" t="s">
+        <v>14</v>
       </c>
       <c r="K136" t="s">
         <v>439</v>
       </c>
       <c r="L136" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -7810,28 +7810,28 @@
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E137" t="s">
-        <v>31</v>
+        <v>425</v>
       </c>
       <c r="F137" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>16</v>
-      </c>
-      <c r="H137" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="I137" t="s">
-        <v>441</v>
+        <v>18</v>
+      </c>
+      <c r="J137" t="s">
+        <v>32</v>
       </c>
       <c r="K137" t="s">
         <v>442</v>
       </c>
       <c r="L137" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -7845,28 +7845,28 @@
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E138" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F138" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>16</v>
-      </c>
-      <c r="H138" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="I138" t="s">
-        <v>444</v>
+        <v>18</v>
+      </c>
+      <c r="J138" t="s">
+        <v>14</v>
       </c>
       <c r="K138" t="s">
         <v>445</v>
       </c>
       <c r="L138" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -7877,31 +7877,31 @@
         <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E139" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F139" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>16</v>
-      </c>
-      <c r="H139" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="I139" t="s">
-        <v>447</v>
+        <v>18</v>
+      </c>
+      <c r="J139" t="s">
+        <v>14</v>
       </c>
       <c r="K139" t="s">
         <v>448</v>
       </c>
       <c r="L139" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -7915,28 +7915,28 @@
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E140" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F140" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>16</v>
-      </c>
-      <c r="H140" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="I140" t="s">
-        <v>450</v>
+        <v>18</v>
+      </c>
+      <c r="J140" t="s">
+        <v>14</v>
       </c>
       <c r="K140" t="s">
         <v>451</v>
       </c>
       <c r="L140" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -7947,31 +7947,31 @@
         <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E141" t="s">
-        <v>31</v>
+        <v>425</v>
       </c>
       <c r="F141" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>16</v>
-      </c>
-      <c r="H141" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="I141" t="s">
-        <v>453</v>
+        <v>18</v>
+      </c>
+      <c r="J141" t="s">
+        <v>32</v>
       </c>
       <c r="K141" t="s">
         <v>454</v>
       </c>
       <c r="L141" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -7985,28 +7985,28 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E142" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="F142" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>16</v>
-      </c>
-      <c r="H142" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="I142" t="s">
-        <v>456</v>
+        <v>18</v>
+      </c>
+      <c r="J142" t="s">
+        <v>14</v>
       </c>
       <c r="K142" t="s">
         <v>457</v>
       </c>
       <c r="L142" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -8020,28 +8020,28 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E143" t="s">
-        <v>31</v>
+        <v>459</v>
       </c>
       <c r="F143" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G143" t="s">
-        <v>31</v>
-      </c>
-      <c r="H143" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I143" t="s">
-        <v>460</v>
+        <v>18</v>
+      </c>
+      <c r="J143" t="s">
+        <v>32</v>
       </c>
       <c r="K143" t="s">
         <v>461</v>
       </c>
       <c r="L143" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -8055,28 +8055,28 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E144" t="s">
-        <v>31</v>
+        <v>459</v>
       </c>
       <c r="F144" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>16</v>
-      </c>
-      <c r="H144" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="I144" t="s">
-        <v>463</v>
+        <v>18</v>
+      </c>
+      <c r="J144" t="s">
+        <v>32</v>
       </c>
       <c r="K144" t="s">
         <v>464</v>
       </c>
       <c r="L144" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -8090,28 +8090,28 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E145" t="s">
-        <v>31</v>
+        <v>459</v>
       </c>
       <c r="F145" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G145" t="s">
-        <v>31</v>
-      </c>
-      <c r="H145" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="I145" t="s">
-        <v>466</v>
+        <v>18</v>
+      </c>
+      <c r="J145" t="s">
+        <v>32</v>
       </c>
       <c r="K145" t="s">
         <v>467</v>
       </c>
       <c r="L145" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -8125,28 +8125,28 @@
         <v>14</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E146" t="s">
-        <v>16</v>
+        <v>459</v>
       </c>
       <c r="F146" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>16</v>
-      </c>
-      <c r="H146" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="I146" t="s">
-        <v>469</v>
+        <v>18</v>
+      </c>
+      <c r="J146" t="s">
+        <v>14</v>
       </c>
       <c r="K146" t="s">
         <v>470</v>
       </c>
       <c r="L146" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -8160,28 +8160,28 @@
         <v>14</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E147" t="s">
-        <v>16</v>
+        <v>459</v>
       </c>
       <c r="F147" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>16</v>
-      </c>
-      <c r="H147" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="I147" t="s">
-        <v>472</v>
+        <v>18</v>
+      </c>
+      <c r="J147" t="s">
+        <v>14</v>
       </c>
       <c r="K147" t="s">
         <v>473</v>
       </c>
       <c r="L147" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -8192,31 +8192,31 @@
         <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E148" t="s">
-        <v>16</v>
+        <v>459</v>
       </c>
       <c r="F148" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>16</v>
-      </c>
-      <c r="H148" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="I148" t="s">
-        <v>475</v>
+        <v>18</v>
+      </c>
+      <c r="J148" t="s">
+        <v>14</v>
       </c>
       <c r="K148" t="s">
         <v>476</v>
       </c>
       <c r="L148" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -8230,28 +8230,28 @@
         <v>14</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E149" t="s">
-        <v>31</v>
+        <v>459</v>
       </c>
       <c r="F149" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G149" t="s">
-        <v>31</v>
-      </c>
-      <c r="H149" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="I149" t="s">
-        <v>478</v>
+        <v>18</v>
+      </c>
+      <c r="J149" t="s">
+        <v>32</v>
       </c>
       <c r="K149" t="s">
         <v>479</v>
       </c>
       <c r="L149" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -8265,28 +8265,28 @@
         <v>14</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E150" t="s">
-        <v>16</v>
+        <v>459</v>
       </c>
       <c r="F150" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>16</v>
-      </c>
-      <c r="H150" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="I150" t="s">
-        <v>481</v>
+        <v>18</v>
+      </c>
+      <c r="J150" t="s">
+        <v>14</v>
       </c>
       <c r="K150" t="s">
         <v>482</v>
       </c>
       <c r="L150" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -8300,28 +8300,28 @@
         <v>14</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E151" t="s">
-        <v>16</v>
+        <v>459</v>
       </c>
       <c r="F151" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G151" t="s">
-        <v>16</v>
-      </c>
-      <c r="H151" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="I151" t="s">
-        <v>484</v>
+        <v>18</v>
+      </c>
+      <c r="J151" t="s">
+        <v>14</v>
       </c>
       <c r="K151" t="s">
         <v>485</v>
       </c>
       <c r="L151" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -8335,28 +8335,28 @@
         <v>14</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E152" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F152" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G152" t="s">
-        <v>31</v>
-      </c>
-      <c r="H152" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I152" t="s">
-        <v>488</v>
+        <v>18</v>
+      </c>
+      <c r="J152" t="s">
+        <v>14</v>
       </c>
       <c r="K152" t="s">
         <v>489</v>
       </c>
       <c r="L152" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -8370,28 +8370,28 @@
         <v>14</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E153" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F153" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="G153" t="s">
-        <v>31</v>
-      </c>
-      <c r="H153" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I153" t="s">
-        <v>491</v>
+        <v>18</v>
+      </c>
+      <c r="J153" t="s">
+        <v>14</v>
       </c>
       <c r="K153" t="s">
         <v>492</v>
       </c>
       <c r="L153" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -8405,28 +8405,28 @@
         <v>14</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E154" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F154" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>16</v>
-      </c>
-      <c r="H154" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="I154" t="s">
-        <v>494</v>
+        <v>18</v>
+      </c>
+      <c r="J154" t="s">
+        <v>14</v>
       </c>
       <c r="K154" t="s">
         <v>495</v>
       </c>
       <c r="L154" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -8440,28 +8440,28 @@
         <v>14</v>
       </c>
       <c r="D155" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E155" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F155" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>16</v>
-      </c>
-      <c r="H155" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="I155" t="s">
-        <v>497</v>
+        <v>368</v>
+      </c>
+      <c r="J155" t="s">
+        <v>14</v>
       </c>
       <c r="K155" t="s">
         <v>498</v>
       </c>
       <c r="L155" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -8475,28 +8475,28 @@
         <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E156" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F156" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G156" t="s">
-        <v>16</v>
-      </c>
-      <c r="H156" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="I156" t="s">
-        <v>500</v>
+        <v>18</v>
+      </c>
+      <c r="J156" t="s">
+        <v>14</v>
       </c>
       <c r="K156" t="s">
         <v>501</v>
       </c>
       <c r="L156" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -8510,28 +8510,28 @@
         <v>14</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E157" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F157" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G157" t="s">
-        <v>16</v>
-      </c>
-      <c r="H157" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="I157" t="s">
-        <v>503</v>
+        <v>18</v>
+      </c>
+      <c r="J157" t="s">
+        <v>14</v>
       </c>
       <c r="K157" t="s">
         <v>504</v>
       </c>
       <c r="L157" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -8545,28 +8545,28 @@
         <v>14</v>
       </c>
       <c r="D158" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E158" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F158" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G158" t="s">
-        <v>16</v>
-      </c>
-      <c r="H158" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="I158" t="s">
-        <v>506</v>
+        <v>368</v>
+      </c>
+      <c r="J158" t="s">
+        <v>14</v>
       </c>
       <c r="K158" t="s">
         <v>507</v>
       </c>
       <c r="L158" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -8580,28 +8580,28 @@
         <v>14</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E159" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F159" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G159" t="s">
-        <v>16</v>
-      </c>
-      <c r="H159" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="I159" t="s">
-        <v>509</v>
+        <v>18</v>
+      </c>
+      <c r="J159" t="s">
+        <v>14</v>
       </c>
       <c r="K159" t="s">
         <v>510</v>
       </c>
       <c r="L159" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -8615,28 +8615,28 @@
         <v>14</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E160" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F160" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G160" t="s">
-        <v>16</v>
-      </c>
-      <c r="H160" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="I160" t="s">
-        <v>512</v>
+        <v>18</v>
+      </c>
+      <c r="J160" t="s">
+        <v>14</v>
       </c>
       <c r="K160" t="s">
         <v>513</v>
       </c>
       <c r="L160" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -8650,28 +8650,28 @@
         <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E161" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F161" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G161" t="s">
-        <v>16</v>
-      </c>
-      <c r="H161" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="I161" t="s">
-        <v>515</v>
+        <v>18</v>
+      </c>
+      <c r="J161" t="s">
+        <v>14</v>
       </c>
       <c r="K161" t="s">
         <v>516</v>
       </c>
       <c r="L161" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -8685,28 +8685,28 @@
         <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E162" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F162" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
-        <v>16</v>
-      </c>
-      <c r="H162" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="I162" t="s">
-        <v>518</v>
+        <v>18</v>
+      </c>
+      <c r="J162" t="s">
+        <v>14</v>
       </c>
       <c r="K162" t="s">
         <v>519</v>
       </c>
       <c r="L162" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -8720,28 +8720,28 @@
         <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E163" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F163" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
-        <v>16</v>
-      </c>
-      <c r="H163" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="I163" t="s">
-        <v>521</v>
+        <v>18</v>
+      </c>
+      <c r="J163" t="s">
+        <v>14</v>
       </c>
       <c r="K163" t="s">
         <v>522</v>
       </c>
       <c r="L163" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -8755,28 +8755,28 @@
         <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E164" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F164" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
-        <v>16</v>
-      </c>
-      <c r="H164" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="I164" t="s">
-        <v>524</v>
+        <v>18</v>
+      </c>
+      <c r="J164" t="s">
+        <v>14</v>
       </c>
       <c r="K164" t="s">
         <v>525</v>
       </c>
       <c r="L164" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -8790,28 +8790,28 @@
         <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E165" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F165" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s">
-        <v>16</v>
-      </c>
-      <c r="H165" t="s">
-        <v>487</v>
+        <v>527</v>
       </c>
       <c r="I165" t="s">
-        <v>527</v>
+        <v>18</v>
+      </c>
+      <c r="J165" t="s">
+        <v>14</v>
       </c>
       <c r="K165" t="s">
         <v>528</v>
       </c>
       <c r="L165" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -8825,28 +8825,28 @@
         <v>14</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E166" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F166" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s">
-        <v>16</v>
-      </c>
-      <c r="H166" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="I166" t="s">
-        <v>530</v>
+        <v>18</v>
+      </c>
+      <c r="J166" t="s">
+        <v>14</v>
       </c>
       <c r="K166" t="s">
         <v>531</v>
       </c>
       <c r="L166" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -8860,28 +8860,28 @@
         <v>14</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E167" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F167" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G167" t="s">
-        <v>16</v>
-      </c>
-      <c r="H167" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="I167" t="s">
-        <v>533</v>
+        <v>18</v>
+      </c>
+      <c r="J167" t="s">
+        <v>14</v>
       </c>
       <c r="K167" t="s">
         <v>534</v>
       </c>
       <c r="L167" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -8895,28 +8895,28 @@
         <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E168" t="s">
-        <v>16</v>
+        <v>487</v>
       </c>
       <c r="F168" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G168" t="s">
-        <v>16</v>
-      </c>
-      <c r="H168" t="s">
-        <v>487</v>
+        <v>536</v>
       </c>
       <c r="I168" t="s">
-        <v>536</v>
+        <v>18</v>
+      </c>
+      <c r="J168" t="s">
+        <v>14</v>
       </c>
       <c r="K168" t="s">
         <v>537</v>
       </c>
       <c r="L168" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -8930,28 +8930,28 @@
         <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>15</v>
+        <v>386</v>
       </c>
       <c r="E169" t="s">
-        <v>31</v>
+        <v>487</v>
       </c>
       <c r="F169" t="s">
-        <v>386</v>
+        <v>14</v>
       </c>
       <c r="G169" t="s">
-        <v>16</v>
-      </c>
-      <c r="H169" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="I169" t="s">
-        <v>539</v>
+        <v>18</v>
+      </c>
+      <c r="J169" t="s">
+        <v>32</v>
       </c>
       <c r="K169" t="s">
         <v>540</v>
       </c>
       <c r="L169" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -8965,28 +8965,28 @@
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E170" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F170" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G170" t="s">
-        <v>16</v>
-      </c>
-      <c r="H170" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I170" t="s">
-        <v>544</v>
+        <v>368</v>
+      </c>
+      <c r="J170" t="s">
+        <v>14</v>
       </c>
       <c r="K170" t="s">
         <v>545</v>
       </c>
       <c r="L170" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -9000,28 +9000,28 @@
         <v>14</v>
       </c>
       <c r="D171" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E171" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F171" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G171" t="s">
-        <v>16</v>
-      </c>
-      <c r="H171" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I171" t="s">
-        <v>547</v>
+        <v>368</v>
+      </c>
+      <c r="J171" t="s">
+        <v>14</v>
       </c>
       <c r="K171" t="s">
         <v>548</v>
       </c>
       <c r="L171" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -9035,28 +9035,28 @@
         <v>14</v>
       </c>
       <c r="D172" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E172" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F172" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s">
-        <v>16</v>
-      </c>
-      <c r="H172" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="I172" t="s">
-        <v>550</v>
+        <v>368</v>
+      </c>
+      <c r="J172" t="s">
+        <v>14</v>
       </c>
       <c r="K172" t="s">
         <v>551</v>
       </c>
       <c r="L172" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -9070,28 +9070,28 @@
         <v>14</v>
       </c>
       <c r="D173" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E173" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F173" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s">
-        <v>16</v>
-      </c>
-      <c r="H173" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="I173" t="s">
-        <v>553</v>
+        <v>368</v>
+      </c>
+      <c r="J173" t="s">
+        <v>14</v>
       </c>
       <c r="K173" t="s">
         <v>554</v>
       </c>
       <c r="L173" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -9105,28 +9105,28 @@
         <v>14</v>
       </c>
       <c r="D174" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E174" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F174" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>16</v>
-      </c>
-      <c r="H174" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="I174" t="s">
-        <v>556</v>
+        <v>368</v>
+      </c>
+      <c r="J174" t="s">
+        <v>14</v>
       </c>
       <c r="K174" t="s">
         <v>557</v>
       </c>
       <c r="L174" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -9140,28 +9140,28 @@
         <v>14</v>
       </c>
       <c r="D175" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E175" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F175" t="s">
-        <v>542</v>
+        <v>32</v>
       </c>
       <c r="G175" t="s">
-        <v>31</v>
-      </c>
-      <c r="H175" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="I175" t="s">
-        <v>559</v>
+        <v>368</v>
+      </c>
+      <c r="J175" t="s">
+        <v>14</v>
       </c>
       <c r="K175" t="s">
         <v>560</v>
       </c>
       <c r="L175" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -9175,28 +9175,28 @@
         <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E176" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F176" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s">
-        <v>16</v>
-      </c>
-      <c r="H176" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="I176" t="s">
-        <v>562</v>
+        <v>368</v>
+      </c>
+      <c r="J176" t="s">
+        <v>14</v>
       </c>
       <c r="K176" t="s">
         <v>563</v>
       </c>
       <c r="L176" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -9210,28 +9210,28 @@
         <v>14</v>
       </c>
       <c r="D177" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E177" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F177" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G177" t="s">
-        <v>16</v>
-      </c>
-      <c r="H177" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="I177" t="s">
-        <v>565</v>
+        <v>368</v>
+      </c>
+      <c r="J177" t="s">
+        <v>14</v>
       </c>
       <c r="K177" t="s">
         <v>566</v>
       </c>
       <c r="L177" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -9245,28 +9245,28 @@
         <v>14</v>
       </c>
       <c r="D178" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E178" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F178" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G178" t="s">
-        <v>16</v>
-      </c>
-      <c r="H178" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="I178" t="s">
-        <v>568</v>
+        <v>368</v>
+      </c>
+      <c r="J178" t="s">
+        <v>14</v>
       </c>
       <c r="K178" t="s">
         <v>569</v>
       </c>
       <c r="L178" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -9280,28 +9280,28 @@
         <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E179" t="s">
-        <v>16</v>
+        <v>543</v>
       </c>
       <c r="F179" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G179" t="s">
-        <v>16</v>
-      </c>
-      <c r="H179" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="I179" t="s">
-        <v>571</v>
+        <v>368</v>
+      </c>
+      <c r="J179" t="s">
+        <v>14</v>
       </c>
       <c r="K179" t="s">
         <v>572</v>
       </c>
       <c r="L179" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -9315,28 +9315,28 @@
         <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E180" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F180" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G180" t="s">
-        <v>16</v>
-      </c>
-      <c r="H180" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I180" t="s">
-        <v>575</v>
+        <v>368</v>
+      </c>
+      <c r="J180" t="s">
+        <v>14</v>
       </c>
       <c r="K180" t="s">
         <v>576</v>
       </c>
       <c r="L180" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -9350,28 +9350,28 @@
         <v>14</v>
       </c>
       <c r="D181" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E181" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F181" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G181" t="s">
-        <v>16</v>
-      </c>
-      <c r="H181" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I181" t="s">
-        <v>578</v>
+        <v>368</v>
+      </c>
+      <c r="J181" t="s">
+        <v>14</v>
       </c>
       <c r="K181" t="s">
         <v>579</v>
       </c>
       <c r="L181" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -9385,28 +9385,28 @@
         <v>14</v>
       </c>
       <c r="D182" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E182" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F182" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s">
-        <v>16</v>
-      </c>
-      <c r="H182" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="I182" t="s">
-        <v>581</v>
+        <v>368</v>
+      </c>
+      <c r="J182" t="s">
+        <v>14</v>
       </c>
       <c r="K182" t="s">
         <v>582</v>
       </c>
       <c r="L182" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -9420,25 +9420,25 @@
         <v>14</v>
       </c>
       <c r="D183" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E183" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F183" t="s">
-        <v>542</v>
-      </c>
-      <c r="G183" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H183" t="s">
-        <v>574</v>
+        <v>585</v>
+      </c>
+      <c r="I183" t="s">
+        <v>368</v>
       </c>
       <c r="J183" t="s">
-        <v>585</v>
+        <v>14</v>
       </c>
       <c r="L183" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -9452,28 +9452,28 @@
         <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E184" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F184" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s">
-        <v>16</v>
-      </c>
-      <c r="H184" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="I184" t="s">
-        <v>587</v>
+        <v>368</v>
+      </c>
+      <c r="J184" t="s">
+        <v>14</v>
       </c>
       <c r="K184" t="s">
         <v>588</v>
       </c>
       <c r="L184" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -9487,28 +9487,28 @@
         <v>14</v>
       </c>
       <c r="D185" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E185" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F185" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s">
-        <v>16</v>
-      </c>
-      <c r="H185" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="I185" t="s">
-        <v>590</v>
+        <v>368</v>
+      </c>
+      <c r="J185" t="s">
+        <v>14</v>
       </c>
       <c r="K185" t="s">
         <v>591</v>
       </c>
       <c r="L185" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -9522,28 +9522,28 @@
         <v>14</v>
       </c>
       <c r="D186" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E186" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F186" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G186" t="s">
-        <v>16</v>
-      </c>
-      <c r="H186" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="I186" t="s">
-        <v>593</v>
+        <v>368</v>
+      </c>
+      <c r="J186" t="s">
+        <v>14</v>
       </c>
       <c r="K186" t="s">
         <v>594</v>
       </c>
       <c r="L186" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -9557,28 +9557,28 @@
         <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E187" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F187" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G187" t="s">
-        <v>16</v>
-      </c>
-      <c r="H187" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="I187" t="s">
-        <v>596</v>
+        <v>368</v>
+      </c>
+      <c r="J187" t="s">
+        <v>14</v>
       </c>
       <c r="K187" t="s">
         <v>597</v>
       </c>
       <c r="L187" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -9592,28 +9592,28 @@
         <v>14</v>
       </c>
       <c r="D188" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E188" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F188" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G188" t="s">
-        <v>16</v>
-      </c>
-      <c r="H188" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="I188" t="s">
-        <v>599</v>
+        <v>368</v>
+      </c>
+      <c r="J188" t="s">
+        <v>14</v>
       </c>
       <c r="K188" t="s">
         <v>600</v>
       </c>
       <c r="L188" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -9627,28 +9627,28 @@
         <v>14</v>
       </c>
       <c r="D189" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E189" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F189" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G189" t="s">
-        <v>16</v>
-      </c>
-      <c r="H189" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="I189" t="s">
-        <v>602</v>
+        <v>368</v>
+      </c>
+      <c r="J189" t="s">
+        <v>14</v>
       </c>
       <c r="K189" t="s">
         <v>603</v>
       </c>
       <c r="L189" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -9662,28 +9662,28 @@
         <v>14</v>
       </c>
       <c r="D190" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E190" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F190" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G190" t="s">
-        <v>16</v>
-      </c>
-      <c r="H190" t="s">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="I190" t="s">
-        <v>605</v>
+        <v>368</v>
+      </c>
+      <c r="J190" t="s">
+        <v>14</v>
       </c>
       <c r="K190" t="s">
         <v>606</v>
       </c>
       <c r="L190" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -9697,28 +9697,28 @@
         <v>14</v>
       </c>
       <c r="D191" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E191" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F191" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G191" t="s">
-        <v>16</v>
-      </c>
-      <c r="H191" t="s">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="I191" t="s">
-        <v>608</v>
+        <v>368</v>
+      </c>
+      <c r="J191" t="s">
+        <v>14</v>
       </c>
       <c r="K191" t="s">
         <v>609</v>
       </c>
       <c r="L191" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -9732,28 +9732,28 @@
         <v>14</v>
       </c>
       <c r="D192" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E192" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F192" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G192" t="s">
-        <v>16</v>
-      </c>
-      <c r="H192" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="I192" t="s">
-        <v>611</v>
+        <v>368</v>
+      </c>
+      <c r="J192" t="s">
+        <v>14</v>
       </c>
       <c r="K192" t="s">
         <v>612</v>
       </c>
       <c r="L192" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -9767,28 +9767,28 @@
         <v>14</v>
       </c>
       <c r="D193" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E193" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F193" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G193" t="s">
-        <v>16</v>
-      </c>
-      <c r="H193" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="I193" t="s">
-        <v>614</v>
+        <v>368</v>
+      </c>
+      <c r="J193" t="s">
+        <v>14</v>
       </c>
       <c r="K193" t="s">
         <v>615</v>
       </c>
       <c r="L193" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -9802,28 +9802,28 @@
         <v>14</v>
       </c>
       <c r="D194" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E194" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F194" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G194" t="s">
-        <v>16</v>
-      </c>
-      <c r="H194" t="s">
-        <v>574</v>
+        <v>617</v>
       </c>
       <c r="I194" t="s">
-        <v>617</v>
+        <v>368</v>
+      </c>
+      <c r="J194" t="s">
+        <v>14</v>
       </c>
       <c r="K194" t="s">
         <v>618</v>
       </c>
       <c r="L194" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -9837,28 +9837,28 @@
         <v>14</v>
       </c>
       <c r="D195" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E195" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F195" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G195" t="s">
-        <v>16</v>
-      </c>
-      <c r="H195" t="s">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="I195" t="s">
-        <v>620</v>
+        <v>368</v>
+      </c>
+      <c r="J195" t="s">
+        <v>14</v>
       </c>
       <c r="K195" t="s">
         <v>621</v>
       </c>
       <c r="L195" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -9872,28 +9872,28 @@
         <v>14</v>
       </c>
       <c r="D196" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E196" t="s">
-        <v>16</v>
+        <v>574</v>
       </c>
       <c r="F196" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G196" t="s">
-        <v>16</v>
-      </c>
-      <c r="H196" t="s">
-        <v>574</v>
+        <v>623</v>
       </c>
       <c r="I196" t="s">
-        <v>623</v>
+        <v>368</v>
+      </c>
+      <c r="J196" t="s">
+        <v>14</v>
       </c>
       <c r="K196" t="s">
         <v>624</v>
       </c>
       <c r="L196" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -9907,28 +9907,28 @@
         <v>14</v>
       </c>
       <c r="D197" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E197" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F197" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>16</v>
-      </c>
-      <c r="H197" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I197" t="s">
-        <v>627</v>
+        <v>368</v>
+      </c>
+      <c r="J197" t="s">
+        <v>14</v>
       </c>
       <c r="K197" t="s">
         <v>628</v>
       </c>
       <c r="L197" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -9942,28 +9942,28 @@
         <v>14</v>
       </c>
       <c r="D198" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E198" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F198" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>16</v>
-      </c>
-      <c r="H198" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="I198" t="s">
-        <v>630</v>
+        <v>368</v>
+      </c>
+      <c r="J198" t="s">
+        <v>14</v>
       </c>
       <c r="K198" t="s">
         <v>631</v>
       </c>
       <c r="L198" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -9977,28 +9977,28 @@
         <v>14</v>
       </c>
       <c r="D199" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E199" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F199" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>16</v>
-      </c>
-      <c r="H199" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="I199" t="s">
-        <v>633</v>
+        <v>368</v>
+      </c>
+      <c r="J199" t="s">
+        <v>14</v>
       </c>
       <c r="K199" t="s">
         <v>634</v>
       </c>
       <c r="L199" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -10012,28 +10012,28 @@
         <v>14</v>
       </c>
       <c r="D200" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E200" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F200" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>16</v>
-      </c>
-      <c r="H200" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="I200" t="s">
-        <v>636</v>
+        <v>368</v>
+      </c>
+      <c r="J200" t="s">
+        <v>14</v>
       </c>
       <c r="K200" t="s">
         <v>637</v>
       </c>
       <c r="L200" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -10047,28 +10047,28 @@
         <v>14</v>
       </c>
       <c r="D201" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E201" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F201" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>16</v>
-      </c>
-      <c r="H201" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="I201" t="s">
-        <v>639</v>
+        <v>368</v>
+      </c>
+      <c r="J201" t="s">
+        <v>14</v>
       </c>
       <c r="K201" t="s">
         <v>640</v>
       </c>
       <c r="L201" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -10082,28 +10082,28 @@
         <v>14</v>
       </c>
       <c r="D202" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E202" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F202" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G202" t="s">
-        <v>16</v>
-      </c>
-      <c r="H202" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="I202" t="s">
-        <v>642</v>
+        <v>368</v>
+      </c>
+      <c r="J202" t="s">
+        <v>14</v>
       </c>
       <c r="K202" t="s">
         <v>643</v>
       </c>
       <c r="L202" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -10117,28 +10117,28 @@
         <v>14</v>
       </c>
       <c r="D203" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E203" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F203" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G203" t="s">
-        <v>16</v>
-      </c>
-      <c r="H203" t="s">
-        <v>626</v>
+        <v>645</v>
       </c>
       <c r="I203" t="s">
-        <v>645</v>
+        <v>368</v>
+      </c>
+      <c r="J203" t="s">
+        <v>14</v>
       </c>
       <c r="K203" t="s">
         <v>646</v>
       </c>
       <c r="L203" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -10152,28 +10152,28 @@
         <v>14</v>
       </c>
       <c r="D204" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E204" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F204" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G204" t="s">
-        <v>16</v>
-      </c>
-      <c r="H204" t="s">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="I204" t="s">
-        <v>648</v>
+        <v>368</v>
+      </c>
+      <c r="J204" t="s">
+        <v>14</v>
       </c>
       <c r="K204" t="s">
         <v>649</v>
       </c>
       <c r="L204" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -10187,28 +10187,28 @@
         <v>14</v>
       </c>
       <c r="D205" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E205" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F205" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G205" t="s">
-        <v>16</v>
-      </c>
-      <c r="H205" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="I205" t="s">
-        <v>651</v>
+        <v>368</v>
+      </c>
+      <c r="J205" t="s">
+        <v>14</v>
       </c>
       <c r="K205" t="s">
         <v>652</v>
       </c>
       <c r="L205" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -10222,28 +10222,28 @@
         <v>14</v>
       </c>
       <c r="D206" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E206" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F206" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G206" t="s">
-        <v>16</v>
-      </c>
-      <c r="H206" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="I206" t="s">
-        <v>654</v>
+        <v>368</v>
+      </c>
+      <c r="J206" t="s">
+        <v>14</v>
       </c>
       <c r="K206" t="s">
         <v>655</v>
       </c>
       <c r="L206" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -10257,28 +10257,28 @@
         <v>14</v>
       </c>
       <c r="D207" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E207" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F207" t="s">
-        <v>542</v>
+        <v>32</v>
       </c>
       <c r="G207" t="s">
-        <v>31</v>
-      </c>
-      <c r="H207" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="I207" t="s">
-        <v>657</v>
+        <v>368</v>
+      </c>
+      <c r="J207" t="s">
+        <v>14</v>
       </c>
       <c r="K207" t="s">
         <v>658</v>
       </c>
       <c r="L207" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -10292,28 +10292,28 @@
         <v>14</v>
       </c>
       <c r="D208" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E208" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F208" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G208" t="s">
-        <v>16</v>
-      </c>
-      <c r="H208" t="s">
-        <v>626</v>
+        <v>660</v>
       </c>
       <c r="I208" t="s">
-        <v>660</v>
+        <v>368</v>
+      </c>
+      <c r="J208" t="s">
+        <v>14</v>
       </c>
       <c r="K208" t="s">
         <v>661</v>
       </c>
       <c r="L208" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -10327,28 +10327,28 @@
         <v>14</v>
       </c>
       <c r="D209" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E209" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F209" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G209" t="s">
-        <v>16</v>
-      </c>
-      <c r="H209" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="I209" t="s">
-        <v>663</v>
+        <v>368</v>
+      </c>
+      <c r="J209" t="s">
+        <v>14</v>
       </c>
       <c r="K209" t="s">
         <v>664</v>
       </c>
       <c r="L209" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -10362,28 +10362,28 @@
         <v>14</v>
       </c>
       <c r="D210" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E210" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F210" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G210" t="s">
-        <v>16</v>
-      </c>
-      <c r="H210" t="s">
-        <v>626</v>
+        <v>666</v>
       </c>
       <c r="I210" t="s">
-        <v>666</v>
+        <v>368</v>
+      </c>
+      <c r="J210" t="s">
+        <v>14</v>
       </c>
       <c r="K210" t="s">
         <v>667</v>
       </c>
       <c r="L210" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -10397,28 +10397,28 @@
         <v>14</v>
       </c>
       <c r="D211" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E211" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F211" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G211" t="s">
-        <v>16</v>
-      </c>
-      <c r="H211" t="s">
-        <v>626</v>
+        <v>669</v>
       </c>
       <c r="I211" t="s">
-        <v>669</v>
+        <v>368</v>
+      </c>
+      <c r="J211" t="s">
+        <v>14</v>
       </c>
       <c r="K211" t="s">
         <v>670</v>
       </c>
       <c r="L211" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -10432,28 +10432,28 @@
         <v>14</v>
       </c>
       <c r="D212" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E212" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="F212" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G212" t="s">
-        <v>16</v>
-      </c>
-      <c r="H212" t="s">
-        <v>626</v>
+        <v>672</v>
       </c>
       <c r="I212" t="s">
-        <v>672</v>
+        <v>368</v>
+      </c>
+      <c r="J212" t="s">
+        <v>14</v>
       </c>
       <c r="K212" t="s">
         <v>673</v>
       </c>
       <c r="L212" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -10467,28 +10467,28 @@
         <v>14</v>
       </c>
       <c r="D213" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E213" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F213" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G213" t="s">
-        <v>16</v>
-      </c>
-      <c r="H213" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I213" t="s">
-        <v>676</v>
+        <v>368</v>
+      </c>
+      <c r="J213" t="s">
+        <v>14</v>
       </c>
       <c r="K213" t="s">
         <v>677</v>
       </c>
       <c r="L213" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -10502,28 +10502,28 @@
         <v>14</v>
       </c>
       <c r="D214" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E214" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F214" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G214" t="s">
-        <v>16</v>
-      </c>
-      <c r="H214" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="I214" t="s">
-        <v>679</v>
+        <v>368</v>
+      </c>
+      <c r="J214" t="s">
+        <v>14</v>
       </c>
       <c r="K214" t="s">
         <v>680</v>
       </c>
       <c r="L214" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -10537,28 +10537,28 @@
         <v>14</v>
       </c>
       <c r="D215" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E215" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F215" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G215" t="s">
-        <v>16</v>
-      </c>
-      <c r="H215" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="I215" t="s">
-        <v>682</v>
+        <v>368</v>
+      </c>
+      <c r="J215" t="s">
+        <v>14</v>
       </c>
       <c r="K215" t="s">
         <v>683</v>
       </c>
       <c r="L215" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -10572,28 +10572,28 @@
         <v>14</v>
       </c>
       <c r="D216" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E216" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F216" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G216" t="s">
-        <v>16</v>
-      </c>
-      <c r="H216" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I216" t="s">
-        <v>685</v>
+        <v>368</v>
+      </c>
+      <c r="J216" t="s">
+        <v>14</v>
       </c>
       <c r="K216" t="s">
         <v>686</v>
       </c>
       <c r="L216" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -10607,28 +10607,28 @@
         <v>14</v>
       </c>
       <c r="D217" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E217" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F217" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G217" t="s">
-        <v>16</v>
-      </c>
-      <c r="H217" t="s">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="I217" t="s">
-        <v>688</v>
+        <v>368</v>
+      </c>
+      <c r="J217" t="s">
+        <v>14</v>
       </c>
       <c r="K217" t="s">
         <v>689</v>
       </c>
       <c r="L217" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -10642,28 +10642,28 @@
         <v>14</v>
       </c>
       <c r="D218" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E218" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F218" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G218" t="s">
-        <v>16</v>
-      </c>
-      <c r="H218" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="I218" t="s">
-        <v>691</v>
+        <v>368</v>
+      </c>
+      <c r="J218" t="s">
+        <v>14</v>
       </c>
       <c r="K218" t="s">
         <v>692</v>
       </c>
       <c r="L218" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -10677,28 +10677,28 @@
         <v>14</v>
       </c>
       <c r="D219" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E219" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F219" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G219" t="s">
-        <v>16</v>
-      </c>
-      <c r="H219" t="s">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="I219" t="s">
-        <v>694</v>
+        <v>368</v>
+      </c>
+      <c r="J219" t="s">
+        <v>14</v>
       </c>
       <c r="K219" t="s">
         <v>695</v>
       </c>
       <c r="L219" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -10712,28 +10712,28 @@
         <v>14</v>
       </c>
       <c r="D220" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E220" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F220" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G220" t="s">
-        <v>16</v>
-      </c>
-      <c r="H220" t="s">
-        <v>675</v>
+        <v>697</v>
       </c>
       <c r="I220" t="s">
-        <v>697</v>
+        <v>368</v>
+      </c>
+      <c r="J220" t="s">
+        <v>14</v>
       </c>
       <c r="K220" t="s">
         <v>698</v>
       </c>
       <c r="L220" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -10747,28 +10747,28 @@
         <v>14</v>
       </c>
       <c r="D221" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="E221" t="s">
-        <v>16</v>
+        <v>675</v>
       </c>
       <c r="F221" t="s">
-        <v>542</v>
+        <v>14</v>
       </c>
       <c r="G221" t="s">
-        <v>16</v>
-      </c>
-      <c r="H221" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="I221" t="s">
-        <v>700</v>
+        <v>368</v>
+      </c>
+      <c r="J221" t="s">
+        <v>14</v>
       </c>
       <c r="K221" t="s">
         <v>701</v>
       </c>
       <c r="L221" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -10782,28 +10782,28 @@
         <v>14</v>
       </c>
       <c r="D222" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E222" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F222" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G222" t="s">
-        <v>16</v>
-      </c>
-      <c r="H222" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I222" t="s">
-        <v>705</v>
+        <v>368</v>
+      </c>
+      <c r="J222" t="s">
+        <v>14</v>
       </c>
       <c r="K222" t="s">
         <v>706</v>
       </c>
       <c r="L222" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -10817,28 +10817,28 @@
         <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E223" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F223" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G223" t="s">
-        <v>16</v>
-      </c>
-      <c r="H223" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="I223" t="s">
-        <v>708</v>
+        <v>368</v>
+      </c>
+      <c r="J223" t="s">
+        <v>14</v>
       </c>
       <c r="K223" t="s">
         <v>709</v>
       </c>
       <c r="L223" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -10852,28 +10852,28 @@
         <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E224" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F224" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G224" t="s">
-        <v>16</v>
-      </c>
-      <c r="H224" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="I224" t="s">
-        <v>711</v>
+        <v>368</v>
+      </c>
+      <c r="J224" t="s">
+        <v>14</v>
       </c>
       <c r="K224" t="s">
         <v>712</v>
       </c>
       <c r="L224" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -10887,28 +10887,28 @@
         <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E225" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F225" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G225" t="s">
-        <v>16</v>
-      </c>
-      <c r="H225" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="I225" t="s">
-        <v>714</v>
+        <v>368</v>
+      </c>
+      <c r="J225" t="s">
+        <v>14</v>
       </c>
       <c r="K225" t="s">
         <v>715</v>
       </c>
       <c r="L225" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -10922,28 +10922,28 @@
         <v>14</v>
       </c>
       <c r="D226" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E226" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F226" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G226" t="s">
-        <v>16</v>
-      </c>
-      <c r="H226" t="s">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="I226" t="s">
-        <v>717</v>
+        <v>368</v>
+      </c>
+      <c r="J226" t="s">
+        <v>14</v>
       </c>
       <c r="K226" t="s">
         <v>718</v>
       </c>
       <c r="L226" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -10957,28 +10957,28 @@
         <v>14</v>
       </c>
       <c r="D227" t="s">
-        <v>366</v>
+        <v>703</v>
       </c>
       <c r="E227" t="s">
-        <v>16</v>
+        <v>704</v>
       </c>
       <c r="F227" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G227" t="s">
-        <v>16</v>
-      </c>
-      <c r="H227" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="I227" t="s">
-        <v>720</v>
+        <v>368</v>
+      </c>
+      <c r="J227" t="s">
+        <v>14</v>
       </c>
       <c r="K227" t="s">
         <v>721</v>
       </c>
       <c r="L227" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -10989,31 +10989,31 @@
         <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E228" t="s">
-        <v>16</v>
+        <v>723</v>
       </c>
       <c r="F228" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G228" t="s">
-        <v>16</v>
-      </c>
-      <c r="H228" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I228" t="s">
-        <v>724</v>
+        <v>18</v>
+      </c>
+      <c r="J228" t="s">
+        <v>14</v>
       </c>
       <c r="K228" t="s">
         <v>725</v>
       </c>
       <c r="L228" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -11024,31 +11024,31 @@
         <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E229" t="s">
-        <v>16</v>
+        <v>723</v>
       </c>
       <c r="F229" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G229" t="s">
-        <v>16</v>
-      </c>
-      <c r="H229" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="I229" t="s">
-        <v>727</v>
+        <v>18</v>
+      </c>
+      <c r="J229" t="s">
+        <v>14</v>
       </c>
       <c r="K229" t="s">
         <v>728</v>
       </c>
       <c r="L229" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -11059,31 +11059,31 @@
         <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D230" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E230" t="s">
-        <v>16</v>
+        <v>723</v>
       </c>
       <c r="F230" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G230" t="s">
-        <v>16</v>
-      </c>
-      <c r="H230" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="I230" t="s">
-        <v>730</v>
+        <v>18</v>
+      </c>
+      <c r="J230" t="s">
+        <v>14</v>
       </c>
       <c r="K230" t="s">
         <v>731</v>
       </c>
       <c r="L230" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -11094,31 +11094,31 @@
         <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D231" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E231" t="s">
-        <v>31</v>
+        <v>723</v>
       </c>
       <c r="F231" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G231" t="s">
-        <v>16</v>
-      </c>
-      <c r="H231" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="I231" t="s">
-        <v>733</v>
+        <v>18</v>
+      </c>
+      <c r="J231" t="s">
+        <v>32</v>
       </c>
       <c r="K231" t="s">
         <v>734</v>
       </c>
       <c r="L231" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -11129,31 +11129,31 @@
         <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D232" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E232" t="s">
-        <v>31</v>
+        <v>723</v>
       </c>
       <c r="F232" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G232" t="s">
-        <v>16</v>
-      </c>
-      <c r="H232" t="s">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="I232" t="s">
-        <v>736</v>
+        <v>18</v>
+      </c>
+      <c r="J232" t="s">
+        <v>32</v>
       </c>
       <c r="K232" t="s">
         <v>737</v>
       </c>
       <c r="L232" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -11164,31 +11164,31 @@
         <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D233" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E233" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F233" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G233" t="s">
-        <v>16</v>
-      </c>
-      <c r="H233" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I233" t="s">
-        <v>740</v>
+        <v>18</v>
+      </c>
+      <c r="J233" t="s">
+        <v>14</v>
       </c>
       <c r="K233" t="s">
         <v>741</v>
       </c>
       <c r="L233" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -11199,31 +11199,31 @@
         <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D234" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E234" t="s">
-        <v>31</v>
+        <v>739</v>
       </c>
       <c r="F234" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G234" t="s">
-        <v>16</v>
-      </c>
-      <c r="H234" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="I234" t="s">
-        <v>743</v>
+        <v>18</v>
+      </c>
+      <c r="J234" t="s">
+        <v>32</v>
       </c>
       <c r="K234" t="s">
         <v>744</v>
       </c>
       <c r="L234" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -11234,31 +11234,31 @@
         <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D235" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E235" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F235" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>16</v>
-      </c>
-      <c r="H235" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="I235" t="s">
-        <v>746</v>
+        <v>18</v>
+      </c>
+      <c r="J235" t="s">
+        <v>14</v>
       </c>
       <c r="K235" t="s">
         <v>747</v>
       </c>
       <c r="L235" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -11269,31 +11269,31 @@
         <v>13</v>
       </c>
       <c r="C236" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E236" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F236" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G236" t="s">
-        <v>16</v>
-      </c>
-      <c r="H236" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="I236" t="s">
-        <v>749</v>
+        <v>18</v>
+      </c>
+      <c r="J236" t="s">
+        <v>14</v>
       </c>
       <c r="K236" t="s">
         <v>750</v>
       </c>
       <c r="L236" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -11304,31 +11304,31 @@
         <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E237" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F237" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G237" t="s">
-        <v>16</v>
-      </c>
-      <c r="H237" t="s">
-        <v>739</v>
+        <v>752</v>
       </c>
       <c r="I237" t="s">
-        <v>752</v>
+        <v>18</v>
+      </c>
+      <c r="J237" t="s">
+        <v>14</v>
       </c>
       <c r="K237" t="s">
         <v>753</v>
       </c>
       <c r="L237" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -11339,31 +11339,31 @@
         <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D238" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E238" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F238" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G238" t="s">
-        <v>16</v>
-      </c>
-      <c r="H238" t="s">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="I238" t="s">
-        <v>755</v>
+        <v>18</v>
+      </c>
+      <c r="J238" t="s">
+        <v>14</v>
       </c>
       <c r="K238" t="s">
         <v>756</v>
       </c>
       <c r="L238" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -11374,31 +11374,31 @@
         <v>13</v>
       </c>
       <c r="C239" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D239" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E239" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F239" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G239" t="s">
-        <v>16</v>
-      </c>
-      <c r="H239" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="I239" t="s">
-        <v>758</v>
+        <v>18</v>
+      </c>
+      <c r="J239" t="s">
+        <v>14</v>
       </c>
       <c r="K239" t="s">
         <v>759</v>
       </c>
       <c r="L239" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -11412,28 +11412,28 @@
         <v>14</v>
       </c>
       <c r="D240" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E240" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F240" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G240" t="s">
-        <v>16</v>
-      </c>
-      <c r="H240" t="s">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="I240" t="s">
-        <v>761</v>
+        <v>18</v>
+      </c>
+      <c r="J240" t="s">
+        <v>14</v>
       </c>
       <c r="K240" t="s">
         <v>762</v>
       </c>
       <c r="L240" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -11444,31 +11444,31 @@
         <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D241" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E241" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F241" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G241" t="s">
-        <v>16</v>
-      </c>
-      <c r="H241" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I241" t="s">
-        <v>765</v>
+        <v>18</v>
+      </c>
+      <c r="J241" t="s">
+        <v>14</v>
       </c>
       <c r="K241" t="s">
         <v>766</v>
       </c>
       <c r="L241" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -11479,31 +11479,31 @@
         <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E242" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F242" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G242" t="s">
-        <v>16</v>
-      </c>
-      <c r="H242" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="I242" t="s">
-        <v>768</v>
+        <v>18</v>
+      </c>
+      <c r="J242" t="s">
+        <v>14</v>
       </c>
       <c r="K242" t="s">
         <v>769</v>
       </c>
       <c r="L242" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -11514,31 +11514,31 @@
         <v>13</v>
       </c>
       <c r="C243" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D243" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E243" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F243" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G243" t="s">
-        <v>16</v>
-      </c>
-      <c r="H243" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="I243" t="s">
-        <v>771</v>
+        <v>18</v>
+      </c>
+      <c r="J243" t="s">
+        <v>14</v>
       </c>
       <c r="K243" t="s">
         <v>772</v>
       </c>
       <c r="L243" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -11549,31 +11549,31 @@
         <v>13</v>
       </c>
       <c r="C244" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D244" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E244" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F244" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G244" t="s">
-        <v>16</v>
-      </c>
-      <c r="H244" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="I244" t="s">
-        <v>774</v>
+        <v>18</v>
+      </c>
+      <c r="J244" t="s">
+        <v>14</v>
       </c>
       <c r="K244" t="s">
         <v>775</v>
       </c>
       <c r="L244" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -11587,28 +11587,28 @@
         <v>14</v>
       </c>
       <c r="D245" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E245" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F245" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G245" t="s">
-        <v>16</v>
-      </c>
-      <c r="H245" t="s">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="I245" t="s">
-        <v>777</v>
+        <v>18</v>
+      </c>
+      <c r="J245" t="s">
+        <v>14</v>
       </c>
       <c r="K245" t="s">
         <v>778</v>
       </c>
       <c r="L245" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -11619,31 +11619,31 @@
         <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D246" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E246" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F246" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s">
-        <v>16</v>
-      </c>
-      <c r="H246" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="I246" t="s">
-        <v>780</v>
+        <v>18</v>
+      </c>
+      <c r="J246" t="s">
+        <v>14</v>
       </c>
       <c r="K246" t="s">
         <v>781</v>
       </c>
       <c r="L246" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -11657,28 +11657,28 @@
         <v>14</v>
       </c>
       <c r="D247" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E247" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F247" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G247" t="s">
-        <v>16</v>
-      </c>
-      <c r="H247" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="I247" t="s">
-        <v>783</v>
+        <v>18</v>
+      </c>
+      <c r="J247" t="s">
+        <v>14</v>
       </c>
       <c r="K247" t="s">
         <v>784</v>
       </c>
       <c r="L247" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -11689,31 +11689,31 @@
         <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E248" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F248" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G248" t="s">
-        <v>16</v>
-      </c>
-      <c r="H248" t="s">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="I248" t="s">
-        <v>786</v>
+        <v>18</v>
+      </c>
+      <c r="J248" t="s">
+        <v>14</v>
       </c>
       <c r="K248" t="s">
         <v>787</v>
       </c>
       <c r="L248" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -11724,31 +11724,31 @@
         <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D249" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E249" t="s">
-        <v>31</v>
+        <v>764</v>
       </c>
       <c r="F249" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G249" t="s">
-        <v>16</v>
-      </c>
-      <c r="H249" t="s">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="I249" t="s">
-        <v>789</v>
+        <v>18</v>
+      </c>
+      <c r="J249" t="s">
+        <v>32</v>
       </c>
       <c r="K249" t="s">
         <v>790</v>
       </c>
       <c r="L249" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -11762,28 +11762,28 @@
         <v>14</v>
       </c>
       <c r="D250" t="s">
-        <v>15</v>
+        <v>703</v>
       </c>
       <c r="E250" t="s">
-        <v>16</v>
+        <v>764</v>
       </c>
       <c r="F250" t="s">
-        <v>703</v>
+        <v>14</v>
       </c>
       <c r="G250" t="s">
-        <v>16</v>
-      </c>
-      <c r="H250" t="s">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="I250" t="s">
-        <v>792</v>
+        <v>18</v>
+      </c>
+      <c r="J250" t="s">
+        <v>14</v>
       </c>
       <c r="K250" t="s">
         <v>793</v>
       </c>
       <c r="L250" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/pt/RegionM49.xlsx
+++ b/api/1/xlsx/pt/RegionM49.xlsx
@@ -25,30 +25,30 @@
     <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:small-island-developing-states</t>
+  </si>
+  <si>
     <t>codeforiati:developed-developing</t>
   </si>
   <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:land-locked-developing-countries</t>
+  </si>
+  <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
     <t>codeforiati:least-developed-countries</t>
   </si>
   <si>
-    <t>codeforiati:land-locked-developing-countries</t>
-  </si>
-  <si>
-    <t>codeforiati:small-island-developing-states</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
@@ -61,24 +61,24 @@
     <t>DZA</t>
   </si>
   <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Developing</t>
   </si>
   <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>015</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>SDN</t>
   </si>
   <si>
+    <t>SD</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>788</t>
   </si>
   <si>
@@ -142,12 +142,12 @@
     <t>IOT</t>
   </si>
   <si>
+    <t>IO</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
     <t>014</t>
   </si>
   <si>
@@ -634,15 +634,15 @@
     <t>AIA</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>419</t>
   </si>
   <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>029</t>
   </si>
   <si>
@@ -1117,15 +1117,15 @@
     <t>BMU</t>
   </si>
   <si>
+    <t>BM</t>
+  </si>
+  <si>
     <t>Developed</t>
   </si>
   <si>
     <t>021</t>
   </si>
   <si>
-    <t>BM</t>
-  </si>
-  <si>
     <t>124</t>
   </si>
   <si>
@@ -1177,15 +1177,15 @@
     <t>KAZ</t>
   </si>
   <si>
+    <t>KZ</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>KZ</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1228,12 +1228,12 @@
     <t>CHN</t>
   </si>
   <si>
+    <t>CN</t>
+  </si>
+  <si>
     <t>030</t>
   </si>
   <si>
-    <t>CN</t>
-  </si>
-  <si>
     <t>344</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>BRN</t>
   </si>
   <si>
+    <t>BN</t>
+  </si>
+  <si>
     <t>035</t>
   </si>
   <si>
-    <t>BN</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1396,12 +1396,12 @@
     <t>AFG</t>
   </si>
   <si>
+    <t>AF</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
     <t>050</t>
   </si>
   <si>
@@ -1480,12 +1480,12 @@
     <t>ARM</t>
   </si>
   <si>
+    <t>AM</t>
+  </si>
+  <si>
     <t>145</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
     <t>031</t>
   </si>
   <si>
@@ -1645,15 +1645,15 @@
     <t>BLR</t>
   </si>
   <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>BY</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>ALA</t>
   </si>
   <si>
+    <t>AX</t>
+  </si>
+  <si>
     <t>154</t>
   </si>
   <si>
-    <t>AX</t>
-  </si>
-  <si>
     <t>831</t>
   </si>
   <si>
@@ -1897,12 +1897,12 @@
     <t>ALB</t>
   </si>
   <si>
+    <t>AL</t>
+  </si>
+  <si>
     <t>039</t>
   </si>
   <si>
-    <t>AL</t>
-  </si>
-  <si>
     <t>020</t>
   </si>
   <si>
@@ -2044,12 +2044,12 @@
     <t>AUT</t>
   </si>
   <si>
+    <t>AT</t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
-    <t>AT</t>
-  </si>
-  <si>
     <t>056</t>
   </si>
   <si>
@@ -2128,15 +2128,15 @@
     <t>AUS</t>
   </si>
   <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
     <t>053</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
     <t>162</t>
   </si>
   <si>
@@ -2188,12 +2188,12 @@
     <t>FJI</t>
   </si>
   <si>
+    <t>FJ</t>
+  </si>
+  <si>
     <t>054</t>
   </si>
   <si>
-    <t>FJ</t>
-  </si>
-  <si>
     <t>540</t>
   </si>
   <si>
@@ -2236,12 +2236,12 @@
     <t>GUM</t>
   </si>
   <si>
+    <t>GU</t>
+  </si>
+  <si>
     <t>057</t>
   </si>
   <si>
-    <t>GU</t>
-  </si>
-  <si>
     <t>296</t>
   </si>
   <si>
@@ -2311,10 +2311,10 @@
     <t>ASM</t>
   </si>
   <si>
+    <t>AS</t>
+  </si>
+  <si>
     <t>061</t>
-  </si>
-  <si>
-    <t>AS</t>
   </si>
   <si>
     <t>184</t>
@@ -2788,19 +2788,19 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2817,25 +2817,25 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2852,25 +2852,25 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2887,25 +2887,25 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2922,22 +2922,22 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>33</v>
@@ -2957,25 +2957,25 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2992,25 +2992,25 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3033,19 +3033,19 @@
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
         <v>44</v>
@@ -3065,25 +3065,25 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
         <v>44</v>
@@ -3103,25 +3103,25 @@
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
         <v>44</v>
@@ -3141,25 +3141,25 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="L12" t="s">
         <v>44</v>
@@ -3179,25 +3179,25 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
         <v>44</v>
@@ -3217,25 +3217,25 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
         <v>44</v>
@@ -3255,25 +3255,25 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
         <v>44</v>
@@ -3293,25 +3293,25 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
         <v>44</v>
@@ -3331,25 +3331,25 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
         <v>44</v>
@@ -3369,25 +3369,25 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K18" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
         <v>44</v>
@@ -3407,25 +3407,25 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
         <v>44</v>
@@ -3445,25 +3445,25 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K20" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="L20" t="s">
         <v>44</v>
@@ -3483,25 +3483,25 @@
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
         <v>44</v>
@@ -3521,25 +3521,25 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="L22" t="s">
         <v>44</v>
@@ -3559,25 +3559,25 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K23" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L23" t="s">
         <v>44</v>
@@ -3597,25 +3597,25 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K24" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="L24" t="s">
         <v>44</v>
@@ -3635,25 +3635,25 @@
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K25" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="L25" t="s">
         <v>44</v>
@@ -3673,25 +3673,25 @@
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K26" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
         <v>44</v>
@@ -3711,25 +3711,25 @@
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K27" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="L27" t="s">
         <v>44</v>
@@ -3749,25 +3749,25 @@
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="L28" t="s">
         <v>44</v>
@@ -3787,25 +3787,25 @@
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="L29" t="s">
         <v>44</v>
@@ -3825,25 +3825,25 @@
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="L30" t="s">
         <v>44</v>
@@ -3863,25 +3863,25 @@
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K31" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
         <v>111</v>
@@ -3901,25 +3901,25 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K32" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="L32" t="s">
         <v>111</v>
@@ -3939,25 +3939,25 @@
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K33" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="L33" t="s">
         <v>111</v>
@@ -3977,25 +3977,25 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K34" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="L34" t="s">
         <v>111</v>
@@ -4015,25 +4015,25 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K35" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
         <v>111</v>
@@ -4053,25 +4053,25 @@
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="L36" t="s">
         <v>111</v>
@@ -4091,25 +4091,25 @@
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="L37" t="s">
         <v>111</v>
@@ -4129,25 +4129,25 @@
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="L38" t="s">
         <v>111</v>
@@ -4167,25 +4167,25 @@
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="L39" t="s">
         <v>111</v>
@@ -4205,25 +4205,25 @@
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K40" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="L40" t="s">
         <v>139</v>
@@ -4243,25 +4243,25 @@
         <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K41" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
         <v>139</v>
@@ -4281,25 +4281,25 @@
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="L42" t="s">
         <v>139</v>
@@ -4319,25 +4319,25 @@
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K43" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
         <v>139</v>
@@ -4357,25 +4357,25 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K44" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="L44" t="s">
         <v>139</v>
@@ -4395,25 +4395,25 @@
         <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L45" t="s">
         <v>155</v>
@@ -4433,25 +4433,25 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="L46" t="s">
         <v>155</v>
@@ -4471,25 +4471,25 @@
         <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="L47" t="s">
         <v>155</v>
@@ -4509,25 +4509,25 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K48" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
       <c r="L48" t="s">
         <v>155</v>
@@ -4547,25 +4547,25 @@
         <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K49" t="s">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="L49" t="s">
         <v>155</v>
@@ -4585,25 +4585,25 @@
         <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K50" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="L50" t="s">
         <v>155</v>
@@ -4623,25 +4623,25 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J51" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="L51" t="s">
         <v>155</v>
@@ -4661,25 +4661,25 @@
         <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H52" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J52" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K52" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="L52" t="s">
         <v>155</v>
@@ -4699,25 +4699,25 @@
         <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J53" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K53" t="s">
-        <v>179</v>
+        <v>33</v>
       </c>
       <c r="L53" t="s">
         <v>155</v>
@@ -4737,25 +4737,25 @@
         <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J54" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K54" t="s">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="L54" t="s">
         <v>155</v>
@@ -4775,25 +4775,25 @@
         <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J55" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K55" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="L55" t="s">
         <v>155</v>
@@ -4813,25 +4813,25 @@
         <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J56" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K56" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="L56" t="s">
         <v>155</v>
@@ -4851,25 +4851,25 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="F57" t="s">
         <v>17</v>
       </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J57" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K57" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="L57" t="s">
         <v>155</v>
@@ -4889,25 +4889,25 @@
         <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
         <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J58" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K58" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
         <v>155</v>
@@ -4927,25 +4927,25 @@
         <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K59" t="s">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="L59" t="s">
         <v>155</v>
@@ -4965,25 +4965,25 @@
         <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J60" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K60" t="s">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="L60" t="s">
         <v>155</v>
@@ -5003,25 +5003,25 @@
         <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J61" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K61" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="L61" t="s">
         <v>155</v>
@@ -5044,22 +5044,22 @@
         <v>206</v>
       </c>
       <c r="F62" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I62" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J62" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K62" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L62" t="s">
         <v>209</v>
@@ -5079,25 +5079,25 @@
         <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F63" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I63" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J63" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K63" t="s">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="L63" t="s">
         <v>209</v>
@@ -5117,25 +5117,25 @@
         <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="F64" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I64" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K64" t="s">
-        <v>215</v>
+        <v>17</v>
       </c>
       <c r="L64" t="s">
         <v>209</v>
@@ -5155,25 +5155,25 @@
         <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F65" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I65" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K65" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="L65" t="s">
         <v>209</v>
@@ -5193,25 +5193,25 @@
         <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F66" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I66" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J66" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K66" t="s">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="L66" t="s">
         <v>209</v>
@@ -5231,25 +5231,25 @@
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F67" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I67" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J67" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K67" t="s">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="L67" t="s">
         <v>209</v>
@@ -5269,25 +5269,25 @@
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="F68" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I68" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J68" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K68" t="s">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="L68" t="s">
         <v>209</v>
@@ -5307,25 +5307,25 @@
         <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I69" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J69" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K69" t="s">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c r="L69" t="s">
         <v>209</v>
@@ -5345,25 +5345,25 @@
         <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="F70" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I70" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J70" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K70" t="s">
-        <v>233</v>
+        <v>17</v>
       </c>
       <c r="L70" t="s">
         <v>209</v>
@@ -5383,25 +5383,25 @@
         <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="F71" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H71" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I71" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J71" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K71" t="s">
-        <v>236</v>
+        <v>17</v>
       </c>
       <c r="L71" t="s">
         <v>209</v>
@@ -5421,25 +5421,25 @@
         <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="F72" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I72" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J72" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K72" t="s">
-        <v>239</v>
+        <v>17</v>
       </c>
       <c r="L72" t="s">
         <v>209</v>
@@ -5459,25 +5459,25 @@
         <v>15</v>
       </c>
       <c r="E73" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="F73" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H73" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I73" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J73" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K73" t="s">
-        <v>242</v>
+        <v>17</v>
       </c>
       <c r="L73" t="s">
         <v>209</v>
@@ -5497,25 +5497,25 @@
         <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="F74" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H74" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I74" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J74" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K74" t="s">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="L74" t="s">
         <v>209</v>
@@ -5535,25 +5535,25 @@
         <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="F75" t="s">
         <v>17</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I75" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J75" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K75" t="s">
-        <v>248</v>
+        <v>17</v>
       </c>
       <c r="L75" t="s">
         <v>209</v>
@@ -5573,25 +5573,25 @@
         <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H76" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I76" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J76" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K76" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="L76" t="s">
         <v>209</v>
@@ -5611,25 +5611,25 @@
         <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H77" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I77" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J77" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K77" t="s">
-        <v>254</v>
+        <v>17</v>
       </c>
       <c r="L77" t="s">
         <v>209</v>
@@ -5649,25 +5649,25 @@
         <v>15</v>
       </c>
       <c r="E78" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="F78" t="s">
         <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I78" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K78" t="s">
-        <v>257</v>
+        <v>17</v>
       </c>
       <c r="L78" t="s">
         <v>209</v>
@@ -5687,25 +5687,25 @@
         <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="F79" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H79" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I79" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K79" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="L79" t="s">
         <v>209</v>
@@ -5725,25 +5725,25 @@
         <v>15</v>
       </c>
       <c r="E80" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="F80" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H80" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I80" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J80" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K80" t="s">
-        <v>263</v>
+        <v>17</v>
       </c>
       <c r="L80" t="s">
         <v>209</v>
@@ -5763,25 +5763,25 @@
         <v>15</v>
       </c>
       <c r="E81" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H81" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I81" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J81" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K81" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c r="L81" t="s">
         <v>209</v>
@@ -5801,25 +5801,25 @@
         <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>206</v>
+        <v>269</v>
       </c>
       <c r="F82" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H82" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I82" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K82" t="s">
-        <v>269</v>
+        <v>17</v>
       </c>
       <c r="L82" t="s">
         <v>209</v>
@@ -5839,25 +5839,25 @@
         <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="F83" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I83" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K83" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="L83" t="s">
         <v>209</v>
@@ -5877,25 +5877,25 @@
         <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H84" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I84" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J84" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K84" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="L84" t="s">
         <v>209</v>
@@ -5915,25 +5915,25 @@
         <v>15</v>
       </c>
       <c r="E85" t="s">
-        <v>206</v>
+        <v>278</v>
       </c>
       <c r="F85" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H85" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I85" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J85" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K85" t="s">
-        <v>278</v>
+        <v>17</v>
       </c>
       <c r="L85" t="s">
         <v>209</v>
@@ -5953,25 +5953,25 @@
         <v>15</v>
       </c>
       <c r="E86" t="s">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="F86" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I86" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J86" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K86" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="L86" t="s">
         <v>209</v>
@@ -5991,25 +5991,25 @@
         <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="F87" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H87" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I87" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J87" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K87" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="L87" t="s">
         <v>209</v>
@@ -6029,25 +6029,25 @@
         <v>15</v>
       </c>
       <c r="E88" t="s">
-        <v>206</v>
+        <v>287</v>
       </c>
       <c r="F88" t="s">
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H88" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I88" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J88" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K88" t="s">
-        <v>287</v>
+        <v>17</v>
       </c>
       <c r="L88" t="s">
         <v>209</v>
@@ -6067,25 +6067,25 @@
         <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="F89" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H89" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I89" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J89" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K89" t="s">
-        <v>290</v>
+        <v>17</v>
       </c>
       <c r="L89" t="s">
         <v>209</v>
@@ -6105,25 +6105,25 @@
         <v>15</v>
       </c>
       <c r="E90" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="F90" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H90" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I90" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J90" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K90" t="s">
-        <v>293</v>
+        <v>17</v>
       </c>
       <c r="L90" t="s">
         <v>294</v>
@@ -6143,25 +6143,25 @@
         <v>15</v>
       </c>
       <c r="E91" t="s">
-        <v>206</v>
+        <v>297</v>
       </c>
       <c r="F91" t="s">
         <v>17</v>
       </c>
       <c r="G91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I91" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J91" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K91" t="s">
-        <v>297</v>
+        <v>17</v>
       </c>
       <c r="L91" t="s">
         <v>294</v>
@@ -6181,25 +6181,25 @@
         <v>15</v>
       </c>
       <c r="E92" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="F92" t="s">
         <v>17</v>
       </c>
       <c r="G92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I92" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J92" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K92" t="s">
-        <v>300</v>
+        <v>17</v>
       </c>
       <c r="L92" t="s">
         <v>294</v>
@@ -6219,25 +6219,25 @@
         <v>15</v>
       </c>
       <c r="E93" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="F93" t="s">
         <v>17</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I93" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J93" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K93" t="s">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c r="L93" t="s">
         <v>294</v>
@@ -6257,25 +6257,25 @@
         <v>15</v>
       </c>
       <c r="E94" t="s">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="F94" t="s">
         <v>17</v>
       </c>
       <c r="G94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I94" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J94" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K94" t="s">
-        <v>306</v>
+        <v>17</v>
       </c>
       <c r="L94" t="s">
         <v>294</v>
@@ -6295,25 +6295,25 @@
         <v>15</v>
       </c>
       <c r="E95" t="s">
-        <v>206</v>
+        <v>309</v>
       </c>
       <c r="F95" t="s">
         <v>17</v>
       </c>
       <c r="G95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H95" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I95" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J95" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K95" t="s">
-        <v>309</v>
+        <v>17</v>
       </c>
       <c r="L95" t="s">
         <v>294</v>
@@ -6333,25 +6333,25 @@
         <v>15</v>
       </c>
       <c r="E96" t="s">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="F96" t="s">
         <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H96" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I96" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J96" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K96" t="s">
-        <v>312</v>
+        <v>17</v>
       </c>
       <c r="L96" t="s">
         <v>294</v>
@@ -6371,25 +6371,25 @@
         <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="F97" t="s">
         <v>17</v>
       </c>
       <c r="G97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I97" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J97" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K97" t="s">
-        <v>315</v>
+        <v>17</v>
       </c>
       <c r="L97" t="s">
         <v>294</v>
@@ -6409,25 +6409,25 @@
         <v>15</v>
       </c>
       <c r="E98" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="F98" t="s">
         <v>17</v>
       </c>
       <c r="G98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I98" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J98" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K98" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="L98" t="s">
         <v>319</v>
@@ -6447,25 +6447,25 @@
         <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="F99" t="s">
         <v>17</v>
       </c>
       <c r="G99" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H99" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I99" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="J99" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K99" t="s">
-        <v>322</v>
+        <v>17</v>
       </c>
       <c r="L99" t="s">
         <v>319</v>
@@ -6485,25 +6485,25 @@
         <v>15</v>
       </c>
       <c r="E100" t="s">
-        <v>206</v>
+        <v>325</v>
       </c>
       <c r="F100" t="s">
         <v>17</v>
       </c>
       <c r="G100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H100" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I100" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J100" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K100" t="s">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="L100" t="s">
         <v>319</v>
@@ -6523,25 +6523,25 @@
         <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>206</v>
+        <v>328</v>
       </c>
       <c r="F101" t="s">
         <v>17</v>
       </c>
       <c r="G101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H101" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I101" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J101" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K101" t="s">
-        <v>328</v>
+        <v>17</v>
       </c>
       <c r="L101" t="s">
         <v>319</v>
@@ -6561,25 +6561,25 @@
         <v>15</v>
       </c>
       <c r="E102" t="s">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="F102" t="s">
         <v>17</v>
       </c>
       <c r="G102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H102" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I102" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J102" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K102" t="s">
-        <v>331</v>
+        <v>17</v>
       </c>
       <c r="L102" t="s">
         <v>319</v>
@@ -6599,25 +6599,25 @@
         <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>206</v>
+        <v>334</v>
       </c>
       <c r="F103" t="s">
         <v>17</v>
       </c>
       <c r="G103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H103" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I103" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J103" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K103" t="s">
-        <v>334</v>
+        <v>17</v>
       </c>
       <c r="L103" t="s">
         <v>319</v>
@@ -6637,25 +6637,25 @@
         <v>15</v>
       </c>
       <c r="E104" t="s">
-        <v>206</v>
+        <v>337</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
       </c>
       <c r="G104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H104" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I104" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J104" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K104" t="s">
-        <v>337</v>
+        <v>17</v>
       </c>
       <c r="L104" t="s">
         <v>319</v>
@@ -6675,25 +6675,25 @@
         <v>15</v>
       </c>
       <c r="E105" t="s">
-        <v>206</v>
+        <v>340</v>
       </c>
       <c r="F105" t="s">
         <v>17</v>
       </c>
       <c r="G105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H105" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I105" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J105" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K105" t="s">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="L105" t="s">
         <v>319</v>
@@ -6713,25 +6713,25 @@
         <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>206</v>
+        <v>343</v>
       </c>
       <c r="F106" t="s">
         <v>17</v>
       </c>
       <c r="G106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H106" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I106" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J106" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K106" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="L106" t="s">
         <v>319</v>
@@ -6751,25 +6751,25 @@
         <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>206</v>
+        <v>346</v>
       </c>
       <c r="F107" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H107" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I107" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J107" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K107" t="s">
-        <v>346</v>
+        <v>17</v>
       </c>
       <c r="L107" t="s">
         <v>319</v>
@@ -6789,25 +6789,25 @@
         <v>15</v>
       </c>
       <c r="E108" t="s">
-        <v>206</v>
+        <v>349</v>
       </c>
       <c r="F108" t="s">
         <v>17</v>
       </c>
       <c r="G108" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H108" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I108" t="s">
-        <v>207</v>
+        <v>33</v>
       </c>
       <c r="J108" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K108" t="s">
-        <v>349</v>
+        <v>17</v>
       </c>
       <c r="L108" t="s">
         <v>319</v>
@@ -6827,25 +6827,25 @@
         <v>15</v>
       </c>
       <c r="E109" t="s">
-        <v>206</v>
+        <v>352</v>
       </c>
       <c r="F109" t="s">
         <v>17</v>
       </c>
       <c r="G109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H109" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I109" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J109" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K109" t="s">
-        <v>352</v>
+        <v>17</v>
       </c>
       <c r="L109" t="s">
         <v>319</v>
@@ -6865,25 +6865,25 @@
         <v>15</v>
       </c>
       <c r="E110" t="s">
-        <v>206</v>
+        <v>355</v>
       </c>
       <c r="F110" t="s">
         <v>17</v>
       </c>
       <c r="G110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H110" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I110" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J110" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K110" t="s">
-        <v>355</v>
+        <v>17</v>
       </c>
       <c r="L110" t="s">
         <v>319</v>
@@ -6903,25 +6903,25 @@
         <v>15</v>
       </c>
       <c r="E111" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="F111" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H111" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I111" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J111" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K111" t="s">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="L111" t="s">
         <v>319</v>
@@ -6941,25 +6941,25 @@
         <v>15</v>
       </c>
       <c r="E112" t="s">
-        <v>206</v>
+        <v>361</v>
       </c>
       <c r="F112" t="s">
         <v>17</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H112" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I112" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J112" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K112" t="s">
-        <v>361</v>
+        <v>17</v>
       </c>
       <c r="L112" t="s">
         <v>319</v>
@@ -6979,25 +6979,25 @@
         <v>15</v>
       </c>
       <c r="E113" t="s">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="F113" t="s">
         <v>17</v>
       </c>
       <c r="G113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H113" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I113" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J113" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="K113" t="s">
-        <v>364</v>
+        <v>17</v>
       </c>
       <c r="L113" t="s">
         <v>319</v>
@@ -7014,28 +7014,28 @@
         <v>366</v>
       </c>
       <c r="D114" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" t="s">
         <v>367</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" t="s">
         <v>368</v>
       </c>
-      <c r="F114" t="s">
-        <v>17</v>
-      </c>
-      <c r="G114" t="s">
-        <v>17</v>
-      </c>
       <c r="H114" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I114" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J114" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="K114" t="s">
-        <v>369</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -7049,28 +7049,28 @@
         <v>371</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E115" t="s">
+        <v>372</v>
+      </c>
+      <c r="F115" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" t="s">
         <v>368</v>
       </c>
-      <c r="F115" t="s">
-        <v>17</v>
-      </c>
-      <c r="G115" t="s">
-        <v>17</v>
-      </c>
       <c r="H115" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I115" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J115" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="K115" t="s">
-        <v>372</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -7084,28 +7084,28 @@
         <v>374</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E116" t="s">
+        <v>375</v>
+      </c>
+      <c r="F116" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" t="s">
         <v>368</v>
       </c>
-      <c r="F116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G116" t="s">
-        <v>17</v>
-      </c>
       <c r="H116" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I116" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J116" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="K116" t="s">
-        <v>375</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -7119,28 +7119,28 @@
         <v>377</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
+        <v>378</v>
+      </c>
+      <c r="F117" t="s">
+        <v>17</v>
+      </c>
+      <c r="G117" t="s">
         <v>368</v>
       </c>
-      <c r="F117" t="s">
-        <v>17</v>
-      </c>
-      <c r="G117" t="s">
-        <v>17</v>
-      </c>
       <c r="H117" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I117" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J117" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="K117" t="s">
-        <v>378</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -7154,28 +7154,28 @@
         <v>380</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
+        <v>381</v>
+      </c>
+      <c r="F118" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s">
         <v>368</v>
       </c>
-      <c r="F118" t="s">
-        <v>17</v>
-      </c>
-      <c r="G118" t="s">
-        <v>17</v>
-      </c>
       <c r="H118" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I118" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="J118" t="s">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="K118" t="s">
-        <v>381</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -7188,20 +7188,20 @@
       <c r="C119" t="s">
         <v>383</v>
       </c>
+      <c r="D119" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" t="s">
+        <v>384</v>
+      </c>
       <c r="F119" t="s">
         <v>17</v>
       </c>
-      <c r="G119" t="s">
-        <v>17</v>
-      </c>
-      <c r="H119" t="s">
-        <v>17</v>
-      </c>
-      <c r="J119" t="s">
-        <v>19</v>
+      <c r="I119" t="s">
+        <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7224,19 +7224,19 @@
         <v>17</v>
       </c>
       <c r="G120" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H120" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I120" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J120" t="s">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="K120" t="s">
-        <v>389</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -7253,25 +7253,25 @@
         <v>15</v>
       </c>
       <c r="E121" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F121" t="s">
         <v>17</v>
       </c>
       <c r="G121" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H121" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I121" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J121" t="s">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="K121" t="s">
-        <v>392</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -7288,25 +7288,25 @@
         <v>15</v>
       </c>
       <c r="E122" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F122" t="s">
         <v>17</v>
       </c>
       <c r="G122" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H122" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I122" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J122" t="s">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="K122" t="s">
-        <v>395</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -7323,25 +7323,25 @@
         <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F123" t="s">
         <v>17</v>
       </c>
       <c r="G123" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H123" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I123" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J123" t="s">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="K123" t="s">
-        <v>398</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -7358,25 +7358,25 @@
         <v>15</v>
       </c>
       <c r="E124" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="F124" t="s">
         <v>17</v>
       </c>
       <c r="G124" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H124" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I124" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J124" t="s">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="K124" t="s">
-        <v>401</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -7399,19 +7399,19 @@
         <v>17</v>
       </c>
       <c r="G125" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H125" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I125" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J125" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K125" t="s">
-        <v>405</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -7428,25 +7428,25 @@
         <v>15</v>
       </c>
       <c r="E126" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F126" t="s">
         <v>17</v>
       </c>
       <c r="G126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H126" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I126" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J126" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K126" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -7463,25 +7463,25 @@
         <v>15</v>
       </c>
       <c r="E127" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F127" t="s">
         <v>17</v>
       </c>
       <c r="G127" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H127" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I127" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J127" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K127" t="s">
-        <v>411</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -7498,25 +7498,25 @@
         <v>15</v>
       </c>
       <c r="E128" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F128" t="s">
         <v>17</v>
       </c>
       <c r="G128" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H128" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I128" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J128" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K128" t="s">
-        <v>414</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7530,28 +7530,28 @@
         <v>416</v>
       </c>
       <c r="D129" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E129" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="F129" t="s">
         <v>17</v>
       </c>
       <c r="G129" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H129" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I129" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J129" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K129" t="s">
-        <v>417</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7568,25 +7568,25 @@
         <v>15</v>
       </c>
       <c r="E130" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="F130" t="s">
         <v>17</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H130" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I130" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J130" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K130" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7603,25 +7603,25 @@
         <v>15</v>
       </c>
       <c r="E131" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="F131" t="s">
         <v>17</v>
       </c>
       <c r="G131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H131" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I131" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J131" t="s">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="K131" t="s">
-        <v>423</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7644,19 +7644,19 @@
         <v>17</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H132" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I132" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J132" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K132" t="s">
-        <v>427</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7673,25 +7673,25 @@
         <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F133" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H133" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I133" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J133" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K133" t="s">
-        <v>430</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -7708,25 +7708,25 @@
         <v>15</v>
       </c>
       <c r="E134" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F134" t="s">
         <v>17</v>
       </c>
       <c r="G134" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H134" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I134" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J134" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K134" t="s">
-        <v>433</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -7743,25 +7743,25 @@
         <v>15</v>
       </c>
       <c r="E135" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F135" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G135" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H135" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I135" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J135" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K135" t="s">
-        <v>436</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -7778,25 +7778,25 @@
         <v>15</v>
       </c>
       <c r="E136" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F136" t="s">
         <v>17</v>
       </c>
       <c r="G136" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H136" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I136" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J136" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K136" t="s">
-        <v>439</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -7813,25 +7813,25 @@
         <v>15</v>
       </c>
       <c r="E137" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="F137" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H137" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I137" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J137" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K137" t="s">
-        <v>442</v>
+        <v>33</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -7848,25 +7848,25 @@
         <v>15</v>
       </c>
       <c r="E138" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="F138" t="s">
         <v>17</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H138" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I138" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J138" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K138" t="s">
-        <v>445</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -7883,25 +7883,25 @@
         <v>15</v>
       </c>
       <c r="E139" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="F139" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G139" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H139" t="s">
-        <v>32</v>
+        <v>388</v>
       </c>
       <c r="I139" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J139" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K139" t="s">
-        <v>448</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -7918,25 +7918,25 @@
         <v>15</v>
       </c>
       <c r="E140" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="F140" t="s">
         <v>17</v>
       </c>
       <c r="G140" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H140" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I140" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J140" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K140" t="s">
-        <v>451</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -7953,25 +7953,25 @@
         <v>15</v>
       </c>
       <c r="E141" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="F141" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H141" t="s">
-        <v>32</v>
+        <v>388</v>
       </c>
       <c r="I141" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J141" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K141" t="s">
-        <v>454</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -7988,25 +7988,25 @@
         <v>15</v>
       </c>
       <c r="E142" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="F142" t="s">
         <v>17</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H142" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I142" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J142" t="s">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="K142" t="s">
-        <v>457</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -8026,22 +8026,22 @@
         <v>460</v>
       </c>
       <c r="F143" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G143" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H143" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I143" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J143" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K143" t="s">
-        <v>461</v>
+        <v>33</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8058,25 +8058,25 @@
         <v>15</v>
       </c>
       <c r="E144" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F144" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H144" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I144" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J144" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K144" t="s">
-        <v>464</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8093,25 +8093,25 @@
         <v>15</v>
       </c>
       <c r="E145" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F145" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G145" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H145" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I145" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J145" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K145" t="s">
-        <v>467</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8128,25 +8128,25 @@
         <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="F146" t="s">
         <v>17</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H146" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I146" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J146" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K146" t="s">
-        <v>470</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -8163,25 +8163,25 @@
         <v>15</v>
       </c>
       <c r="E147" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="F147" t="s">
         <v>17</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H147" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I147" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J147" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K147" t="s">
-        <v>473</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8198,25 +8198,25 @@
         <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="F148" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G148" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H148" t="s">
-        <v>32</v>
+        <v>388</v>
       </c>
       <c r="I148" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J148" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K148" t="s">
-        <v>476</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8233,25 +8233,25 @@
         <v>15</v>
       </c>
       <c r="E149" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="F149" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G149" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H149" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I149" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J149" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K149" t="s">
-        <v>479</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8268,25 +8268,25 @@
         <v>15</v>
       </c>
       <c r="E150" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="F150" t="s">
         <v>17</v>
       </c>
       <c r="G150" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H150" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I150" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J150" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K150" t="s">
-        <v>482</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8303,25 +8303,25 @@
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="F151" t="s">
         <v>17</v>
       </c>
       <c r="G151" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H151" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I151" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J151" t="s">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="K151" t="s">
-        <v>485</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8344,19 +8344,19 @@
         <v>17</v>
       </c>
       <c r="G152" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H152" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I152" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J152" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K152" t="s">
-        <v>489</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8373,25 +8373,25 @@
         <v>15</v>
       </c>
       <c r="E153" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F153" t="s">
         <v>17</v>
       </c>
       <c r="G153" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H153" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I153" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
       <c r="J153" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K153" t="s">
-        <v>492</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8408,25 +8408,25 @@
         <v>15</v>
       </c>
       <c r="E154" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F154" t="s">
         <v>17</v>
       </c>
       <c r="G154" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H154" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I154" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J154" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K154" t="s">
-        <v>495</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8440,28 +8440,28 @@
         <v>497</v>
       </c>
       <c r="D155" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E155" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="F155" t="s">
         <v>17</v>
       </c>
       <c r="G155" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H155" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I155" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J155" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K155" t="s">
-        <v>498</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8478,25 +8478,25 @@
         <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="F156" t="s">
         <v>17</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H156" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I156" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J156" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K156" t="s">
-        <v>501</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8513,25 +8513,25 @@
         <v>15</v>
       </c>
       <c r="E157" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="F157" t="s">
         <v>17</v>
       </c>
       <c r="G157" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H157" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I157" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J157" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K157" t="s">
-        <v>504</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8545,28 +8545,28 @@
         <v>506</v>
       </c>
       <c r="D158" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="F158" t="s">
         <v>17</v>
       </c>
       <c r="G158" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H158" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I158" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J158" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K158" t="s">
-        <v>507</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8583,25 +8583,25 @@
         <v>15</v>
       </c>
       <c r="E159" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="F159" t="s">
         <v>17</v>
       </c>
       <c r="G159" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H159" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I159" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J159" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K159" t="s">
-        <v>510</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8618,25 +8618,25 @@
         <v>15</v>
       </c>
       <c r="E160" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="F160" t="s">
         <v>17</v>
       </c>
       <c r="G160" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H160" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I160" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J160" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K160" t="s">
-        <v>513</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8653,25 +8653,25 @@
         <v>15</v>
       </c>
       <c r="E161" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
       <c r="F161" t="s">
         <v>17</v>
       </c>
       <c r="G161" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H161" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I161" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J161" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K161" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8688,25 +8688,25 @@
         <v>15</v>
       </c>
       <c r="E162" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="F162" t="s">
         <v>17</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H162" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I162" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J162" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K162" t="s">
-        <v>519</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8723,25 +8723,25 @@
         <v>15</v>
       </c>
       <c r="E163" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="F163" t="s">
         <v>17</v>
       </c>
       <c r="G163" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H163" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I163" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J163" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K163" t="s">
-        <v>522</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -8758,25 +8758,25 @@
         <v>15</v>
       </c>
       <c r="E164" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="F164" t="s">
         <v>17</v>
       </c>
       <c r="G164" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H164" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I164" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J164" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K164" t="s">
-        <v>525</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -8793,25 +8793,25 @@
         <v>15</v>
       </c>
       <c r="E165" t="s">
-        <v>488</v>
+        <v>528</v>
       </c>
       <c r="F165" t="s">
         <v>17</v>
       </c>
       <c r="G165" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H165" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I165" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J165" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K165" t="s">
-        <v>528</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -8828,25 +8828,25 @@
         <v>15</v>
       </c>
       <c r="E166" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="F166" t="s">
         <v>17</v>
       </c>
       <c r="G166" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H166" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I166" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J166" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K166" t="s">
-        <v>531</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -8863,25 +8863,25 @@
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>488</v>
+        <v>534</v>
       </c>
       <c r="F167" t="s">
         <v>17</v>
       </c>
       <c r="G167" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H167" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I167" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J167" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K167" t="s">
-        <v>534</v>
+        <v>17</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -8898,25 +8898,25 @@
         <v>15</v>
       </c>
       <c r="E168" t="s">
-        <v>488</v>
+        <v>537</v>
       </c>
       <c r="F168" t="s">
         <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H168" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I168" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J168" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K168" t="s">
-        <v>537</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -8933,25 +8933,25 @@
         <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="F169" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G169" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H169" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="I169" t="s">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="J169" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="K169" t="s">
-        <v>540</v>
+        <v>33</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -8965,7 +8965,7 @@
         <v>542</v>
       </c>
       <c r="D170" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
         <v>543</v>
@@ -8974,19 +8974,19 @@
         <v>17</v>
       </c>
       <c r="G170" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H170" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I170" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J170" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K170" t="s">
-        <v>545</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9000,28 +9000,28 @@
         <v>547</v>
       </c>
       <c r="D171" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E171" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F171" t="s">
         <v>17</v>
       </c>
       <c r="G171" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H171" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I171" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J171" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K171" t="s">
-        <v>548</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9035,28 +9035,28 @@
         <v>550</v>
       </c>
       <c r="D172" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
       </c>
       <c r="G172" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H172" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I172" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J172" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K172" t="s">
-        <v>551</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9070,28 +9070,28 @@
         <v>553</v>
       </c>
       <c r="D173" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
       </c>
       <c r="G173" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H173" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I173" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J173" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K173" t="s">
-        <v>554</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9105,28 +9105,28 @@
         <v>556</v>
       </c>
       <c r="D174" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E174" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H174" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I174" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J174" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K174" t="s">
-        <v>557</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9140,28 +9140,28 @@
         <v>559</v>
       </c>
       <c r="D175" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E175" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
       </c>
       <c r="G175" t="s">
-        <v>32</v>
+        <v>368</v>
       </c>
       <c r="H175" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I175" t="s">
-        <v>544</v>
+        <v>33</v>
       </c>
       <c r="J175" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K175" t="s">
-        <v>560</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9175,28 +9175,28 @@
         <v>562</v>
       </c>
       <c r="D176" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="F176" t="s">
         <v>17</v>
       </c>
       <c r="G176" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H176" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I176" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J176" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K176" t="s">
-        <v>563</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -9210,28 +9210,28 @@
         <v>565</v>
       </c>
       <c r="D177" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E177" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="F177" t="s">
         <v>17</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H177" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I177" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J177" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K177" t="s">
-        <v>566</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -9245,28 +9245,28 @@
         <v>568</v>
       </c>
       <c r="D178" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="F178" t="s">
         <v>17</v>
       </c>
       <c r="G178" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H178" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I178" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J178" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K178" t="s">
-        <v>569</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -9280,28 +9280,28 @@
         <v>571</v>
       </c>
       <c r="D179" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
       </c>
       <c r="G179" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H179" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I179" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J179" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="K179" t="s">
-        <v>572</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -9315,7 +9315,7 @@
         <v>574</v>
       </c>
       <c r="D180" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E180" t="s">
         <v>575</v>
@@ -9324,19 +9324,19 @@
         <v>17</v>
       </c>
       <c r="G180" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H180" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I180" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J180" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K180" t="s">
-        <v>576</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -9350,28 +9350,28 @@
         <v>578</v>
       </c>
       <c r="D181" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E181" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
       </c>
       <c r="G181" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H181" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I181" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J181" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K181" t="s">
-        <v>579</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -9385,28 +9385,28 @@
         <v>581</v>
       </c>
       <c r="D182" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="F182" t="s">
         <v>17</v>
       </c>
       <c r="G182" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H182" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I182" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J182" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K182" t="s">
-        <v>582</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -9417,25 +9417,25 @@
         <v>584</v>
       </c>
       <c r="D183" t="s">
-        <v>367</v>
-      </c>
-      <c r="E183" t="s">
-        <v>575</v>
+        <v>15</v>
       </c>
       <c r="F183" t="s">
         <v>17</v>
       </c>
       <c r="G183" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H183" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I183" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J183" t="s">
-        <v>19</v>
+        <v>576</v>
+      </c>
+      <c r="K183" t="s">
+        <v>17</v>
       </c>
       <c r="L183" t="s">
         <v>585</v>
@@ -9452,28 +9452,28 @@
         <v>587</v>
       </c>
       <c r="D184" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E184" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="F184" t="s">
         <v>17</v>
       </c>
       <c r="G184" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H184" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I184" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J184" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K184" t="s">
-        <v>588</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -9487,28 +9487,28 @@
         <v>590</v>
       </c>
       <c r="D185" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E185" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="F185" t="s">
         <v>17</v>
       </c>
       <c r="G185" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H185" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I185" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J185" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K185" t="s">
-        <v>591</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -9522,28 +9522,28 @@
         <v>593</v>
       </c>
       <c r="D186" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E186" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="F186" t="s">
         <v>17</v>
       </c>
       <c r="G186" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H186" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I186" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J186" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K186" t="s">
-        <v>594</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -9557,28 +9557,28 @@
         <v>596</v>
       </c>
       <c r="D187" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E187" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="F187" t="s">
         <v>17</v>
       </c>
       <c r="G187" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H187" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I187" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J187" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K187" t="s">
-        <v>597</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -9592,28 +9592,28 @@
         <v>599</v>
       </c>
       <c r="D188" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="F188" t="s">
         <v>17</v>
       </c>
       <c r="G188" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H188" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I188" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J188" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K188" t="s">
-        <v>600</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -9627,28 +9627,28 @@
         <v>602</v>
       </c>
       <c r="D189" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="F189" t="s">
         <v>17</v>
       </c>
       <c r="G189" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H189" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I189" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J189" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K189" t="s">
-        <v>603</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -9662,28 +9662,28 @@
         <v>605</v>
       </c>
       <c r="D190" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E190" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="F190" t="s">
         <v>17</v>
       </c>
       <c r="G190" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H190" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I190" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J190" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K190" t="s">
-        <v>606</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -9697,28 +9697,28 @@
         <v>608</v>
       </c>
       <c r="D191" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
-        <v>575</v>
+        <v>609</v>
       </c>
       <c r="F191" t="s">
         <v>17</v>
       </c>
       <c r="G191" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H191" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I191" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J191" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K191" t="s">
-        <v>609</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -9732,28 +9732,28 @@
         <v>611</v>
       </c>
       <c r="D192" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E192" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="F192" t="s">
         <v>17</v>
       </c>
       <c r="G192" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H192" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I192" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J192" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K192" t="s">
-        <v>612</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -9767,28 +9767,28 @@
         <v>614</v>
       </c>
       <c r="D193" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E193" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="F193" t="s">
         <v>17</v>
       </c>
       <c r="G193" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H193" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I193" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J193" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K193" t="s">
-        <v>615</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -9802,28 +9802,28 @@
         <v>617</v>
       </c>
       <c r="D194" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E194" t="s">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="F194" t="s">
         <v>17</v>
       </c>
       <c r="G194" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H194" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I194" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J194" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K194" t="s">
-        <v>618</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -9837,28 +9837,28 @@
         <v>620</v>
       </c>
       <c r="D195" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E195" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="F195" t="s">
         <v>17</v>
       </c>
       <c r="G195" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H195" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I195" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J195" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K195" t="s">
-        <v>621</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -9872,28 +9872,28 @@
         <v>623</v>
       </c>
       <c r="D196" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>575</v>
+        <v>624</v>
       </c>
       <c r="F196" t="s">
         <v>17</v>
       </c>
       <c r="G196" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H196" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I196" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J196" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="K196" t="s">
-        <v>624</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -9907,7 +9907,7 @@
         <v>626</v>
       </c>
       <c r="D197" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E197" t="s">
         <v>627</v>
@@ -9916,19 +9916,19 @@
         <v>17</v>
       </c>
       <c r="G197" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H197" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I197" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J197" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K197" t="s">
-        <v>628</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -9942,28 +9942,28 @@
         <v>630</v>
       </c>
       <c r="D198" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E198" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="F198" t="s">
         <v>17</v>
       </c>
       <c r="G198" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H198" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I198" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J198" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K198" t="s">
-        <v>631</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -9977,28 +9977,28 @@
         <v>633</v>
       </c>
       <c r="D199" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E199" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="F199" t="s">
         <v>17</v>
       </c>
       <c r="G199" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H199" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I199" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J199" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K199" t="s">
-        <v>634</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10012,28 +10012,28 @@
         <v>636</v>
       </c>
       <c r="D200" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="F200" t="s">
         <v>17</v>
       </c>
       <c r="G200" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H200" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I200" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J200" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K200" t="s">
-        <v>637</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10047,28 +10047,28 @@
         <v>639</v>
       </c>
       <c r="D201" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E201" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="F201" t="s">
         <v>17</v>
       </c>
       <c r="G201" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H201" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I201" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J201" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K201" t="s">
-        <v>640</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10082,28 +10082,28 @@
         <v>642</v>
       </c>
       <c r="D202" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E202" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="F202" t="s">
         <v>17</v>
       </c>
       <c r="G202" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H202" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I202" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J202" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K202" t="s">
-        <v>643</v>
+        <v>17</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10117,28 +10117,28 @@
         <v>645</v>
       </c>
       <c r="D203" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E203" t="s">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="F203" t="s">
         <v>17</v>
       </c>
       <c r="G203" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H203" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I203" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J203" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K203" t="s">
-        <v>646</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10152,28 +10152,28 @@
         <v>648</v>
       </c>
       <c r="D204" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
-        <v>627</v>
+        <v>649</v>
       </c>
       <c r="F204" t="s">
         <v>17</v>
       </c>
       <c r="G204" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H204" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I204" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J204" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K204" t="s">
-        <v>649</v>
+        <v>17</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10187,28 +10187,28 @@
         <v>651</v>
       </c>
       <c r="D205" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E205" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="F205" t="s">
         <v>17</v>
       </c>
       <c r="G205" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H205" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I205" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J205" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K205" t="s">
-        <v>652</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10222,28 +10222,28 @@
         <v>654</v>
       </c>
       <c r="D206" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="F206" t="s">
         <v>17</v>
       </c>
       <c r="G206" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H206" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I206" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J206" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K206" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10257,28 +10257,28 @@
         <v>657</v>
       </c>
       <c r="D207" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E207" t="s">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="F207" t="s">
         <v>17</v>
       </c>
       <c r="G207" t="s">
-        <v>32</v>
+        <v>368</v>
       </c>
       <c r="H207" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I207" t="s">
-        <v>544</v>
+        <v>33</v>
       </c>
       <c r="J207" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K207" t="s">
-        <v>658</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10292,28 +10292,28 @@
         <v>660</v>
       </c>
       <c r="D208" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E208" t="s">
-        <v>627</v>
+        <v>661</v>
       </c>
       <c r="F208" t="s">
         <v>17</v>
       </c>
       <c r="G208" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H208" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I208" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J208" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K208" t="s">
-        <v>661</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10327,28 +10327,28 @@
         <v>663</v>
       </c>
       <c r="D209" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E209" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="F209" t="s">
         <v>17</v>
       </c>
       <c r="G209" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H209" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I209" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J209" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K209" t="s">
-        <v>664</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10362,28 +10362,28 @@
         <v>666</v>
       </c>
       <c r="D210" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="F210" t="s">
         <v>17</v>
       </c>
       <c r="G210" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H210" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I210" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J210" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K210" t="s">
-        <v>667</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -10397,28 +10397,28 @@
         <v>669</v>
       </c>
       <c r="D211" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
-        <v>627</v>
+        <v>670</v>
       </c>
       <c r="F211" t="s">
         <v>17</v>
       </c>
       <c r="G211" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H211" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I211" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J211" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K211" t="s">
-        <v>670</v>
+        <v>17</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -10432,28 +10432,28 @@
         <v>672</v>
       </c>
       <c r="D212" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E212" t="s">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="F212" t="s">
         <v>17</v>
       </c>
       <c r="G212" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H212" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I212" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J212" t="s">
-        <v>19</v>
+        <v>628</v>
       </c>
       <c r="K212" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -10467,7 +10467,7 @@
         <v>675</v>
       </c>
       <c r="D213" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E213" t="s">
         <v>676</v>
@@ -10476,19 +10476,19 @@
         <v>17</v>
       </c>
       <c r="G213" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H213" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I213" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J213" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K213" t="s">
-        <v>677</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -10502,28 +10502,28 @@
         <v>679</v>
       </c>
       <c r="D214" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E214" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F214" t="s">
         <v>17</v>
       </c>
       <c r="G214" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H214" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I214" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J214" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K214" t="s">
-        <v>680</v>
+        <v>17</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -10537,28 +10537,28 @@
         <v>682</v>
       </c>
       <c r="D215" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E215" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="F215" t="s">
         <v>17</v>
       </c>
       <c r="G215" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H215" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I215" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J215" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K215" t="s">
-        <v>683</v>
+        <v>17</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10572,28 +10572,28 @@
         <v>685</v>
       </c>
       <c r="D216" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="F216" t="s">
         <v>17</v>
       </c>
       <c r="G216" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H216" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I216" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J216" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K216" t="s">
-        <v>686</v>
+        <v>17</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -10607,28 +10607,28 @@
         <v>688</v>
       </c>
       <c r="D217" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E217" t="s">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="F217" t="s">
         <v>17</v>
       </c>
       <c r="G217" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H217" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I217" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J217" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K217" t="s">
-        <v>689</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -10642,28 +10642,28 @@
         <v>691</v>
       </c>
       <c r="D218" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E218" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="F218" t="s">
         <v>17</v>
       </c>
       <c r="G218" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H218" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I218" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J218" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K218" t="s">
-        <v>692</v>
+        <v>17</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -10677,28 +10677,28 @@
         <v>694</v>
       </c>
       <c r="D219" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E219" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="F219" t="s">
         <v>17</v>
       </c>
       <c r="G219" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H219" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I219" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J219" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K219" t="s">
-        <v>695</v>
+        <v>17</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -10712,28 +10712,28 @@
         <v>697</v>
       </c>
       <c r="D220" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E220" t="s">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="F220" t="s">
         <v>17</v>
       </c>
       <c r="G220" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H220" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I220" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J220" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K220" t="s">
-        <v>698</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10747,28 +10747,28 @@
         <v>700</v>
       </c>
       <c r="D221" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E221" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="F221" t="s">
         <v>17</v>
       </c>
       <c r="G221" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H221" t="s">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="I221" t="s">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="J221" t="s">
-        <v>19</v>
+        <v>677</v>
       </c>
       <c r="K221" t="s">
-        <v>701</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -10782,7 +10782,7 @@
         <v>703</v>
       </c>
       <c r="D222" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E222" t="s">
         <v>704</v>
@@ -10791,19 +10791,19 @@
         <v>17</v>
       </c>
       <c r="G222" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H222" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I222" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J222" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K222" t="s">
-        <v>706</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -10817,28 +10817,28 @@
         <v>708</v>
       </c>
       <c r="D223" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="F223" t="s">
         <v>17</v>
       </c>
       <c r="G223" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H223" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I223" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J223" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K223" t="s">
-        <v>709</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -10852,28 +10852,28 @@
         <v>711</v>
       </c>
       <c r="D224" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E224" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="F224" t="s">
         <v>17</v>
       </c>
       <c r="G224" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H224" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I224" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J224" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K224" t="s">
-        <v>712</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -10887,28 +10887,28 @@
         <v>714</v>
       </c>
       <c r="D225" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E225" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="F225" t="s">
         <v>17</v>
       </c>
       <c r="G225" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H225" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I225" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J225" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K225" t="s">
-        <v>715</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -10922,28 +10922,28 @@
         <v>717</v>
       </c>
       <c r="D226" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="F226" t="s">
         <v>17</v>
       </c>
       <c r="G226" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H226" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I226" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J226" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K226" t="s">
-        <v>718</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -10957,28 +10957,28 @@
         <v>720</v>
       </c>
       <c r="D227" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="E227" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="F227" t="s">
         <v>17</v>
       </c>
       <c r="G227" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="H227" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I227" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J227" t="s">
-        <v>19</v>
+        <v>706</v>
       </c>
       <c r="K227" t="s">
-        <v>721</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -10998,22 +10998,22 @@
         <v>724</v>
       </c>
       <c r="F228" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G228" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H228" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I228" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J228" t="s">
-        <v>19</v>
+        <v>725</v>
       </c>
       <c r="K228" t="s">
-        <v>725</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11030,25 +11030,25 @@
         <v>15</v>
       </c>
       <c r="E229" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F229" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G229" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H229" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I229" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J229" t="s">
-        <v>19</v>
+        <v>725</v>
       </c>
       <c r="K229" t="s">
-        <v>728</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11065,25 +11065,25 @@
         <v>15</v>
       </c>
       <c r="E230" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F230" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G230" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H230" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I230" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J230" t="s">
-        <v>19</v>
+        <v>725</v>
       </c>
       <c r="K230" t="s">
-        <v>731</v>
+        <v>17</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11100,25 +11100,25 @@
         <v>15</v>
       </c>
       <c r="E231" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="F231" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G231" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H231" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I231" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J231" t="s">
-        <v>19</v>
+        <v>725</v>
       </c>
       <c r="K231" t="s">
-        <v>734</v>
+        <v>33</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11135,25 +11135,25 @@
         <v>15</v>
       </c>
       <c r="E232" t="s">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="F232" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G232" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H232" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I232" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J232" t="s">
-        <v>19</v>
+        <v>725</v>
       </c>
       <c r="K232" t="s">
-        <v>737</v>
+        <v>33</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11173,22 +11173,22 @@
         <v>740</v>
       </c>
       <c r="F233" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G233" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H233" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I233" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J233" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K233" t="s">
-        <v>741</v>
+        <v>17</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11205,25 +11205,25 @@
         <v>15</v>
       </c>
       <c r="E234" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F234" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G234" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H234" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I234" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J234" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K234" t="s">
-        <v>744</v>
+        <v>33</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11240,25 +11240,25 @@
         <v>15</v>
       </c>
       <c r="E235" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="F235" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G235" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H235" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I235" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J235" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K235" t="s">
-        <v>747</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11275,25 +11275,25 @@
         <v>15</v>
       </c>
       <c r="E236" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="F236" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G236" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H236" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I236" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J236" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K236" t="s">
-        <v>750</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11310,25 +11310,25 @@
         <v>15</v>
       </c>
       <c r="E237" t="s">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="F237" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G237" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H237" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I237" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J237" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K237" t="s">
-        <v>753</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11345,25 +11345,25 @@
         <v>15</v>
       </c>
       <c r="E238" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
       <c r="F238" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G238" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H238" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I238" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J238" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K238" t="s">
-        <v>756</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11380,25 +11380,25 @@
         <v>15</v>
       </c>
       <c r="E239" t="s">
-        <v>740</v>
+        <v>759</v>
       </c>
       <c r="F239" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G239" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H239" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I239" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J239" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K239" t="s">
-        <v>759</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11415,25 +11415,25 @@
         <v>15</v>
       </c>
       <c r="E240" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="F240" t="s">
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H240" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I240" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J240" t="s">
-        <v>19</v>
+        <v>741</v>
       </c>
       <c r="K240" t="s">
-        <v>762</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11453,22 +11453,22 @@
         <v>765</v>
       </c>
       <c r="F241" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G241" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H241" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I241" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J241" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K241" t="s">
-        <v>766</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11485,25 +11485,25 @@
         <v>15</v>
       </c>
       <c r="E242" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F242" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G242" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H242" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I242" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J242" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K242" t="s">
-        <v>769</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11520,25 +11520,25 @@
         <v>15</v>
       </c>
       <c r="E243" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="F243" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G243" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H243" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I243" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J243" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K243" t="s">
-        <v>772</v>
+        <v>17</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11555,25 +11555,25 @@
         <v>15</v>
       </c>
       <c r="E244" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="F244" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G244" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H244" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I244" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J244" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K244" t="s">
-        <v>775</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11590,25 +11590,25 @@
         <v>15</v>
       </c>
       <c r="E245" t="s">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="F245" t="s">
         <v>17</v>
       </c>
       <c r="G245" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H245" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I245" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J245" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K245" t="s">
-        <v>778</v>
+        <v>17</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11625,25 +11625,25 @@
         <v>15</v>
       </c>
       <c r="E246" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="F246" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G246" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H246" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I246" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J246" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K246" t="s">
-        <v>781</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11660,25 +11660,25 @@
         <v>15</v>
       </c>
       <c r="E247" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="F247" t="s">
         <v>17</v>
       </c>
       <c r="G247" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H247" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I247" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J247" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K247" t="s">
-        <v>784</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11695,25 +11695,25 @@
         <v>15</v>
       </c>
       <c r="E248" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="F248" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G248" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H248" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I248" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J248" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K248" t="s">
-        <v>787</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11730,25 +11730,25 @@
         <v>15</v>
       </c>
       <c r="E249" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="F249" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G249" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H249" t="s">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="I249" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J249" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K249" t="s">
-        <v>790</v>
+        <v>33</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11765,25 +11765,25 @@
         <v>15</v>
       </c>
       <c r="E250" t="s">
-        <v>765</v>
+        <v>793</v>
       </c>
       <c r="F250" t="s">
         <v>17</v>
       </c>
       <c r="G250" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H250" t="s">
-        <v>17</v>
+        <v>705</v>
       </c>
       <c r="I250" t="s">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="J250" t="s">
-        <v>19</v>
+        <v>766</v>
       </c>
       <c r="K250" t="s">
-        <v>793</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/pt/RegionM49.xlsx
+++ b/api/1/xlsx/pt/RegionM49.xlsx
@@ -22,33 +22,33 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:least-developed-countries</t>
+  </si>
+  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
     <t>codeforiati:small-island-developing-states</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:least-developed-countries</t>
+    <t>codeforiati:developed-developing</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
     <t>codeforiati:land-locked-developing-countries</t>
   </si>
   <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:developed-developing</t>
-  </si>
-  <si>
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
@@ -58,24 +58,24 @@
     <t>active</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>DZ</t>
   </si>
   <si>
     <t>001</t>
   </si>
   <si>
+    <t>Developing</t>
+  </si>
+  <si>
     <t>DZA</t>
   </si>
   <si>
-    <t>Developing</t>
-  </si>
-  <si>
     <t>015</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>729</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>SD</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>SDN</t>
   </si>
   <si>
@@ -139,12 +139,12 @@
     <t>086</t>
   </si>
   <si>
+    <t>IO</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>024</t>
   </si>
   <si>
+    <t>AO</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -427,12 +427,12 @@
     <t>072</t>
   </si>
   <si>
+    <t>BW</t>
+  </si>
+  <si>
     <t>018</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>204</t>
   </si>
   <si>
+    <t>BJ</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -634,12 +634,12 @@
     <t>019</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>029</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>AIA</t>
   </si>
   <si>
@@ -892,12 +892,12 @@
     <t>084</t>
   </si>
   <si>
+    <t>BZ</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>032</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1117,10 +1117,10 @@
     <t>BM</t>
   </si>
   <si>
+    <t>Developed</t>
+  </si>
+  <si>
     <t>BMU</t>
-  </si>
-  <si>
-    <t>Developed</t>
   </si>
   <si>
     <t>021</t>
@@ -2778,26 +2778,26 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -2813,26 +2813,26 @@
       <c r="C3" t="s">
         <v>14</v>
       </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
         <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -2848,26 +2848,26 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>20</v>
@@ -2883,26 +2883,26 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
       <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
         <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
         <v>20</v>
@@ -2916,28 +2916,28 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
         <v>33</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
         <v>20</v>
@@ -2953,26 +2953,26 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -2988,26 +2988,26 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
       <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
         <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
         <v>20</v>
@@ -3024,28 +3024,28 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
         <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
         <v>44</v>
@@ -3059,31 +3059,31 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
         <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L10" t="s">
         <v>44</v>
@@ -3097,31 +3097,31 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
         <v>50</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
         <v>44</v>
@@ -3135,31 +3135,31 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L12" t="s">
         <v>44</v>
@@ -3173,31 +3173,31 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
         <v>56</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L13" t="s">
         <v>44</v>
@@ -3211,31 +3211,31 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
         <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L14" t="s">
         <v>44</v>
@@ -3252,28 +3252,28 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
         <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L15" t="s">
         <v>44</v>
@@ -3290,28 +3290,28 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
         <v>65</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L16" t="s">
         <v>44</v>
@@ -3325,31 +3325,31 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
         <v>68</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L17" t="s">
         <v>44</v>
@@ -3363,31 +3363,31 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
         <v>71</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L18" t="s">
         <v>44</v>
@@ -3404,28 +3404,28 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
         <v>74</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L19" t="s">
         <v>44</v>
@@ -3442,28 +3442,28 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
         <v>77</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L20" t="s">
         <v>44</v>
@@ -3477,31 +3477,31 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
         <v>80</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L21" t="s">
         <v>44</v>
@@ -3518,28 +3518,28 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
         <v>83</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L22" t="s">
         <v>44</v>
@@ -3553,31 +3553,31 @@
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
         <v>86</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L23" t="s">
         <v>44</v>
@@ -3594,28 +3594,28 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
         <v>89</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L24" t="s">
         <v>44</v>
@@ -3629,31 +3629,31 @@
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
         <v>92</v>
       </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L25" t="s">
         <v>44</v>
@@ -3667,31 +3667,31 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="F26" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
         <v>95</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L26" t="s">
         <v>44</v>
@@ -3705,31 +3705,31 @@
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
         <v>98</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L27" t="s">
         <v>44</v>
@@ -3743,31 +3743,31 @@
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
         <v>101</v>
       </c>
       <c r="K28" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L28" t="s">
         <v>44</v>
@@ -3781,31 +3781,31 @@
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
         <v>104</v>
       </c>
       <c r="K29" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L29" t="s">
         <v>44</v>
@@ -3822,28 +3822,28 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
         <v>107</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L30" t="s">
         <v>44</v>
@@ -3857,31 +3857,31 @@
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
         <v>109</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
         <v>111</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L31" t="s">
         <v>44</v>
@@ -3898,28 +3898,28 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
         <v>114</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L32" t="s">
         <v>44</v>
@@ -3933,31 +3933,31 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J33" t="s">
         <v>117</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L33" t="s">
         <v>44</v>
@@ -3971,31 +3971,31 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s">
         <v>120</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L34" t="s">
         <v>44</v>
@@ -4012,28 +4012,28 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="F35" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
         <v>123</v>
       </c>
       <c r="K35" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L35" t="s">
         <v>44</v>
@@ -4047,31 +4047,31 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G36" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
         <v>126</v>
       </c>
       <c r="K36" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L36" t="s">
         <v>44</v>
@@ -4088,28 +4088,28 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
         <v>129</v>
       </c>
       <c r="K37" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L37" t="s">
         <v>44</v>
@@ -4126,28 +4126,28 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
         <v>132</v>
       </c>
       <c r="K38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L38" t="s">
         <v>44</v>
@@ -4161,31 +4161,31 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
         <v>135</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L39" t="s">
         <v>44</v>
@@ -4202,28 +4202,28 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
         <v>137</v>
-      </c>
-      <c r="E40" t="s">
-        <v>15</v>
       </c>
       <c r="F40" t="s">
         <v>138</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
         <v>139</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L40" t="s">
         <v>44</v>
@@ -4240,28 +4240,28 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" t="s">
         <v>142</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L41" t="s">
         <v>44</v>
@@ -4275,31 +4275,31 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="F42" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
         <v>145</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L42" t="s">
         <v>44</v>
@@ -4316,28 +4316,28 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="F43" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
         <v>148</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L43" t="s">
         <v>44</v>
@@ -4354,28 +4354,28 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="F44" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
         <v>151</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L44" t="s">
         <v>44</v>
@@ -4389,31 +4389,31 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
         <v>153</v>
-      </c>
-      <c r="E45" t="s">
-        <v>15</v>
       </c>
       <c r="F45" t="s">
         <v>154</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
         <v>155</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L45" t="s">
         <v>44</v>
@@ -4427,31 +4427,31 @@
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="F46" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
         <v>158</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L46" t="s">
         <v>44</v>
@@ -4468,28 +4468,28 @@
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J47" t="s">
         <v>161</v>
       </c>
       <c r="K47" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L47" t="s">
         <v>44</v>
@@ -4506,28 +4506,28 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J48" t="s">
         <v>164</v>
       </c>
       <c r="K48" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L48" t="s">
         <v>44</v>
@@ -4541,31 +4541,31 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="F49" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s">
         <v>167</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L49" t="s">
         <v>44</v>
@@ -4582,28 +4582,28 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
         <v>170</v>
       </c>
       <c r="K50" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L50" t="s">
         <v>44</v>
@@ -4617,31 +4617,31 @@
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="F51" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s">
         <v>173</v>
       </c>
       <c r="K51" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L51" t="s">
         <v>44</v>
@@ -4655,31 +4655,31 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>175</v>
       </c>
       <c r="F52" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J52" t="s">
         <v>176</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L52" t="s">
         <v>44</v>
@@ -4693,31 +4693,31 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="F53" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J53" t="s">
         <v>179</v>
       </c>
       <c r="K53" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L53" t="s">
         <v>44</v>
@@ -4731,31 +4731,31 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="F54" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J54" t="s">
         <v>182</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L54" t="s">
         <v>44</v>
@@ -4769,31 +4769,31 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F55" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J55" t="s">
         <v>185</v>
       </c>
       <c r="K55" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L55" t="s">
         <v>44</v>
@@ -4807,31 +4807,31 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>187</v>
       </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J56" t="s">
         <v>188</v>
       </c>
       <c r="K56" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L56" t="s">
         <v>44</v>
@@ -4848,28 +4848,28 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="F57" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
         <v>191</v>
       </c>
       <c r="K57" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L57" t="s">
         <v>44</v>
@@ -4886,28 +4886,28 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="F58" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
         <v>194</v>
       </c>
       <c r="K58" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L58" t="s">
         <v>44</v>
@@ -4921,31 +4921,31 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="F59" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="G59" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
         <v>197</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L59" t="s">
         <v>44</v>
@@ -4959,31 +4959,31 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="F60" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="G60" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
         <v>200</v>
       </c>
       <c r="K60" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L60" t="s">
         <v>44</v>
@@ -4997,31 +4997,31 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="F61" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="G61" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s">
         <v>203</v>
       </c>
       <c r="K61" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L61" t="s">
         <v>44</v>
@@ -5035,31 +5035,31 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
         <v>205</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>206</v>
-      </c>
-      <c r="E62" t="s">
-        <v>32</v>
       </c>
       <c r="F62" t="s">
         <v>207</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s">
         <v>208</v>
       </c>
       <c r="K62" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L62" t="s">
         <v>209</v>
@@ -5073,31 +5073,31 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
         <v>205</v>
       </c>
-      <c r="D63" t="s">
-        <v>206</v>
-      </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>211</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
         <v>212</v>
       </c>
       <c r="K63" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L63" t="s">
         <v>209</v>
@@ -5111,31 +5111,31 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s">
         <v>205</v>
       </c>
-      <c r="D64" t="s">
-        <v>206</v>
-      </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="F64" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
         <v>215</v>
       </c>
       <c r="K64" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L64" t="s">
         <v>209</v>
@@ -5149,31 +5149,31 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
         <v>205</v>
       </c>
-      <c r="D65" t="s">
-        <v>206</v>
-      </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>217</v>
       </c>
       <c r="F65" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
         <v>218</v>
       </c>
       <c r="K65" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L65" t="s">
         <v>209</v>
@@ -5187,31 +5187,31 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
         <v>205</v>
       </c>
-      <c r="D66" t="s">
-        <v>206</v>
-      </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>220</v>
       </c>
       <c r="F66" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
         <v>221</v>
       </c>
       <c r="K66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L66" t="s">
         <v>209</v>
@@ -5225,31 +5225,31 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
         <v>205</v>
       </c>
-      <c r="D67" t="s">
-        <v>206</v>
-      </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>223</v>
       </c>
       <c r="F67" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
         <v>224</v>
       </c>
       <c r="K67" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L67" t="s">
         <v>209</v>
@@ -5263,31 +5263,31 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" t="s">
         <v>205</v>
       </c>
-      <c r="D68" t="s">
-        <v>206</v>
-      </c>
       <c r="E68" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="F68" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
         <v>227</v>
       </c>
       <c r="K68" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L68" t="s">
         <v>209</v>
@@ -5301,31 +5301,31 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s">
         <v>205</v>
       </c>
-      <c r="D69" t="s">
-        <v>206</v>
-      </c>
       <c r="E69" t="s">
-        <v>15</v>
+        <v>229</v>
       </c>
       <c r="F69" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J69" t="s">
         <v>230</v>
       </c>
       <c r="K69" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L69" t="s">
         <v>209</v>
@@ -5339,31 +5339,31 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
         <v>205</v>
       </c>
-      <c r="D70" t="s">
-        <v>206</v>
-      </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="F70" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s">
         <v>233</v>
       </c>
       <c r="K70" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L70" t="s">
         <v>209</v>
@@ -5377,31 +5377,31 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" t="s">
         <v>205</v>
       </c>
-      <c r="D71" t="s">
-        <v>206</v>
-      </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="F71" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J71" t="s">
         <v>236</v>
       </c>
       <c r="K71" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L71" t="s">
         <v>209</v>
@@ -5415,31 +5415,31 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
         <v>205</v>
       </c>
-      <c r="D72" t="s">
-        <v>206</v>
-      </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="F72" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J72" t="s">
         <v>239</v>
       </c>
       <c r="K72" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L72" t="s">
         <v>209</v>
@@ -5453,31 +5453,31 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
         <v>205</v>
       </c>
-      <c r="D73" t="s">
-        <v>206</v>
-      </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="F73" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
         <v>242</v>
       </c>
       <c r="K73" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L73" t="s">
         <v>209</v>
@@ -5491,31 +5491,31 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" t="s">
         <v>205</v>
       </c>
-      <c r="D74" t="s">
-        <v>206</v>
-      </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="F74" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J74" t="s">
         <v>245</v>
       </c>
       <c r="K74" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L74" t="s">
         <v>209</v>
@@ -5529,31 +5529,31 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
         <v>205</v>
       </c>
-      <c r="D75" t="s">
-        <v>206</v>
-      </c>
       <c r="E75" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="F75" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" t="s">
         <v>248</v>
       </c>
       <c r="K75" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L75" t="s">
         <v>209</v>
@@ -5567,31 +5567,31 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" t="s">
         <v>205</v>
       </c>
-      <c r="D76" t="s">
-        <v>206</v>
-      </c>
       <c r="E76" t="s">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="F76" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="G76" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J76" t="s">
         <v>251</v>
       </c>
       <c r="K76" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L76" t="s">
         <v>209</v>
@@ -5605,31 +5605,31 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
         <v>205</v>
       </c>
-      <c r="D77" t="s">
-        <v>206</v>
-      </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="F77" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
         <v>254</v>
       </c>
       <c r="K77" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L77" t="s">
         <v>209</v>
@@ -5643,31 +5643,31 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
         <v>205</v>
       </c>
-      <c r="D78" t="s">
-        <v>206</v>
-      </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>256</v>
       </c>
       <c r="F78" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
         <v>257</v>
       </c>
       <c r="K78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L78" t="s">
         <v>209</v>
@@ -5681,31 +5681,31 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
         <v>205</v>
       </c>
-      <c r="D79" t="s">
-        <v>206</v>
-      </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>259</v>
       </c>
       <c r="F79" t="s">
-        <v>259</v>
+        <v>207</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
         <v>260</v>
       </c>
       <c r="K79" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L79" t="s">
         <v>209</v>
@@ -5719,31 +5719,31 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
         <v>205</v>
       </c>
-      <c r="D80" t="s">
-        <v>206</v>
-      </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="F80" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
         <v>263</v>
       </c>
       <c r="K80" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L80" t="s">
         <v>209</v>
@@ -5757,31 +5757,31 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
         <v>205</v>
       </c>
-      <c r="D81" t="s">
-        <v>206</v>
-      </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
       <c r="F81" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
         <v>266</v>
       </c>
       <c r="K81" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L81" t="s">
         <v>209</v>
@@ -5795,31 +5795,31 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" t="s">
         <v>205</v>
       </c>
-      <c r="D82" t="s">
-        <v>206</v>
-      </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="F82" t="s">
-        <v>268</v>
+        <v>207</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
         <v>269</v>
       </c>
       <c r="K82" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L82" t="s">
         <v>209</v>
@@ -5833,31 +5833,31 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
         <v>205</v>
       </c>
-      <c r="D83" t="s">
-        <v>206</v>
-      </c>
       <c r="E83" t="s">
-        <v>32</v>
+        <v>271</v>
       </c>
       <c r="F83" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
         <v>272</v>
       </c>
       <c r="K83" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L83" t="s">
         <v>209</v>
@@ -5871,31 +5871,31 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" t="s">
         <v>205</v>
       </c>
-      <c r="D84" t="s">
-        <v>206</v>
-      </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="F84" t="s">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
         <v>275</v>
       </c>
       <c r="K84" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L84" t="s">
         <v>209</v>
@@ -5909,31 +5909,31 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
         <v>205</v>
       </c>
-      <c r="D85" t="s">
-        <v>206</v>
-      </c>
       <c r="E85" t="s">
-        <v>32</v>
+        <v>277</v>
       </c>
       <c r="F85" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J85" t="s">
         <v>278</v>
       </c>
       <c r="K85" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L85" t="s">
         <v>209</v>
@@ -5947,31 +5947,31 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
         <v>205</v>
       </c>
-      <c r="D86" t="s">
-        <v>206</v>
-      </c>
       <c r="E86" t="s">
-        <v>32</v>
+        <v>280</v>
       </c>
       <c r="F86" t="s">
-        <v>280</v>
+        <v>207</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J86" t="s">
         <v>281</v>
       </c>
       <c r="K86" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L86" t="s">
         <v>209</v>
@@ -5985,31 +5985,31 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
         <v>205</v>
       </c>
-      <c r="D87" t="s">
-        <v>206</v>
-      </c>
       <c r="E87" t="s">
-        <v>32</v>
+        <v>283</v>
       </c>
       <c r="F87" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
         <v>284</v>
       </c>
       <c r="K87" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L87" t="s">
         <v>209</v>
@@ -6023,31 +6023,31 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" t="s">
         <v>205</v>
       </c>
-      <c r="D88" t="s">
-        <v>206</v>
-      </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F88" t="s">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J88" t="s">
         <v>287</v>
       </c>
       <c r="K88" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L88" t="s">
         <v>209</v>
@@ -6061,31 +6061,31 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
         <v>205</v>
       </c>
-      <c r="D89" t="s">
-        <v>206</v>
-      </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="F89" t="s">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s">
         <v>290</v>
       </c>
       <c r="K89" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L89" t="s">
         <v>209</v>
@@ -6099,31 +6099,31 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" t="s">
         <v>205</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>292</v>
-      </c>
-      <c r="E90" t="s">
-        <v>32</v>
       </c>
       <c r="F90" t="s">
         <v>293</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J90" t="s">
         <v>294</v>
       </c>
       <c r="K90" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L90" t="s">
         <v>209</v>
@@ -6137,31 +6137,31 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" t="s">
         <v>205</v>
       </c>
-      <c r="D91" t="s">
-        <v>292</v>
-      </c>
       <c r="E91" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="F91" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J91" t="s">
         <v>297</v>
       </c>
       <c r="K91" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L91" t="s">
         <v>209</v>
@@ -6175,31 +6175,31 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" t="s">
         <v>205</v>
       </c>
-      <c r="D92" t="s">
-        <v>292</v>
-      </c>
       <c r="E92" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="F92" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J92" t="s">
         <v>300</v>
       </c>
       <c r="K92" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L92" t="s">
         <v>209</v>
@@ -6213,31 +6213,31 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
         <v>205</v>
       </c>
-      <c r="D93" t="s">
-        <v>292</v>
-      </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>302</v>
       </c>
       <c r="F93" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J93" t="s">
         <v>303</v>
       </c>
       <c r="K93" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L93" t="s">
         <v>209</v>
@@ -6251,31 +6251,31 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
         <v>205</v>
       </c>
-      <c r="D94" t="s">
-        <v>292</v>
-      </c>
       <c r="E94" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="F94" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J94" t="s">
         <v>306</v>
       </c>
       <c r="K94" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L94" t="s">
         <v>209</v>
@@ -6289,31 +6289,31 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
         <v>205</v>
       </c>
-      <c r="D95" t="s">
-        <v>292</v>
-      </c>
       <c r="E95" t="s">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="F95" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J95" t="s">
         <v>309</v>
       </c>
       <c r="K95" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L95" t="s">
         <v>209</v>
@@ -6327,31 +6327,31 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" t="s">
         <v>205</v>
       </c>
-      <c r="D96" t="s">
-        <v>292</v>
-      </c>
       <c r="E96" t="s">
-        <v>15</v>
+        <v>311</v>
       </c>
       <c r="F96" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J96" t="s">
         <v>312</v>
       </c>
       <c r="K96" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L96" t="s">
         <v>209</v>
@@ -6365,31 +6365,31 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" t="s">
         <v>205</v>
       </c>
-      <c r="D97" t="s">
-        <v>292</v>
-      </c>
       <c r="E97" t="s">
-        <v>15</v>
+        <v>314</v>
       </c>
       <c r="F97" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
         <v>315</v>
       </c>
       <c r="K97" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L97" t="s">
         <v>209</v>
@@ -6403,31 +6403,31 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
         <v>205</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>317</v>
-      </c>
-      <c r="E98" t="s">
-        <v>15</v>
       </c>
       <c r="F98" t="s">
         <v>318</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J98" t="s">
         <v>319</v>
       </c>
       <c r="K98" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L98" t="s">
         <v>209</v>
@@ -6441,31 +6441,31 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
         <v>205</v>
       </c>
-      <c r="D99" t="s">
-        <v>317</v>
-      </c>
       <c r="E99" t="s">
-        <v>15</v>
+        <v>321</v>
       </c>
       <c r="F99" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J99" t="s">
         <v>322</v>
       </c>
       <c r="K99" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L99" t="s">
         <v>209</v>
@@ -6479,31 +6479,31 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
         <v>205</v>
       </c>
-      <c r="D100" t="s">
-        <v>317</v>
-      </c>
       <c r="E100" t="s">
-        <v>15</v>
+        <v>324</v>
       </c>
       <c r="F100" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
         <v>325</v>
       </c>
       <c r="K100" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L100" t="s">
         <v>209</v>
@@ -6517,31 +6517,31 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" t="s">
         <v>205</v>
       </c>
-      <c r="D101" t="s">
-        <v>317</v>
-      </c>
       <c r="E101" t="s">
-        <v>15</v>
+        <v>327</v>
       </c>
       <c r="F101" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J101" t="s">
         <v>328</v>
       </c>
       <c r="K101" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L101" t="s">
         <v>209</v>
@@ -6555,31 +6555,31 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
+        <v>14</v>
+      </c>
+      <c r="D102" t="s">
         <v>205</v>
       </c>
-      <c r="D102" t="s">
-        <v>317</v>
-      </c>
       <c r="E102" t="s">
-        <v>15</v>
+        <v>330</v>
       </c>
       <c r="F102" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
         <v>331</v>
       </c>
       <c r="K102" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L102" t="s">
         <v>209</v>
@@ -6593,31 +6593,31 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" t="s">
         <v>205</v>
       </c>
-      <c r="D103" t="s">
-        <v>317</v>
-      </c>
       <c r="E103" t="s">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="F103" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
         <v>334</v>
       </c>
       <c r="K103" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L103" t="s">
         <v>209</v>
@@ -6631,31 +6631,31 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s">
         <v>205</v>
       </c>
-      <c r="D104" t="s">
-        <v>317</v>
-      </c>
       <c r="E104" t="s">
-        <v>15</v>
+        <v>336</v>
       </c>
       <c r="F104" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
         <v>337</v>
       </c>
       <c r="K104" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L104" t="s">
         <v>209</v>
@@ -6669,31 +6669,31 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" t="s">
         <v>205</v>
       </c>
-      <c r="D105" t="s">
-        <v>317</v>
-      </c>
       <c r="E105" t="s">
-        <v>15</v>
+        <v>339</v>
       </c>
       <c r="F105" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
         <v>340</v>
       </c>
       <c r="K105" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L105" t="s">
         <v>209</v>
@@ -6707,31 +6707,31 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" t="s">
         <v>205</v>
       </c>
-      <c r="D106" t="s">
-        <v>317</v>
-      </c>
       <c r="E106" t="s">
-        <v>15</v>
+        <v>342</v>
       </c>
       <c r="F106" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
         <v>343</v>
       </c>
       <c r="K106" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L106" t="s">
         <v>209</v>
@@ -6745,31 +6745,31 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s">
         <v>205</v>
       </c>
-      <c r="D107" t="s">
-        <v>317</v>
-      </c>
       <c r="E107" t="s">
-        <v>32</v>
+        <v>345</v>
       </c>
       <c r="F107" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="G107" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H107" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" t="s">
         <v>346</v>
       </c>
       <c r="K107" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L107" t="s">
         <v>209</v>
@@ -6783,31 +6783,31 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s">
         <v>205</v>
       </c>
-      <c r="D108" t="s">
-        <v>317</v>
-      </c>
       <c r="E108" t="s">
-        <v>15</v>
+        <v>348</v>
       </c>
       <c r="F108" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="G108" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J108" t="s">
         <v>349</v>
       </c>
       <c r="K108" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L108" t="s">
         <v>209</v>
@@ -6821,31 +6821,31 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" t="s">
         <v>205</v>
       </c>
-      <c r="D109" t="s">
-        <v>317</v>
-      </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
       <c r="F109" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="G109" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J109" t="s">
         <v>352</v>
       </c>
       <c r="K109" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L109" t="s">
         <v>209</v>
@@ -6859,31 +6859,31 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" t="s">
         <v>205</v>
       </c>
-      <c r="D110" t="s">
-        <v>317</v>
-      </c>
       <c r="E110" t="s">
-        <v>15</v>
+        <v>354</v>
       </c>
       <c r="F110" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" t="s">
         <v>355</v>
       </c>
       <c r="K110" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L110" t="s">
         <v>209</v>
@@ -6897,31 +6897,31 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" t="s">
         <v>205</v>
       </c>
-      <c r="D111" t="s">
-        <v>317</v>
-      </c>
       <c r="E111" t="s">
-        <v>32</v>
+        <v>357</v>
       </c>
       <c r="F111" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="G111" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H111" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J111" t="s">
         <v>358</v>
       </c>
       <c r="K111" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L111" t="s">
         <v>209</v>
@@ -6935,31 +6935,31 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" t="s">
         <v>205</v>
       </c>
-      <c r="D112" t="s">
-        <v>317</v>
-      </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="F112" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="G112" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J112" t="s">
         <v>361</v>
       </c>
       <c r="K112" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L112" t="s">
         <v>209</v>
@@ -6973,31 +6973,31 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
+        <v>14</v>
+      </c>
+      <c r="D113" t="s">
         <v>205</v>
       </c>
-      <c r="D113" t="s">
-        <v>317</v>
-      </c>
       <c r="E113" t="s">
-        <v>15</v>
+        <v>363</v>
       </c>
       <c r="F113" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="G113" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J113" t="s">
         <v>364</v>
       </c>
       <c r="K113" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L113" t="s">
         <v>209</v>
@@ -7011,28 +7011,28 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114" t="s">
         <v>205</v>
       </c>
       <c r="E114" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" t="s">
         <v>366</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J114" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K114" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L114" t="s">
         <v>369</v>
@@ -7046,28 +7046,28 @@
         <v>13</v>
       </c>
       <c r="C115" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" t="s">
         <v>205</v>
       </c>
       <c r="E115" t="s">
-        <v>15</v>
-      </c>
-      <c r="F115" t="s">
         <v>371</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I115" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J115" t="s">
         <v>372</v>
       </c>
       <c r="K115" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L115" t="s">
         <v>369</v>
@@ -7081,28 +7081,28 @@
         <v>13</v>
       </c>
       <c r="C116" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" t="s">
         <v>205</v>
       </c>
       <c r="E116" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" t="s">
         <v>374</v>
       </c>
       <c r="G116" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I116" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J116" t="s">
         <v>375</v>
       </c>
       <c r="K116" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L116" t="s">
         <v>369</v>
@@ -7116,28 +7116,28 @@
         <v>13</v>
       </c>
       <c r="C117" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" t="s">
         <v>205</v>
       </c>
       <c r="E117" t="s">
-        <v>15</v>
-      </c>
-      <c r="F117" t="s">
         <v>377</v>
       </c>
       <c r="G117" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I117" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J117" t="s">
         <v>378</v>
       </c>
       <c r="K117" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L117" t="s">
         <v>369</v>
@@ -7151,28 +7151,28 @@
         <v>13</v>
       </c>
       <c r="C118" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" t="s">
         <v>205</v>
       </c>
       <c r="E118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
         <v>380</v>
       </c>
       <c r="G118" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I118" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J118" t="s">
         <v>381</v>
       </c>
       <c r="K118" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L118" t="s">
         <v>369</v>
@@ -7185,23 +7185,23 @@
       <c r="B119" t="s">
         <v>13</v>
       </c>
+      <c r="C119" t="s">
+        <v>14</v>
+      </c>
       <c r="E119" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" t="s">
         <v>383</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
-      </c>
-      <c r="I119" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J119" t="s">
         <v>384</v>
+      </c>
+      <c r="K119" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7212,28 +7212,28 @@
         <v>13</v>
       </c>
       <c r="C120" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120" t="s">
         <v>386</v>
       </c>
       <c r="E120" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" t="s">
         <v>387</v>
       </c>
       <c r="G120" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I120" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J120" t="s">
         <v>388</v>
       </c>
       <c r="K120" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L120" t="s">
         <v>389</v>
@@ -7247,28 +7247,28 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" t="s">
         <v>386</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
         <v>391</v>
       </c>
       <c r="G121" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H121" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I121" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J121" t="s">
         <v>392</v>
       </c>
       <c r="K121" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L121" t="s">
         <v>389</v>
@@ -7282,28 +7282,28 @@
         <v>13</v>
       </c>
       <c r="C122" t="s">
+        <v>14</v>
+      </c>
+      <c r="D122" t="s">
         <v>386</v>
       </c>
       <c r="E122" t="s">
-        <v>15</v>
-      </c>
-      <c r="F122" t="s">
         <v>394</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I122" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J122" t="s">
         <v>395</v>
       </c>
       <c r="K122" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L122" t="s">
         <v>389</v>
@@ -7317,28 +7317,28 @@
         <v>13</v>
       </c>
       <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" t="s">
         <v>386</v>
       </c>
       <c r="E123" t="s">
-        <v>15</v>
-      </c>
-      <c r="F123" t="s">
         <v>397</v>
       </c>
       <c r="G123" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H123" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I123" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J123" t="s">
         <v>398</v>
       </c>
       <c r="K123" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L123" t="s">
         <v>389</v>
@@ -7352,28 +7352,28 @@
         <v>13</v>
       </c>
       <c r="C124" t="s">
+        <v>14</v>
+      </c>
+      <c r="D124" t="s">
         <v>386</v>
       </c>
       <c r="E124" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" t="s">
         <v>400</v>
       </c>
       <c r="G124" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H124" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I124" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J124" t="s">
         <v>401</v>
       </c>
       <c r="K124" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L124" t="s">
         <v>389</v>
@@ -7387,28 +7387,28 @@
         <v>13</v>
       </c>
       <c r="C125" t="s">
+        <v>14</v>
+      </c>
+      <c r="D125" t="s">
         <v>386</v>
       </c>
       <c r="E125" t="s">
-        <v>15</v>
-      </c>
-      <c r="F125" t="s">
         <v>403</v>
       </c>
       <c r="G125" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I125" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J125" t="s">
         <v>404</v>
       </c>
       <c r="K125" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L125" t="s">
         <v>405</v>
@@ -7422,28 +7422,28 @@
         <v>13</v>
       </c>
       <c r="C126" t="s">
+        <v>14</v>
+      </c>
+      <c r="D126" t="s">
         <v>386</v>
       </c>
       <c r="E126" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" t="s">
         <v>407</v>
       </c>
       <c r="G126" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J126" t="s">
         <v>408</v>
       </c>
       <c r="K126" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L126" t="s">
         <v>405</v>
@@ -7457,28 +7457,28 @@
         <v>13</v>
       </c>
       <c r="C127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" t="s">
         <v>386</v>
       </c>
       <c r="E127" t="s">
-        <v>15</v>
-      </c>
-      <c r="F127" t="s">
         <v>410</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J127" t="s">
         <v>411</v>
       </c>
       <c r="K127" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L127" t="s">
         <v>405</v>
@@ -7492,28 +7492,28 @@
         <v>13</v>
       </c>
       <c r="C128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" t="s">
         <v>386</v>
       </c>
       <c r="E128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
         <v>413</v>
       </c>
       <c r="G128" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J128" t="s">
         <v>414</v>
       </c>
       <c r="K128" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L128" t="s">
         <v>405</v>
@@ -7527,28 +7527,28 @@
         <v>13</v>
       </c>
       <c r="C129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129" t="s">
         <v>386</v>
       </c>
       <c r="E129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
         <v>416</v>
       </c>
       <c r="G129" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I129" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J129" t="s">
         <v>417</v>
       </c>
       <c r="K129" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L129" t="s">
         <v>405</v>
@@ -7562,28 +7562,28 @@
         <v>13</v>
       </c>
       <c r="C130" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" t="s">
         <v>386</v>
       </c>
       <c r="E130" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" t="s">
         <v>419</v>
       </c>
       <c r="G130" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H130" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I130" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J130" t="s">
         <v>420</v>
       </c>
       <c r="K130" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L130" t="s">
         <v>405</v>
@@ -7597,28 +7597,28 @@
         <v>13</v>
       </c>
       <c r="C131" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" t="s">
         <v>386</v>
       </c>
       <c r="E131" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" t="s">
         <v>422</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J131" t="s">
         <v>423</v>
       </c>
       <c r="K131" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L131" t="s">
         <v>405</v>
@@ -7632,28 +7632,28 @@
         <v>13</v>
       </c>
       <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" t="s">
         <v>386</v>
       </c>
       <c r="E132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" t="s">
         <v>425</v>
       </c>
       <c r="G132" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I132" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J132" t="s">
         <v>426</v>
       </c>
       <c r="K132" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L132" t="s">
         <v>427</v>
@@ -7667,28 +7667,28 @@
         <v>13</v>
       </c>
       <c r="C133" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" t="s">
         <v>386</v>
       </c>
       <c r="E133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
         <v>429</v>
       </c>
       <c r="G133" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I133" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J133" t="s">
         <v>430</v>
       </c>
       <c r="K133" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L133" t="s">
         <v>427</v>
@@ -7702,28 +7702,28 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134" t="s">
         <v>386</v>
       </c>
       <c r="E134" t="s">
-        <v>15</v>
-      </c>
-      <c r="F134" t="s">
         <v>432</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I134" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J134" t="s">
         <v>433</v>
       </c>
       <c r="K134" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L134" t="s">
         <v>427</v>
@@ -7737,28 +7737,28 @@
         <v>13</v>
       </c>
       <c r="C135" t="s">
+        <v>31</v>
+      </c>
+      <c r="D135" t="s">
         <v>386</v>
       </c>
       <c r="E135" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" t="s">
         <v>435</v>
       </c>
       <c r="G135" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H135" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I135" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J135" t="s">
         <v>436</v>
       </c>
       <c r="K135" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L135" t="s">
         <v>427</v>
@@ -7772,28 +7772,28 @@
         <v>13</v>
       </c>
       <c r="C136" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" t="s">
         <v>386</v>
       </c>
       <c r="E136" t="s">
-        <v>15</v>
-      </c>
-      <c r="F136" t="s">
         <v>438</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I136" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J136" t="s">
         <v>439</v>
       </c>
       <c r="K136" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L136" t="s">
         <v>427</v>
@@ -7807,28 +7807,28 @@
         <v>13</v>
       </c>
       <c r="C137" t="s">
+        <v>31</v>
+      </c>
+      <c r="D137" t="s">
         <v>386</v>
       </c>
       <c r="E137" t="s">
-        <v>15</v>
-      </c>
-      <c r="F137" t="s">
         <v>441</v>
       </c>
       <c r="G137" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J137" t="s">
         <v>442</v>
       </c>
       <c r="K137" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L137" t="s">
         <v>427</v>
@@ -7842,28 +7842,28 @@
         <v>13</v>
       </c>
       <c r="C138" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" t="s">
         <v>386</v>
       </c>
       <c r="E138" t="s">
-        <v>15</v>
-      </c>
-      <c r="F138" t="s">
         <v>444</v>
       </c>
       <c r="G138" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J138" t="s">
         <v>445</v>
       </c>
       <c r="K138" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L138" t="s">
         <v>427</v>
@@ -7877,28 +7877,28 @@
         <v>13</v>
       </c>
       <c r="C139" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" t="s">
         <v>386</v>
       </c>
       <c r="E139" t="s">
-        <v>32</v>
-      </c>
-      <c r="F139" t="s">
         <v>447</v>
       </c>
       <c r="G139" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H139" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I139" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J139" t="s">
         <v>448</v>
       </c>
       <c r="K139" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L139" t="s">
         <v>427</v>
@@ -7912,28 +7912,28 @@
         <v>13</v>
       </c>
       <c r="C140" t="s">
+        <v>14</v>
+      </c>
+      <c r="D140" t="s">
         <v>386</v>
       </c>
       <c r="E140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" t="s">
         <v>450</v>
       </c>
       <c r="G140" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I140" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J140" t="s">
         <v>451</v>
       </c>
       <c r="K140" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L140" t="s">
         <v>427</v>
@@ -7947,28 +7947,28 @@
         <v>13</v>
       </c>
       <c r="C141" t="s">
+        <v>31</v>
+      </c>
+      <c r="D141" t="s">
         <v>386</v>
       </c>
       <c r="E141" t="s">
-        <v>32</v>
-      </c>
-      <c r="F141" t="s">
         <v>453</v>
       </c>
       <c r="G141" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H141" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I141" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J141" t="s">
         <v>454</v>
       </c>
       <c r="K141" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L141" t="s">
         <v>427</v>
@@ -7982,28 +7982,28 @@
         <v>13</v>
       </c>
       <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" t="s">
         <v>386</v>
       </c>
       <c r="E142" t="s">
-        <v>15</v>
-      </c>
-      <c r="F142" t="s">
         <v>456</v>
       </c>
       <c r="G142" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J142" t="s">
         <v>457</v>
       </c>
       <c r="K142" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L142" t="s">
         <v>427</v>
@@ -8017,28 +8017,28 @@
         <v>13</v>
       </c>
       <c r="C143" t="s">
+        <v>31</v>
+      </c>
+      <c r="D143" t="s">
         <v>386</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
-      </c>
-      <c r="F143" t="s">
         <v>459</v>
       </c>
       <c r="G143" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H143" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I143" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J143" t="s">
         <v>460</v>
       </c>
       <c r="K143" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L143" t="s">
         <v>461</v>
@@ -8052,28 +8052,28 @@
         <v>13</v>
       </c>
       <c r="C144" t="s">
+        <v>31</v>
+      </c>
+      <c r="D144" t="s">
         <v>386</v>
       </c>
       <c r="E144" t="s">
-        <v>15</v>
-      </c>
-      <c r="F144" t="s">
         <v>463</v>
       </c>
       <c r="G144" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J144" t="s">
         <v>464</v>
       </c>
       <c r="K144" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L144" t="s">
         <v>461</v>
@@ -8087,28 +8087,28 @@
         <v>13</v>
       </c>
       <c r="C145" t="s">
+        <v>31</v>
+      </c>
+      <c r="D145" t="s">
         <v>386</v>
       </c>
       <c r="E145" t="s">
-        <v>15</v>
-      </c>
-      <c r="F145" t="s">
         <v>466</v>
       </c>
       <c r="G145" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H145" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I145" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J145" t="s">
         <v>467</v>
       </c>
       <c r="K145" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L145" t="s">
         <v>461</v>
@@ -8122,28 +8122,28 @@
         <v>13</v>
       </c>
       <c r="C146" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" t="s">
         <v>386</v>
       </c>
       <c r="E146" t="s">
-        <v>15</v>
-      </c>
-      <c r="F146" t="s">
         <v>469</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I146" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J146" t="s">
         <v>470</v>
       </c>
       <c r="K146" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L146" t="s">
         <v>461</v>
@@ -8157,28 +8157,28 @@
         <v>13</v>
       </c>
       <c r="C147" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" t="s">
         <v>386</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
-      </c>
-      <c r="F147" t="s">
         <v>472</v>
       </c>
       <c r="G147" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I147" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J147" t="s">
         <v>473</v>
       </c>
       <c r="K147" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L147" t="s">
         <v>461</v>
@@ -8192,28 +8192,28 @@
         <v>13</v>
       </c>
       <c r="C148" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" t="s">
         <v>386</v>
       </c>
       <c r="E148" t="s">
-        <v>32</v>
-      </c>
-      <c r="F148" t="s">
         <v>475</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I148" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J148" t="s">
         <v>476</v>
       </c>
       <c r="K148" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L148" t="s">
         <v>461</v>
@@ -8227,28 +8227,28 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
+        <v>31</v>
+      </c>
+      <c r="D149" t="s">
         <v>386</v>
       </c>
       <c r="E149" t="s">
-        <v>15</v>
-      </c>
-      <c r="F149" t="s">
         <v>478</v>
       </c>
       <c r="G149" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H149" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I149" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J149" t="s">
         <v>479</v>
       </c>
       <c r="K149" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L149" t="s">
         <v>461</v>
@@ -8262,28 +8262,28 @@
         <v>13</v>
       </c>
       <c r="C150" t="s">
+        <v>14</v>
+      </c>
+      <c r="D150" t="s">
         <v>386</v>
       </c>
       <c r="E150" t="s">
-        <v>15</v>
-      </c>
-      <c r="F150" t="s">
         <v>481</v>
       </c>
       <c r="G150" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I150" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J150" t="s">
         <v>482</v>
       </c>
       <c r="K150" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L150" t="s">
         <v>461</v>
@@ -8297,28 +8297,28 @@
         <v>13</v>
       </c>
       <c r="C151" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" t="s">
         <v>386</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
-      </c>
-      <c r="F151" t="s">
         <v>484</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I151" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J151" t="s">
         <v>485</v>
       </c>
       <c r="K151" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L151" t="s">
         <v>461</v>
@@ -8332,28 +8332,28 @@
         <v>13</v>
       </c>
       <c r="C152" t="s">
+        <v>14</v>
+      </c>
+      <c r="D152" t="s">
         <v>386</v>
       </c>
       <c r="E152" t="s">
-        <v>15</v>
-      </c>
-      <c r="F152" t="s">
         <v>487</v>
       </c>
       <c r="G152" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I152" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J152" t="s">
         <v>488</v>
       </c>
       <c r="K152" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L152" t="s">
         <v>489</v>
@@ -8367,28 +8367,28 @@
         <v>13</v>
       </c>
       <c r="C153" t="s">
+        <v>14</v>
+      </c>
+      <c r="D153" t="s">
         <v>386</v>
       </c>
       <c r="E153" t="s">
-        <v>15</v>
-      </c>
-      <c r="F153" t="s">
         <v>491</v>
       </c>
       <c r="G153" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I153" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J153" t="s">
         <v>492</v>
       </c>
       <c r="K153" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L153" t="s">
         <v>489</v>
@@ -8402,28 +8402,28 @@
         <v>13</v>
       </c>
       <c r="C154" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" t="s">
         <v>386</v>
       </c>
       <c r="E154" t="s">
-        <v>15</v>
-      </c>
-      <c r="F154" t="s">
         <v>494</v>
       </c>
       <c r="G154" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I154" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J154" t="s">
         <v>495</v>
       </c>
       <c r="K154" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L154" t="s">
         <v>489</v>
@@ -8437,28 +8437,28 @@
         <v>13</v>
       </c>
       <c r="C155" t="s">
+        <v>14</v>
+      </c>
+      <c r="D155" t="s">
         <v>386</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
-      </c>
-      <c r="F155" t="s">
         <v>497</v>
       </c>
       <c r="G155" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I155" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J155" t="s">
         <v>498</v>
       </c>
       <c r="K155" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L155" t="s">
         <v>489</v>
@@ -8472,28 +8472,28 @@
         <v>13</v>
       </c>
       <c r="C156" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" t="s">
         <v>386</v>
       </c>
       <c r="E156" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" t="s">
         <v>500</v>
       </c>
       <c r="G156" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I156" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J156" t="s">
         <v>501</v>
       </c>
       <c r="K156" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L156" t="s">
         <v>489</v>
@@ -8507,28 +8507,28 @@
         <v>13</v>
       </c>
       <c r="C157" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" t="s">
         <v>386</v>
       </c>
       <c r="E157" t="s">
-        <v>15</v>
-      </c>
-      <c r="F157" t="s">
         <v>503</v>
       </c>
       <c r="G157" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I157" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J157" t="s">
         <v>504</v>
       </c>
       <c r="K157" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L157" t="s">
         <v>489</v>
@@ -8542,28 +8542,28 @@
         <v>13</v>
       </c>
       <c r="C158" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" t="s">
         <v>386</v>
       </c>
       <c r="E158" t="s">
-        <v>15</v>
-      </c>
-      <c r="F158" t="s">
         <v>506</v>
       </c>
       <c r="G158" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I158" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J158" t="s">
         <v>507</v>
       </c>
       <c r="K158" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L158" t="s">
         <v>489</v>
@@ -8577,28 +8577,28 @@
         <v>13</v>
       </c>
       <c r="C159" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" t="s">
         <v>386</v>
       </c>
       <c r="E159" t="s">
-        <v>15</v>
-      </c>
-      <c r="F159" t="s">
         <v>509</v>
       </c>
       <c r="G159" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I159" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J159" t="s">
         <v>510</v>
       </c>
       <c r="K159" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L159" t="s">
         <v>489</v>
@@ -8612,28 +8612,28 @@
         <v>13</v>
       </c>
       <c r="C160" t="s">
+        <v>14</v>
+      </c>
+      <c r="D160" t="s">
         <v>386</v>
       </c>
       <c r="E160" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" t="s">
         <v>512</v>
       </c>
       <c r="G160" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I160" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J160" t="s">
         <v>513</v>
       </c>
       <c r="K160" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L160" t="s">
         <v>489</v>
@@ -8647,28 +8647,28 @@
         <v>13</v>
       </c>
       <c r="C161" t="s">
+        <v>14</v>
+      </c>
+      <c r="D161" t="s">
         <v>386</v>
       </c>
       <c r="E161" t="s">
-        <v>15</v>
-      </c>
-      <c r="F161" t="s">
         <v>515</v>
       </c>
       <c r="G161" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I161" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J161" t="s">
         <v>516</v>
       </c>
       <c r="K161" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L161" t="s">
         <v>489</v>
@@ -8682,28 +8682,28 @@
         <v>13</v>
       </c>
       <c r="C162" t="s">
+        <v>14</v>
+      </c>
+      <c r="D162" t="s">
         <v>386</v>
       </c>
       <c r="E162" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" t="s">
         <v>518</v>
       </c>
       <c r="G162" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J162" t="s">
         <v>519</v>
       </c>
       <c r="K162" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L162" t="s">
         <v>489</v>
@@ -8717,28 +8717,28 @@
         <v>13</v>
       </c>
       <c r="C163" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" t="s">
         <v>386</v>
       </c>
       <c r="E163" t="s">
-        <v>15</v>
-      </c>
-      <c r="F163" t="s">
         <v>521</v>
       </c>
       <c r="G163" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I163" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J163" t="s">
         <v>522</v>
       </c>
       <c r="K163" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L163" t="s">
         <v>489</v>
@@ -8752,28 +8752,28 @@
         <v>13</v>
       </c>
       <c r="C164" t="s">
+        <v>14</v>
+      </c>
+      <c r="D164" t="s">
         <v>386</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
-      </c>
-      <c r="F164" t="s">
         <v>524</v>
       </c>
       <c r="G164" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I164" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J164" t="s">
         <v>525</v>
       </c>
       <c r="K164" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L164" t="s">
         <v>489</v>
@@ -8787,28 +8787,28 @@
         <v>13</v>
       </c>
       <c r="C165" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" t="s">
         <v>386</v>
       </c>
       <c r="E165" t="s">
-        <v>15</v>
-      </c>
-      <c r="F165" t="s">
         <v>527</v>
       </c>
       <c r="G165" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I165" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J165" t="s">
         <v>528</v>
       </c>
       <c r="K165" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L165" t="s">
         <v>489</v>
@@ -8822,28 +8822,28 @@
         <v>13</v>
       </c>
       <c r="C166" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" t="s">
         <v>386</v>
       </c>
       <c r="E166" t="s">
-        <v>15</v>
-      </c>
-      <c r="F166" t="s">
         <v>530</v>
       </c>
       <c r="G166" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J166" t="s">
         <v>531</v>
       </c>
       <c r="K166" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L166" t="s">
         <v>489</v>
@@ -8857,28 +8857,28 @@
         <v>13</v>
       </c>
       <c r="C167" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167" t="s">
         <v>386</v>
       </c>
       <c r="E167" t="s">
-        <v>15</v>
-      </c>
-      <c r="F167" t="s">
         <v>533</v>
       </c>
       <c r="G167" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J167" t="s">
         <v>534</v>
       </c>
       <c r="K167" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L167" t="s">
         <v>489</v>
@@ -8892,28 +8892,28 @@
         <v>13</v>
       </c>
       <c r="C168" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168" t="s">
         <v>386</v>
       </c>
       <c r="E168" t="s">
-        <v>15</v>
-      </c>
-      <c r="F168" t="s">
         <v>536</v>
       </c>
       <c r="G168" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J168" t="s">
         <v>537</v>
       </c>
       <c r="K168" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L168" t="s">
         <v>489</v>
@@ -8927,28 +8927,28 @@
         <v>13</v>
       </c>
       <c r="C169" t="s">
+        <v>31</v>
+      </c>
+      <c r="D169" t="s">
         <v>386</v>
       </c>
       <c r="E169" t="s">
-        <v>15</v>
-      </c>
-      <c r="F169" t="s">
         <v>539</v>
       </c>
       <c r="G169" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J169" t="s">
         <v>540</v>
       </c>
       <c r="K169" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L169" t="s">
         <v>489</v>
@@ -8962,28 +8962,28 @@
         <v>13</v>
       </c>
       <c r="C170" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" t="s">
         <v>542</v>
       </c>
       <c r="E170" t="s">
-        <v>15</v>
-      </c>
-      <c r="F170" t="s">
         <v>543</v>
       </c>
       <c r="G170" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I170" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J170" t="s">
         <v>544</v>
       </c>
       <c r="K170" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L170" t="s">
         <v>545</v>
@@ -8997,28 +8997,28 @@
         <v>13</v>
       </c>
       <c r="C171" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" t="s">
         <v>542</v>
       </c>
       <c r="E171" t="s">
-        <v>15</v>
-      </c>
-      <c r="F171" t="s">
         <v>547</v>
       </c>
       <c r="G171" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I171" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J171" t="s">
         <v>548</v>
       </c>
       <c r="K171" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L171" t="s">
         <v>545</v>
@@ -9032,28 +9032,28 @@
         <v>13</v>
       </c>
       <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
         <v>542</v>
       </c>
       <c r="E172" t="s">
-        <v>15</v>
-      </c>
-      <c r="F172" t="s">
         <v>550</v>
       </c>
       <c r="G172" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I172" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J172" t="s">
         <v>551</v>
       </c>
       <c r="K172" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L172" t="s">
         <v>545</v>
@@ -9067,28 +9067,28 @@
         <v>13</v>
       </c>
       <c r="C173" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" t="s">
         <v>542</v>
       </c>
       <c r="E173" t="s">
-        <v>15</v>
-      </c>
-      <c r="F173" t="s">
         <v>553</v>
       </c>
       <c r="G173" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I173" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J173" t="s">
         <v>554</v>
       </c>
       <c r="K173" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L173" t="s">
         <v>545</v>
@@ -9102,28 +9102,28 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" t="s">
         <v>542</v>
       </c>
       <c r="E174" t="s">
-        <v>15</v>
-      </c>
-      <c r="F174" t="s">
         <v>556</v>
       </c>
       <c r="G174" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H174" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I174" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J174" t="s">
         <v>557</v>
       </c>
       <c r="K174" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L174" t="s">
         <v>545</v>
@@ -9137,28 +9137,28 @@
         <v>13</v>
       </c>
       <c r="C175" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" t="s">
         <v>542</v>
       </c>
       <c r="E175" t="s">
-        <v>15</v>
-      </c>
-      <c r="F175" t="s">
         <v>559</v>
       </c>
       <c r="G175" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H175" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I175" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J175" t="s">
         <v>560</v>
       </c>
       <c r="K175" t="s">
-        <v>368</v>
+        <v>31</v>
       </c>
       <c r="L175" t="s">
         <v>545</v>
@@ -9172,28 +9172,28 @@
         <v>13</v>
       </c>
       <c r="C176" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" t="s">
         <v>542</v>
       </c>
       <c r="E176" t="s">
-        <v>15</v>
-      </c>
-      <c r="F176" t="s">
         <v>562</v>
       </c>
       <c r="G176" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H176" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I176" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J176" t="s">
         <v>563</v>
       </c>
       <c r="K176" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L176" t="s">
         <v>545</v>
@@ -9207,28 +9207,28 @@
         <v>13</v>
       </c>
       <c r="C177" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" t="s">
         <v>542</v>
       </c>
       <c r="E177" t="s">
-        <v>15</v>
-      </c>
-      <c r="F177" t="s">
         <v>565</v>
       </c>
       <c r="G177" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H177" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I177" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J177" t="s">
         <v>566</v>
       </c>
       <c r="K177" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L177" t="s">
         <v>545</v>
@@ -9242,28 +9242,28 @@
         <v>13</v>
       </c>
       <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" t="s">
         <v>542</v>
       </c>
       <c r="E178" t="s">
-        <v>15</v>
-      </c>
-      <c r="F178" t="s">
         <v>568</v>
       </c>
       <c r="G178" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I178" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J178" t="s">
         <v>569</v>
       </c>
       <c r="K178" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L178" t="s">
         <v>545</v>
@@ -9277,28 +9277,28 @@
         <v>13</v>
       </c>
       <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" t="s">
         <v>542</v>
       </c>
       <c r="E179" t="s">
-        <v>15</v>
-      </c>
-      <c r="F179" t="s">
         <v>571</v>
       </c>
       <c r="G179" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H179" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I179" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J179" t="s">
         <v>572</v>
       </c>
       <c r="K179" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L179" t="s">
         <v>545</v>
@@ -9312,28 +9312,28 @@
         <v>13</v>
       </c>
       <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" t="s">
         <v>542</v>
       </c>
       <c r="E180" t="s">
-        <v>15</v>
-      </c>
-      <c r="F180" t="s">
         <v>574</v>
       </c>
       <c r="G180" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I180" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J180" t="s">
         <v>575</v>
       </c>
       <c r="K180" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L180" t="s">
         <v>576</v>
@@ -9347,28 +9347,28 @@
         <v>13</v>
       </c>
       <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" t="s">
         <v>542</v>
       </c>
       <c r="E181" t="s">
-        <v>15</v>
-      </c>
-      <c r="F181" t="s">
         <v>578</v>
       </c>
       <c r="G181" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H181" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I181" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J181" t="s">
         <v>579</v>
       </c>
       <c r="K181" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L181" t="s">
         <v>576</v>
@@ -9382,28 +9382,28 @@
         <v>13</v>
       </c>
       <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" t="s">
         <v>542</v>
       </c>
       <c r="E182" t="s">
-        <v>15</v>
-      </c>
-      <c r="F182" t="s">
         <v>581</v>
       </c>
       <c r="G182" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I182" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J182" t="s">
         <v>582</v>
       </c>
       <c r="K182" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L182" t="s">
         <v>576</v>
@@ -9417,25 +9417,25 @@
         <v>584</v>
       </c>
       <c r="C183" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183" t="s">
         <v>542</v>
       </c>
-      <c r="D183" t="s">
+      <c r="F183" t="s">
         <v>585</v>
       </c>
-      <c r="E183" t="s">
-        <v>15</v>
-      </c>
       <c r="G183" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H183" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I183" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="K183" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L183" t="s">
         <v>576</v>
@@ -9449,28 +9449,28 @@
         <v>13</v>
       </c>
       <c r="C184" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184" t="s">
         <v>542</v>
       </c>
       <c r="E184" t="s">
-        <v>15</v>
-      </c>
-      <c r="F184" t="s">
         <v>587</v>
       </c>
       <c r="G184" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I184" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J184" t="s">
         <v>588</v>
       </c>
       <c r="K184" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L184" t="s">
         <v>576</v>
@@ -9484,28 +9484,28 @@
         <v>13</v>
       </c>
       <c r="C185" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185" t="s">
         <v>542</v>
       </c>
       <c r="E185" t="s">
-        <v>15</v>
-      </c>
-      <c r="F185" t="s">
         <v>590</v>
       </c>
       <c r="G185" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H185" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I185" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J185" t="s">
         <v>591</v>
       </c>
       <c r="K185" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L185" t="s">
         <v>576</v>
@@ -9519,28 +9519,28 @@
         <v>13</v>
       </c>
       <c r="C186" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" t="s">
         <v>542</v>
       </c>
       <c r="E186" t="s">
-        <v>15</v>
-      </c>
-      <c r="F186" t="s">
         <v>593</v>
       </c>
       <c r="G186" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I186" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J186" t="s">
         <v>594</v>
       </c>
       <c r="K186" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L186" t="s">
         <v>576</v>
@@ -9554,28 +9554,28 @@
         <v>13</v>
       </c>
       <c r="C187" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" t="s">
         <v>542</v>
       </c>
       <c r="E187" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" t="s">
         <v>596</v>
       </c>
       <c r="G187" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I187" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J187" t="s">
         <v>597</v>
       </c>
       <c r="K187" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L187" t="s">
         <v>576</v>
@@ -9589,28 +9589,28 @@
         <v>13</v>
       </c>
       <c r="C188" t="s">
+        <v>14</v>
+      </c>
+      <c r="D188" t="s">
         <v>542</v>
       </c>
       <c r="E188" t="s">
-        <v>15</v>
-      </c>
-      <c r="F188" t="s">
         <v>599</v>
       </c>
       <c r="G188" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I188" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J188" t="s">
         <v>600</v>
       </c>
       <c r="K188" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L188" t="s">
         <v>576</v>
@@ -9624,28 +9624,28 @@
         <v>13</v>
       </c>
       <c r="C189" t="s">
+        <v>14</v>
+      </c>
+      <c r="D189" t="s">
         <v>542</v>
       </c>
       <c r="E189" t="s">
-        <v>15</v>
-      </c>
-      <c r="F189" t="s">
         <v>602</v>
       </c>
       <c r="G189" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H189" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I189" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J189" t="s">
         <v>603</v>
       </c>
       <c r="K189" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L189" t="s">
         <v>576</v>
@@ -9659,28 +9659,28 @@
         <v>13</v>
       </c>
       <c r="C190" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190" t="s">
         <v>542</v>
       </c>
       <c r="E190" t="s">
-        <v>15</v>
-      </c>
-      <c r="F190" t="s">
         <v>605</v>
       </c>
       <c r="G190" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H190" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I190" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J190" t="s">
         <v>606</v>
       </c>
       <c r="K190" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L190" t="s">
         <v>576</v>
@@ -9694,28 +9694,28 @@
         <v>13</v>
       </c>
       <c r="C191" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" t="s">
         <v>542</v>
       </c>
       <c r="E191" t="s">
-        <v>15</v>
-      </c>
-      <c r="F191" t="s">
         <v>608</v>
       </c>
       <c r="G191" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H191" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I191" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J191" t="s">
         <v>609</v>
       </c>
       <c r="K191" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L191" t="s">
         <v>576</v>
@@ -9729,28 +9729,28 @@
         <v>13</v>
       </c>
       <c r="C192" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192" t="s">
         <v>542</v>
       </c>
       <c r="E192" t="s">
-        <v>15</v>
-      </c>
-      <c r="F192" t="s">
         <v>611</v>
       </c>
       <c r="G192" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H192" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I192" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J192" t="s">
         <v>612</v>
       </c>
       <c r="K192" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L192" t="s">
         <v>576</v>
@@ -9764,28 +9764,28 @@
         <v>13</v>
       </c>
       <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" t="s">
         <v>542</v>
       </c>
       <c r="E193" t="s">
-        <v>15</v>
-      </c>
-      <c r="F193" t="s">
         <v>614</v>
       </c>
       <c r="G193" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I193" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J193" t="s">
         <v>615</v>
       </c>
       <c r="K193" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L193" t="s">
         <v>576</v>
@@ -9799,28 +9799,28 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" t="s">
         <v>542</v>
       </c>
       <c r="E194" t="s">
-        <v>15</v>
-      </c>
-      <c r="F194" t="s">
         <v>617</v>
       </c>
       <c r="G194" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I194" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J194" t="s">
         <v>618</v>
       </c>
       <c r="K194" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L194" t="s">
         <v>576</v>
@@ -9834,28 +9834,28 @@
         <v>13</v>
       </c>
       <c r="C195" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" t="s">
         <v>542</v>
       </c>
       <c r="E195" t="s">
-        <v>15</v>
-      </c>
-      <c r="F195" t="s">
         <v>620</v>
       </c>
       <c r="G195" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I195" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J195" t="s">
         <v>621</v>
       </c>
       <c r="K195" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L195" t="s">
         <v>576</v>
@@ -9869,28 +9869,28 @@
         <v>13</v>
       </c>
       <c r="C196" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196" t="s">
         <v>542</v>
       </c>
       <c r="E196" t="s">
-        <v>15</v>
-      </c>
-      <c r="F196" t="s">
         <v>623</v>
       </c>
       <c r="G196" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I196" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J196" t="s">
         <v>624</v>
       </c>
       <c r="K196" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L196" t="s">
         <v>576</v>
@@ -9904,28 +9904,28 @@
         <v>13</v>
       </c>
       <c r="C197" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197" t="s">
         <v>542</v>
       </c>
       <c r="E197" t="s">
-        <v>15</v>
-      </c>
-      <c r="F197" t="s">
         <v>626</v>
       </c>
       <c r="G197" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H197" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I197" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J197" t="s">
         <v>627</v>
       </c>
       <c r="K197" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L197" t="s">
         <v>628</v>
@@ -9939,28 +9939,28 @@
         <v>13</v>
       </c>
       <c r="C198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198" t="s">
         <v>542</v>
       </c>
       <c r="E198" t="s">
-        <v>15</v>
-      </c>
-      <c r="F198" t="s">
         <v>630</v>
       </c>
       <c r="G198" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I198" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J198" t="s">
         <v>631</v>
       </c>
       <c r="K198" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L198" t="s">
         <v>628</v>
@@ -9974,28 +9974,28 @@
         <v>13</v>
       </c>
       <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
         <v>542</v>
       </c>
       <c r="E199" t="s">
-        <v>15</v>
-      </c>
-      <c r="F199" t="s">
         <v>633</v>
       </c>
       <c r="G199" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H199" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I199" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J199" t="s">
         <v>634</v>
       </c>
       <c r="K199" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L199" t="s">
         <v>628</v>
@@ -10009,28 +10009,28 @@
         <v>13</v>
       </c>
       <c r="C200" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200" t="s">
         <v>542</v>
       </c>
       <c r="E200" t="s">
-        <v>15</v>
-      </c>
-      <c r="F200" t="s">
         <v>636</v>
       </c>
       <c r="G200" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H200" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I200" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J200" t="s">
         <v>637</v>
       </c>
       <c r="K200" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L200" t="s">
         <v>628</v>
@@ -10044,28 +10044,28 @@
         <v>13</v>
       </c>
       <c r="C201" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" t="s">
         <v>542</v>
       </c>
       <c r="E201" t="s">
-        <v>15</v>
-      </c>
-      <c r="F201" t="s">
         <v>639</v>
       </c>
       <c r="G201" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H201" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I201" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J201" t="s">
         <v>640</v>
       </c>
       <c r="K201" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L201" t="s">
         <v>628</v>
@@ -10079,28 +10079,28 @@
         <v>13</v>
       </c>
       <c r="C202" t="s">
+        <v>14</v>
+      </c>
+      <c r="D202" t="s">
         <v>542</v>
       </c>
       <c r="E202" t="s">
-        <v>15</v>
-      </c>
-      <c r="F202" t="s">
         <v>642</v>
       </c>
       <c r="G202" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I202" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J202" t="s">
         <v>643</v>
       </c>
       <c r="K202" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L202" t="s">
         <v>628</v>
@@ -10114,28 +10114,28 @@
         <v>13</v>
       </c>
       <c r="C203" t="s">
+        <v>14</v>
+      </c>
+      <c r="D203" t="s">
         <v>542</v>
       </c>
       <c r="E203" t="s">
-        <v>15</v>
-      </c>
-      <c r="F203" t="s">
         <v>645</v>
       </c>
       <c r="G203" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H203" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I203" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J203" t="s">
         <v>646</v>
       </c>
       <c r="K203" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L203" t="s">
         <v>628</v>
@@ -10149,28 +10149,28 @@
         <v>13</v>
       </c>
       <c r="C204" t="s">
+        <v>14</v>
+      </c>
+      <c r="D204" t="s">
         <v>542</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
-      </c>
-      <c r="F204" t="s">
         <v>648</v>
       </c>
       <c r="G204" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H204" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I204" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J204" t="s">
         <v>649</v>
       </c>
       <c r="K204" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L204" t="s">
         <v>628</v>
@@ -10184,28 +10184,28 @@
         <v>13</v>
       </c>
       <c r="C205" t="s">
+        <v>14</v>
+      </c>
+      <c r="D205" t="s">
         <v>542</v>
       </c>
       <c r="E205" t="s">
-        <v>15</v>
-      </c>
-      <c r="F205" t="s">
         <v>651</v>
       </c>
       <c r="G205" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H205" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I205" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J205" t="s">
         <v>652</v>
       </c>
       <c r="K205" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L205" t="s">
         <v>628</v>
@@ -10219,28 +10219,28 @@
         <v>13</v>
       </c>
       <c r="C206" t="s">
+        <v>14</v>
+      </c>
+      <c r="D206" t="s">
         <v>542</v>
       </c>
       <c r="E206" t="s">
-        <v>15</v>
-      </c>
-      <c r="F206" t="s">
         <v>654</v>
       </c>
       <c r="G206" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I206" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J206" t="s">
         <v>655</v>
       </c>
       <c r="K206" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L206" t="s">
         <v>628</v>
@@ -10254,28 +10254,28 @@
         <v>13</v>
       </c>
       <c r="C207" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207" t="s">
         <v>542</v>
       </c>
       <c r="E207" t="s">
-        <v>15</v>
-      </c>
-      <c r="F207" t="s">
         <v>657</v>
       </c>
       <c r="G207" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H207" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I207" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J207" t="s">
         <v>658</v>
       </c>
       <c r="K207" t="s">
-        <v>368</v>
+        <v>31</v>
       </c>
       <c r="L207" t="s">
         <v>628</v>
@@ -10289,28 +10289,28 @@
         <v>13</v>
       </c>
       <c r="C208" t="s">
+        <v>14</v>
+      </c>
+      <c r="D208" t="s">
         <v>542</v>
       </c>
       <c r="E208" t="s">
-        <v>15</v>
-      </c>
-      <c r="F208" t="s">
         <v>660</v>
       </c>
       <c r="G208" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H208" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I208" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J208" t="s">
         <v>661</v>
       </c>
       <c r="K208" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L208" t="s">
         <v>628</v>
@@ -10324,28 +10324,28 @@
         <v>13</v>
       </c>
       <c r="C209" t="s">
+        <v>14</v>
+      </c>
+      <c r="D209" t="s">
         <v>542</v>
       </c>
       <c r="E209" t="s">
-        <v>15</v>
-      </c>
-      <c r="F209" t="s">
         <v>663</v>
       </c>
       <c r="G209" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H209" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I209" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J209" t="s">
         <v>664</v>
       </c>
       <c r="K209" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L209" t="s">
         <v>628</v>
@@ -10359,28 +10359,28 @@
         <v>13</v>
       </c>
       <c r="C210" t="s">
+        <v>14</v>
+      </c>
+      <c r="D210" t="s">
         <v>542</v>
       </c>
       <c r="E210" t="s">
-        <v>15</v>
-      </c>
-      <c r="F210" t="s">
         <v>666</v>
       </c>
       <c r="G210" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H210" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I210" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J210" t="s">
         <v>667</v>
       </c>
       <c r="K210" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L210" t="s">
         <v>628</v>
@@ -10394,28 +10394,28 @@
         <v>13</v>
       </c>
       <c r="C211" t="s">
+        <v>14</v>
+      </c>
+      <c r="D211" t="s">
         <v>542</v>
       </c>
       <c r="E211" t="s">
-        <v>15</v>
-      </c>
-      <c r="F211" t="s">
         <v>669</v>
       </c>
       <c r="G211" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I211" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J211" t="s">
         <v>670</v>
       </c>
       <c r="K211" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L211" t="s">
         <v>628</v>
@@ -10429,28 +10429,28 @@
         <v>13</v>
       </c>
       <c r="C212" t="s">
+        <v>14</v>
+      </c>
+      <c r="D212" t="s">
         <v>542</v>
       </c>
       <c r="E212" t="s">
-        <v>15</v>
-      </c>
-      <c r="F212" t="s">
         <v>672</v>
       </c>
       <c r="G212" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H212" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I212" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J212" t="s">
         <v>673</v>
       </c>
       <c r="K212" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L212" t="s">
         <v>628</v>
@@ -10464,28 +10464,28 @@
         <v>13</v>
       </c>
       <c r="C213" t="s">
+        <v>14</v>
+      </c>
+      <c r="D213" t="s">
         <v>542</v>
       </c>
       <c r="E213" t="s">
-        <v>15</v>
-      </c>
-      <c r="F213" t="s">
         <v>675</v>
       </c>
       <c r="G213" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H213" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I213" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J213" t="s">
         <v>676</v>
       </c>
       <c r="K213" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L213" t="s">
         <v>677</v>
@@ -10499,28 +10499,28 @@
         <v>13</v>
       </c>
       <c r="C214" t="s">
+        <v>14</v>
+      </c>
+      <c r="D214" t="s">
         <v>542</v>
       </c>
       <c r="E214" t="s">
-        <v>15</v>
-      </c>
-      <c r="F214" t="s">
         <v>679</v>
       </c>
       <c r="G214" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H214" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I214" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J214" t="s">
         <v>680</v>
       </c>
       <c r="K214" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L214" t="s">
         <v>677</v>
@@ -10534,28 +10534,28 @@
         <v>13</v>
       </c>
       <c r="C215" t="s">
+        <v>14</v>
+      </c>
+      <c r="D215" t="s">
         <v>542</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
-      </c>
-      <c r="F215" t="s">
         <v>682</v>
       </c>
       <c r="G215" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H215" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I215" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J215" t="s">
         <v>683</v>
       </c>
       <c r="K215" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L215" t="s">
         <v>677</v>
@@ -10569,28 +10569,28 @@
         <v>13</v>
       </c>
       <c r="C216" t="s">
+        <v>14</v>
+      </c>
+      <c r="D216" t="s">
         <v>542</v>
       </c>
       <c r="E216" t="s">
-        <v>15</v>
-      </c>
-      <c r="F216" t="s">
         <v>685</v>
       </c>
       <c r="G216" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H216" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I216" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J216" t="s">
         <v>686</v>
       </c>
       <c r="K216" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L216" t="s">
         <v>677</v>
@@ -10604,28 +10604,28 @@
         <v>13</v>
       </c>
       <c r="C217" t="s">
+        <v>14</v>
+      </c>
+      <c r="D217" t="s">
         <v>542</v>
       </c>
       <c r="E217" t="s">
-        <v>15</v>
-      </c>
-      <c r="F217" t="s">
         <v>688</v>
       </c>
       <c r="G217" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H217" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I217" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J217" t="s">
         <v>689</v>
       </c>
       <c r="K217" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L217" t="s">
         <v>677</v>
@@ -10639,28 +10639,28 @@
         <v>13</v>
       </c>
       <c r="C218" t="s">
+        <v>14</v>
+      </c>
+      <c r="D218" t="s">
         <v>542</v>
       </c>
       <c r="E218" t="s">
-        <v>15</v>
-      </c>
-      <c r="F218" t="s">
         <v>691</v>
       </c>
       <c r="G218" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H218" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I218" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J218" t="s">
         <v>692</v>
       </c>
       <c r="K218" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L218" t="s">
         <v>677</v>
@@ -10674,28 +10674,28 @@
         <v>13</v>
       </c>
       <c r="C219" t="s">
+        <v>14</v>
+      </c>
+      <c r="D219" t="s">
         <v>542</v>
       </c>
       <c r="E219" t="s">
-        <v>15</v>
-      </c>
-      <c r="F219" t="s">
         <v>694</v>
       </c>
       <c r="G219" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H219" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I219" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J219" t="s">
         <v>695</v>
       </c>
       <c r="K219" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L219" t="s">
         <v>677</v>
@@ -10709,28 +10709,28 @@
         <v>13</v>
       </c>
       <c r="C220" t="s">
+        <v>14</v>
+      </c>
+      <c r="D220" t="s">
         <v>542</v>
       </c>
       <c r="E220" t="s">
-        <v>15</v>
-      </c>
-      <c r="F220" t="s">
         <v>697</v>
       </c>
       <c r="G220" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H220" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I220" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J220" t="s">
         <v>698</v>
       </c>
       <c r="K220" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L220" t="s">
         <v>677</v>
@@ -10744,28 +10744,28 @@
         <v>13</v>
       </c>
       <c r="C221" t="s">
+        <v>14</v>
+      </c>
+      <c r="D221" t="s">
         <v>542</v>
       </c>
       <c r="E221" t="s">
-        <v>15</v>
-      </c>
-      <c r="F221" t="s">
         <v>700</v>
       </c>
       <c r="G221" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H221" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I221" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J221" t="s">
         <v>701</v>
       </c>
       <c r="K221" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L221" t="s">
         <v>677</v>
@@ -10779,28 +10779,28 @@
         <v>13</v>
       </c>
       <c r="C222" t="s">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
         <v>703</v>
       </c>
       <c r="E222" t="s">
-        <v>15</v>
-      </c>
-      <c r="F222" t="s">
         <v>704</v>
       </c>
       <c r="G222" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H222" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I222" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J222" t="s">
         <v>705</v>
       </c>
       <c r="K222" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L222" t="s">
         <v>706</v>
@@ -10814,28 +10814,28 @@
         <v>13</v>
       </c>
       <c r="C223" t="s">
+        <v>14</v>
+      </c>
+      <c r="D223" t="s">
         <v>703</v>
       </c>
       <c r="E223" t="s">
-        <v>15</v>
-      </c>
-      <c r="F223" t="s">
         <v>708</v>
       </c>
       <c r="G223" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H223" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I223" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J223" t="s">
         <v>709</v>
       </c>
       <c r="K223" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L223" t="s">
         <v>706</v>
@@ -10849,28 +10849,28 @@
         <v>13</v>
       </c>
       <c r="C224" t="s">
+        <v>14</v>
+      </c>
+      <c r="D224" t="s">
         <v>703</v>
       </c>
       <c r="E224" t="s">
-        <v>15</v>
-      </c>
-      <c r="F224" t="s">
         <v>711</v>
       </c>
       <c r="G224" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H224" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I224" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J224" t="s">
         <v>712</v>
       </c>
       <c r="K224" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L224" t="s">
         <v>706</v>
@@ -10884,28 +10884,28 @@
         <v>13</v>
       </c>
       <c r="C225" t="s">
+        <v>14</v>
+      </c>
+      <c r="D225" t="s">
         <v>703</v>
       </c>
       <c r="E225" t="s">
-        <v>15</v>
-      </c>
-      <c r="F225" t="s">
         <v>714</v>
       </c>
       <c r="G225" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H225" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I225" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J225" t="s">
         <v>715</v>
       </c>
       <c r="K225" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L225" t="s">
         <v>706</v>
@@ -10919,28 +10919,28 @@
         <v>13</v>
       </c>
       <c r="C226" t="s">
+        <v>14</v>
+      </c>
+      <c r="D226" t="s">
         <v>703</v>
       </c>
       <c r="E226" t="s">
-        <v>15</v>
-      </c>
-      <c r="F226" t="s">
         <v>717</v>
       </c>
       <c r="G226" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H226" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I226" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J226" t="s">
         <v>718</v>
       </c>
       <c r="K226" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L226" t="s">
         <v>706</v>
@@ -10954,28 +10954,28 @@
         <v>13</v>
       </c>
       <c r="C227" t="s">
+        <v>14</v>
+      </c>
+      <c r="D227" t="s">
         <v>703</v>
       </c>
       <c r="E227" t="s">
-        <v>15</v>
-      </c>
-      <c r="F227" t="s">
         <v>720</v>
       </c>
       <c r="G227" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H227" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I227" t="s">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="J227" t="s">
         <v>721</v>
       </c>
       <c r="K227" t="s">
-        <v>368</v>
+        <v>14</v>
       </c>
       <c r="L227" t="s">
         <v>706</v>
@@ -10989,28 +10989,28 @@
         <v>13</v>
       </c>
       <c r="C228" t="s">
+        <v>14</v>
+      </c>
+      <c r="D228" t="s">
         <v>703</v>
       </c>
       <c r="E228" t="s">
-        <v>32</v>
-      </c>
-      <c r="F228" t="s">
         <v>723</v>
       </c>
       <c r="G228" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H228" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I228" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J228" t="s">
         <v>724</v>
       </c>
       <c r="K228" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L228" t="s">
         <v>725</v>
@@ -11024,28 +11024,28 @@
         <v>13</v>
       </c>
       <c r="C229" t="s">
+        <v>14</v>
+      </c>
+      <c r="D229" t="s">
         <v>703</v>
       </c>
       <c r="E229" t="s">
-        <v>32</v>
-      </c>
-      <c r="F229" t="s">
         <v>727</v>
       </c>
       <c r="G229" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H229" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I229" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J229" t="s">
         <v>728</v>
       </c>
       <c r="K229" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L229" t="s">
         <v>725</v>
@@ -11059,28 +11059,28 @@
         <v>13</v>
       </c>
       <c r="C230" t="s">
+        <v>14</v>
+      </c>
+      <c r="D230" t="s">
         <v>703</v>
       </c>
       <c r="E230" t="s">
-        <v>32</v>
-      </c>
-      <c r="F230" t="s">
         <v>730</v>
       </c>
       <c r="G230" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H230" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I230" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J230" t="s">
         <v>731</v>
       </c>
       <c r="K230" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L230" t="s">
         <v>725</v>
@@ -11094,28 +11094,28 @@
         <v>13</v>
       </c>
       <c r="C231" t="s">
+        <v>31</v>
+      </c>
+      <c r="D231" t="s">
         <v>703</v>
       </c>
       <c r="E231" t="s">
-        <v>32</v>
-      </c>
-      <c r="F231" t="s">
         <v>733</v>
       </c>
       <c r="G231" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H231" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I231" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J231" t="s">
         <v>734</v>
       </c>
       <c r="K231" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L231" t="s">
         <v>725</v>
@@ -11129,28 +11129,28 @@
         <v>13</v>
       </c>
       <c r="C232" t="s">
+        <v>31</v>
+      </c>
+      <c r="D232" t="s">
         <v>703</v>
       </c>
       <c r="E232" t="s">
-        <v>32</v>
-      </c>
-      <c r="F232" t="s">
         <v>736</v>
       </c>
       <c r="G232" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H232" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I232" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J232" t="s">
         <v>737</v>
       </c>
       <c r="K232" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L232" t="s">
         <v>725</v>
@@ -11164,28 +11164,28 @@
         <v>13</v>
       </c>
       <c r="C233" t="s">
+        <v>14</v>
+      </c>
+      <c r="D233" t="s">
         <v>703</v>
       </c>
       <c r="E233" t="s">
-        <v>32</v>
-      </c>
-      <c r="F233" t="s">
         <v>739</v>
       </c>
       <c r="G233" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H233" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I233" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J233" t="s">
         <v>740</v>
       </c>
       <c r="K233" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L233" t="s">
         <v>741</v>
@@ -11199,28 +11199,28 @@
         <v>13</v>
       </c>
       <c r="C234" t="s">
+        <v>31</v>
+      </c>
+      <c r="D234" t="s">
         <v>703</v>
       </c>
       <c r="E234" t="s">
-        <v>32</v>
-      </c>
-      <c r="F234" t="s">
         <v>743</v>
       </c>
       <c r="G234" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H234" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I234" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J234" t="s">
         <v>744</v>
       </c>
       <c r="K234" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L234" t="s">
         <v>741</v>
@@ -11234,28 +11234,28 @@
         <v>13</v>
       </c>
       <c r="C235" t="s">
+        <v>14</v>
+      </c>
+      <c r="D235" t="s">
         <v>703</v>
       </c>
       <c r="E235" t="s">
-        <v>32</v>
-      </c>
-      <c r="F235" t="s">
         <v>746</v>
       </c>
       <c r="G235" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H235" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I235" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J235" t="s">
         <v>747</v>
       </c>
       <c r="K235" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L235" t="s">
         <v>741</v>
@@ -11269,28 +11269,28 @@
         <v>13</v>
       </c>
       <c r="C236" t="s">
+        <v>14</v>
+      </c>
+      <c r="D236" t="s">
         <v>703</v>
       </c>
       <c r="E236" t="s">
-        <v>32</v>
-      </c>
-      <c r="F236" t="s">
         <v>749</v>
       </c>
       <c r="G236" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H236" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I236" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J236" t="s">
         <v>750</v>
       </c>
       <c r="K236" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L236" t="s">
         <v>741</v>
@@ -11304,28 +11304,28 @@
         <v>13</v>
       </c>
       <c r="C237" t="s">
+        <v>14</v>
+      </c>
+      <c r="D237" t="s">
         <v>703</v>
       </c>
       <c r="E237" t="s">
-        <v>32</v>
-      </c>
-      <c r="F237" t="s">
         <v>752</v>
       </c>
       <c r="G237" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H237" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I237" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J237" t="s">
         <v>753</v>
       </c>
       <c r="K237" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L237" t="s">
         <v>741</v>
@@ -11339,28 +11339,28 @@
         <v>13</v>
       </c>
       <c r="C238" t="s">
+        <v>14</v>
+      </c>
+      <c r="D238" t="s">
         <v>703</v>
       </c>
       <c r="E238" t="s">
-        <v>32</v>
-      </c>
-      <c r="F238" t="s">
         <v>755</v>
       </c>
       <c r="G238" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H238" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I238" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J238" t="s">
         <v>756</v>
       </c>
       <c r="K238" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L238" t="s">
         <v>741</v>
@@ -11374,28 +11374,28 @@
         <v>13</v>
       </c>
       <c r="C239" t="s">
+        <v>14</v>
+      </c>
+      <c r="D239" t="s">
         <v>703</v>
       </c>
       <c r="E239" t="s">
-        <v>32</v>
-      </c>
-      <c r="F239" t="s">
         <v>758</v>
       </c>
       <c r="G239" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H239" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I239" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J239" t="s">
         <v>759</v>
       </c>
       <c r="K239" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L239" t="s">
         <v>741</v>
@@ -11409,28 +11409,28 @@
         <v>13</v>
       </c>
       <c r="C240" t="s">
+        <v>14</v>
+      </c>
+      <c r="D240" t="s">
         <v>703</v>
       </c>
       <c r="E240" t="s">
-        <v>15</v>
-      </c>
-      <c r="F240" t="s">
         <v>761</v>
       </c>
       <c r="G240" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H240" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I240" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J240" t="s">
         <v>762</v>
       </c>
       <c r="K240" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L240" t="s">
         <v>741</v>
@@ -11444,28 +11444,28 @@
         <v>13</v>
       </c>
       <c r="C241" t="s">
+        <v>14</v>
+      </c>
+      <c r="D241" t="s">
         <v>703</v>
       </c>
       <c r="E241" t="s">
-        <v>32</v>
-      </c>
-      <c r="F241" t="s">
         <v>764</v>
       </c>
       <c r="G241" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H241" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I241" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J241" t="s">
         <v>765</v>
       </c>
       <c r="K241" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L241" t="s">
         <v>766</v>
@@ -11479,28 +11479,28 @@
         <v>13</v>
       </c>
       <c r="C242" t="s">
+        <v>14</v>
+      </c>
+      <c r="D242" t="s">
         <v>703</v>
       </c>
       <c r="E242" t="s">
-        <v>32</v>
-      </c>
-      <c r="F242" t="s">
         <v>768</v>
       </c>
       <c r="G242" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H242" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I242" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J242" t="s">
         <v>769</v>
       </c>
       <c r="K242" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L242" t="s">
         <v>766</v>
@@ -11514,28 +11514,28 @@
         <v>13</v>
       </c>
       <c r="C243" t="s">
+        <v>14</v>
+      </c>
+      <c r="D243" t="s">
         <v>703</v>
       </c>
       <c r="E243" t="s">
-        <v>32</v>
-      </c>
-      <c r="F243" t="s">
         <v>771</v>
       </c>
       <c r="G243" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H243" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I243" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J243" t="s">
         <v>772</v>
       </c>
       <c r="K243" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L243" t="s">
         <v>766</v>
@@ -11549,28 +11549,28 @@
         <v>13</v>
       </c>
       <c r="C244" t="s">
+        <v>14</v>
+      </c>
+      <c r="D244" t="s">
         <v>703</v>
       </c>
       <c r="E244" t="s">
-        <v>32</v>
-      </c>
-      <c r="F244" t="s">
         <v>774</v>
       </c>
       <c r="G244" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H244" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I244" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J244" t="s">
         <v>775</v>
       </c>
       <c r="K244" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L244" t="s">
         <v>766</v>
@@ -11584,28 +11584,28 @@
         <v>13</v>
       </c>
       <c r="C245" t="s">
+        <v>14</v>
+      </c>
+      <c r="D245" t="s">
         <v>703</v>
       </c>
       <c r="E245" t="s">
-        <v>15</v>
-      </c>
-      <c r="F245" t="s">
         <v>777</v>
       </c>
       <c r="G245" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H245" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I245" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J245" t="s">
         <v>778</v>
       </c>
       <c r="K245" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L245" t="s">
         <v>766</v>
@@ -11619,28 +11619,28 @@
         <v>13</v>
       </c>
       <c r="C246" t="s">
+        <v>14</v>
+      </c>
+      <c r="D246" t="s">
         <v>703</v>
       </c>
       <c r="E246" t="s">
-        <v>32</v>
-      </c>
-      <c r="F246" t="s">
         <v>780</v>
       </c>
       <c r="G246" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H246" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I246" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J246" t="s">
         <v>781</v>
       </c>
       <c r="K246" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L246" t="s">
         <v>766</v>
@@ -11654,28 +11654,28 @@
         <v>13</v>
       </c>
       <c r="C247" t="s">
+        <v>14</v>
+      </c>
+      <c r="D247" t="s">
         <v>703</v>
       </c>
       <c r="E247" t="s">
-        <v>15</v>
-      </c>
-      <c r="F247" t="s">
         <v>783</v>
       </c>
       <c r="G247" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H247" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I247" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J247" t="s">
         <v>784</v>
       </c>
       <c r="K247" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L247" t="s">
         <v>766</v>
@@ -11689,28 +11689,28 @@
         <v>13</v>
       </c>
       <c r="C248" t="s">
+        <v>14</v>
+      </c>
+      <c r="D248" t="s">
         <v>703</v>
       </c>
       <c r="E248" t="s">
-        <v>32</v>
-      </c>
-      <c r="F248" t="s">
         <v>786</v>
       </c>
       <c r="G248" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H248" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I248" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J248" t="s">
         <v>787</v>
       </c>
       <c r="K248" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L248" t="s">
         <v>766</v>
@@ -11724,28 +11724,28 @@
         <v>13</v>
       </c>
       <c r="C249" t="s">
+        <v>31</v>
+      </c>
+      <c r="D249" t="s">
         <v>703</v>
       </c>
       <c r="E249" t="s">
-        <v>32</v>
-      </c>
-      <c r="F249" t="s">
         <v>789</v>
       </c>
       <c r="G249" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H249" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I249" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J249" t="s">
         <v>790</v>
       </c>
       <c r="K249" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L249" t="s">
         <v>766</v>
@@ -11759,28 +11759,28 @@
         <v>13</v>
       </c>
       <c r="C250" t="s">
+        <v>14</v>
+      </c>
+      <c r="D250" t="s">
         <v>703</v>
       </c>
       <c r="E250" t="s">
-        <v>15</v>
-      </c>
-      <c r="F250" t="s">
         <v>792</v>
       </c>
       <c r="G250" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I250" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J250" t="s">
         <v>793</v>
       </c>
       <c r="K250" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L250" t="s">
         <v>766</v>
